--- a/Datos/PIB mensual per capita.xlsx
+++ b/Datos/PIB mensual per capita.xlsx
@@ -1,24 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bancodelarepublica-my.sharepoint.com/personal/ojaulime_banrep_gov_co/Documents/Documents/Research/MP transmission in Colombia/Monetary-Policy-Shocks-and-Central-bank-information-in-Colombia/Datos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Disco C\Repositorios Git\Monetary-Policy-Shocks-and-Central-bank-information-in-Colombia\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{20423DA7-42DD-47FA-89D0-B6CDD30B5E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF9E31CF-6268-462F-9901-3F3772BCEF5F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7439396A-9292-4B5D-A46D-54918C37A183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{9535A740-7E69-41C9-8479-535D748B30AD}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9535A740-7E69-41C9-8479-535D748B30AD}"/>
   </bookViews>
   <sheets>
     <sheet name="Mensual_Values" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-    <externalReference r:id="rId3"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -596,1327 +592,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Nacional_1950_2017"/>
-      <sheetName val="Hoja1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="A2"/>
-          <cell r="B2"/>
-          <cell r="C2"/>
-        </row>
-        <row r="3">
-          <cell r="A3"/>
-          <cell r="B3"/>
-          <cell r="C3"/>
-        </row>
-        <row r="4">
-          <cell r="A4"/>
-          <cell r="B4"/>
-          <cell r="C4"/>
-        </row>
-        <row r="5">
-          <cell r="A5"/>
-          <cell r="B5"/>
-          <cell r="C5"/>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>PROYECCIONES DE POBLACIÓN NACIONAL POR ÁREA.</v>
-          </cell>
-          <cell r="B6"/>
-          <cell r="C6"/>
-        </row>
-        <row r="7">
-          <cell r="A7"/>
-          <cell r="B7"/>
-          <cell r="C7"/>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>PROYECCIONES DE POBLACIÓN A NIVEL NACIONAL. PERIODO 1950 - 2017.</v>
-          </cell>
-          <cell r="B8"/>
-          <cell r="C8"/>
-        </row>
-        <row r="9">
-          <cell r="A9"/>
-          <cell r="B9"/>
-          <cell r="C9"/>
-        </row>
-        <row r="10">
-          <cell r="A10"/>
-          <cell r="B10"/>
-          <cell r="C10"/>
-        </row>
-        <row r="11">
-          <cell r="A11"/>
-          <cell r="B11"/>
-          <cell r="C11"/>
-        </row>
-        <row r="12">
-          <cell r="A12" t="str">
-            <v>DP</v>
-          </cell>
-          <cell r="B12" t="str">
-            <v>DPNOM</v>
-          </cell>
-          <cell r="C12" t="str">
-            <v>AÑO</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B13" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C13">
-            <v>1950</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B14" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C14">
-            <v>1950</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B15" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C15">
-            <v>1950</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B16" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C16">
-            <v>1951</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B17" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C17">
-            <v>1951</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B18" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C18">
-            <v>1951</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B19" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C19">
-            <v>1952</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B20" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C20">
-            <v>1952</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B21" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C21">
-            <v>1952</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B22" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C22">
-            <v>1953</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B23" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C23">
-            <v>1953</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B24" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C24">
-            <v>1953</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B25" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C25">
-            <v>1954</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B26" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C26">
-            <v>1954</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B27" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C27">
-            <v>1954</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B28" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C28">
-            <v>1955</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B29" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C29">
-            <v>1955</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B30" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C30">
-            <v>1955</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B31" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C31">
-            <v>1956</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B32" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C32">
-            <v>1956</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B33" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C33">
-            <v>1956</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="A34" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B34" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C34">
-            <v>1957</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="A35" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B35" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C35">
-            <v>1957</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B36" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C36">
-            <v>1957</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B37" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C37">
-            <v>1958</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="A38" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B38" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C38">
-            <v>1958</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="A39" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B39" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C39">
-            <v>1958</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="A40" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B40" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C40">
-            <v>1959</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="A41" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B41" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C41">
-            <v>1959</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="A42" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B42" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C42">
-            <v>1959</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="A43" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B43" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C43">
-            <v>1960</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="A44" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B44" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C44">
-            <v>1960</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="A45" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B45" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C45">
-            <v>1960</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="A46" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B46" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C46">
-            <v>1961</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="A47" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B47" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C47">
-            <v>1961</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="A48" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B48" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C48">
-            <v>1961</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="A49" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B49" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C49">
-            <v>1962</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="A50" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B50" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C50">
-            <v>1962</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="A51" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B51" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C51">
-            <v>1962</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="A52" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B52" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C52">
-            <v>1963</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="A53" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B53" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C53">
-            <v>1963</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="A54" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B54" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C54">
-            <v>1963</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="A55" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B55" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C55">
-            <v>1964</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="A56" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B56" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C56">
-            <v>1964</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="A57" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B57" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C57">
-            <v>1964</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="A58" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B58" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C58">
-            <v>1965</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="A59" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B59" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C59">
-            <v>1965</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="A60" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B60" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C60">
-            <v>1965</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="A61" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B61" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C61">
-            <v>1966</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="A62" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B62" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C62">
-            <v>1966</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="A63" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B63" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C63">
-            <v>1966</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="A64" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B64" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C64">
-            <v>1967</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="A65" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B65" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C65">
-            <v>1967</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="A66" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B66" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C66">
-            <v>1967</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="A67" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B67" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C67">
-            <v>1968</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="A68" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B68" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C68">
-            <v>1968</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="A69" t="str">
-            <v>00</v>
-          </cell>
-          <cell r="B69" t="str">
-            <v>Nacional</v>
-          </cell>
-          <cell r="C69">
-            <v>1968</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Índice"/>
-      <sheetName val="PPED"/>
-      <sheetName val="PobNacionalxÁrea"/>
-      <sheetName val="Hoja1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
-        <row r="2">
-          <cell r="A2">
-            <v>2018</v>
-          </cell>
-          <cell r="B2" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C2">
-            <v>48258494</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3">
-            <v>2019</v>
-          </cell>
-          <cell r="B3" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C3">
-            <v>49266526</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4">
-            <v>2020</v>
-          </cell>
-          <cell r="B4" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C4">
-            <v>50390790</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5">
-            <v>2021</v>
-          </cell>
-          <cell r="B5" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C5">
-            <v>51115637</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6">
-            <v>2022</v>
-          </cell>
-          <cell r="B6" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C6">
-            <v>51643565</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7">
-            <v>2023</v>
-          </cell>
-          <cell r="B7" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C7">
-            <v>52117067</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8">
-            <v>2024</v>
-          </cell>
-          <cell r="B8" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C8">
-            <v>52613753</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9">
-            <v>2025</v>
-          </cell>
-          <cell r="B9" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C9">
-            <v>53057212</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10">
-            <v>2026</v>
-          </cell>
-          <cell r="B10" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C10">
-            <v>53399171</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11">
-            <v>2027</v>
-          </cell>
-          <cell r="B11" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C11">
-            <v>53712233</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12">
-            <v>2028</v>
-          </cell>
-          <cell r="B12" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C12">
-            <v>54001502</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13">
-            <v>2029</v>
-          </cell>
-          <cell r="B13" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C13">
-            <v>54269406</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14">
-            <v>2030</v>
-          </cell>
-          <cell r="B14" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C14">
-            <v>54518223</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15">
-            <v>2031</v>
-          </cell>
-          <cell r="B15" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C15">
-            <v>54747818</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16">
-            <v>2032</v>
-          </cell>
-          <cell r="B16" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C16">
-            <v>54958383</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17">
-            <v>2033</v>
-          </cell>
-          <cell r="B17" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C17">
-            <v>55149988</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18">
-            <v>2034</v>
-          </cell>
-          <cell r="B18" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C18">
-            <v>55322674</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19">
-            <v>2035</v>
-          </cell>
-          <cell r="B19" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C19">
-            <v>55476504</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20">
-            <v>2036</v>
-          </cell>
-          <cell r="B20" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C20">
-            <v>55611578</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21">
-            <v>2037</v>
-          </cell>
-          <cell r="B21" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C21">
-            <v>55728042</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22">
-            <v>2038</v>
-          </cell>
-          <cell r="B22" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C22">
-            <v>55826079</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23">
-            <v>2039</v>
-          </cell>
-          <cell r="B23" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C23">
-            <v>55905896</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24">
-            <v>2040</v>
-          </cell>
-          <cell r="B24" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C24">
-            <v>55967762</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25">
-            <v>2041</v>
-          </cell>
-          <cell r="B25" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C25">
-            <v>56011924</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26">
-            <v>2042</v>
-          </cell>
-          <cell r="B26" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C26">
-            <v>56038651</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27">
-            <v>2043</v>
-          </cell>
-          <cell r="B27" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C27">
-            <v>56048194</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28">
-            <v>2044</v>
-          </cell>
-          <cell r="B28" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C28">
-            <v>56040786</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29">
-            <v>2045</v>
-          </cell>
-          <cell r="B29" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C29">
-            <v>56016662</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30">
-            <v>2046</v>
-          </cell>
-          <cell r="B30" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C30">
-            <v>55976045</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31">
-            <v>2047</v>
-          </cell>
-          <cell r="B31" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C31">
-            <v>55919179</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32">
-            <v>2048</v>
-          </cell>
-          <cell r="B32" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C32">
-            <v>55846298</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33">
-            <v>2049</v>
-          </cell>
-          <cell r="B33" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C33">
-            <v>55757657</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="A34">
-            <v>2050</v>
-          </cell>
-          <cell r="B34" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C34">
-            <v>55653490</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="A35">
-            <v>2051</v>
-          </cell>
-          <cell r="B35" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C35">
-            <v>55534043</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36">
-            <v>2052</v>
-          </cell>
-          <cell r="B36" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C36">
-            <v>55399539</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37">
-            <v>2053</v>
-          </cell>
-          <cell r="B37" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C37">
-            <v>55250202</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="A38">
-            <v>2054</v>
-          </cell>
-          <cell r="B38" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C38">
-            <v>55086260</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="A39">
-            <v>2055</v>
-          </cell>
-          <cell r="B39" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C39">
-            <v>54907921</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="A40">
-            <v>2056</v>
-          </cell>
-          <cell r="B40" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C40">
-            <v>54715374</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="A41">
-            <v>2057</v>
-          </cell>
-          <cell r="B41" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C41">
-            <v>54508782</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="A42">
-            <v>2058</v>
-          </cell>
-          <cell r="B42" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C42">
-            <v>54288293</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="A43">
-            <v>2059</v>
-          </cell>
-          <cell r="B43" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C43">
-            <v>54054043</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="A44">
-            <v>2060</v>
-          </cell>
-          <cell r="B44" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C44">
-            <v>53806118</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="A45">
-            <v>2061</v>
-          </cell>
-          <cell r="B45" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C45">
-            <v>53544613</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="A46">
-            <v>2062</v>
-          </cell>
-          <cell r="B46" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C46">
-            <v>53269610</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="A47">
-            <v>2063</v>
-          </cell>
-          <cell r="B47" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C47">
-            <v>52981169</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="A48">
-            <v>2064</v>
-          </cell>
-          <cell r="B48" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C48">
-            <v>52679381</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="A49">
-            <v>2065</v>
-          </cell>
-          <cell r="B49" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C49">
-            <v>52364311</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="A50">
-            <v>2066</v>
-          </cell>
-          <cell r="B50" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C50">
-            <v>52036013</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="A51">
-            <v>2067</v>
-          </cell>
-          <cell r="B51" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C51">
-            <v>51694579</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="A52">
-            <v>2068</v>
-          </cell>
-          <cell r="B52" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C52">
-            <v>51340058</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="A53">
-            <v>2069</v>
-          </cell>
-          <cell r="B53" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C53">
-            <v>50972537</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="A54">
-            <v>2070</v>
-          </cell>
-          <cell r="B54" t="str">
-            <v>Total</v>
-          </cell>
-          <cell r="C54">
-            <v>50592097</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
@@ -2235,9 +910,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11F4FC61-3FA9-4B34-8553-92A3C9D4856C}">
   <dimension ref="A1:H253"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>1</v>
       </c>
@@ -2257,7 +932,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>38353</v>
       </c>
@@ -2272,20 +947,19 @@
         <f>EXP(C2)</f>
         <v>124839.13658945698</v>
       </c>
-      <c r="E2" t="e">
-        <f>VLOOKUP(B2,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F2" t="e">
-        <f>D2*1000000000/E2</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G2" t="e">
+      <c r="E2">
+        <v>41671878</v>
+      </c>
+      <c r="F2">
+        <f>D2*10000000/E2</f>
+        <v>29957.645918779323</v>
+      </c>
+      <c r="G2">
         <f>LN(F2)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.307539860404505</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>38384</v>
       </c>
@@ -2300,20 +974,19 @@
         <f t="shared" ref="D3:D66" si="1">EXP(C3)</f>
         <v>126376.08023012828</v>
       </c>
-      <c r="E3" t="e">
-        <f>VLOOKUP(B3,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F3" t="e">
-        <f t="shared" ref="F3:F66" si="2">D3*1000000000/E3</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G3" t="e">
+      <c r="E3">
+        <v>41671878</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F66" si="2">D3*10000000/E3</f>
+        <v>30326.466263442286</v>
+      </c>
+      <c r="G3">
         <f t="shared" ref="G3:G66" si="3">LN(F3)</f>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.319776084282006</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>38412</v>
       </c>
@@ -2328,20 +1001,19 @@
         <f t="shared" si="1"/>
         <v>126785.65018268391</v>
       </c>
-      <c r="E4" t="e">
-        <f>VLOOKUP(B4,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F4" t="e">
+      <c r="E4">
+        <v>41671878</v>
+      </c>
+      <c r="F4">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G4" t="e">
+        <v>30424.750759417158</v>
+      </c>
+      <c r="G4">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.323011725855606</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>38443</v>
       </c>
@@ -2356,20 +1028,19 @@
         <f t="shared" si="1"/>
         <v>129737.97375360945</v>
       </c>
-      <c r="E5" t="e">
-        <f>VLOOKUP(B5,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F5" t="e">
+      <c r="E5">
+        <v>41671878</v>
+      </c>
+      <c r="F5">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G5" t="e">
+        <v>31133.219806798592</v>
+      </c>
+      <c r="G5">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.346030689079605</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>38473</v>
       </c>
@@ -2384,20 +1055,19 @@
         <f t="shared" si="1"/>
         <v>128253.09533010586</v>
       </c>
-      <c r="E6" t="e">
-        <f>VLOOKUP(B6,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F6" t="e">
+      <c r="E6">
+        <v>41671878</v>
+      </c>
+      <c r="F6">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G6" t="e">
+        <v>30776.89355159512</v>
+      </c>
+      <c r="G6">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.334519478050003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>38504</v>
       </c>
@@ -2412,20 +1082,19 @@
         <f t="shared" si="1"/>
         <v>129347.06968883204</v>
       </c>
-      <c r="E7" t="e">
-        <f>VLOOKUP(B7,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F7" t="e">
+      <c r="E7">
+        <v>41671878</v>
+      </c>
+      <c r="F7">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G7" t="e">
+        <v>31039.414563661383</v>
+      </c>
+      <c r="G7">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.343013113412505</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>38534</v>
       </c>
@@ -2440,20 +1109,19 @@
         <f t="shared" si="1"/>
         <v>127618.76776550814</v>
       </c>
-      <c r="E8" t="e">
-        <f>VLOOKUP(B8,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F8" t="e">
+      <c r="E8">
+        <v>41671878</v>
+      </c>
+      <c r="F8">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G8" t="e">
+        <v>30624.673974498612</v>
+      </c>
+      <c r="G8">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.329561302059703</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>38565</v>
       </c>
@@ -2468,20 +1136,19 @@
         <f t="shared" si="1"/>
         <v>129387.38516314505</v>
       </c>
-      <c r="E9" t="e">
-        <f>VLOOKUP(B9,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F9" t="e">
+      <c r="E9">
+        <v>41671878</v>
+      </c>
+      <c r="F9">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G9" t="e">
+        <v>31049.089067486962</v>
+      </c>
+      <c r="G9">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.343324749330206</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>38596</v>
       </c>
@@ -2496,20 +1163,19 @@
         <f t="shared" si="1"/>
         <v>129089.51778142918</v>
       </c>
-      <c r="E10" t="e">
-        <f>VLOOKUP(B10,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F10" t="e">
+      <c r="E10">
+        <v>41671878</v>
+      </c>
+      <c r="F10">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G10" t="e">
+        <v>30977.609835925603</v>
+      </c>
+      <c r="G10">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.341019959152206</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>38626</v>
       </c>
@@ -2524,20 +1190,19 @@
         <f t="shared" si="1"/>
         <v>129474.62893141054</v>
       </c>
-      <c r="E11" t="e">
-        <f>VLOOKUP(B11,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F11" t="e">
+      <c r="E11">
+        <v>41671878</v>
+      </c>
+      <c r="F11">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G11" t="e">
+        <v>31070.024953377564</v>
+      </c>
+      <c r="G11">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.343998805520906</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>38657</v>
       </c>
@@ -2552,20 +1217,19 @@
         <f t="shared" si="1"/>
         <v>130169.48361775282</v>
       </c>
-      <c r="E12" t="e">
-        <f>VLOOKUP(B12,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F12" t="e">
+      <c r="E12">
+        <v>41671878</v>
+      </c>
+      <c r="F12">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G12" t="e">
+        <v>31236.769223060408</v>
+      </c>
+      <c r="G12">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.349351180649803</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>38687</v>
       </c>
@@ -2580,20 +1244,19 @@
         <f t="shared" si="1"/>
         <v>133535.9774056334</v>
       </c>
-      <c r="E13" t="e">
-        <f>VLOOKUP(B13,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F13" t="e">
+      <c r="E13">
+        <v>41671878</v>
+      </c>
+      <c r="F13">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G13" t="e">
+        <v>32044.626691802419</v>
+      </c>
+      <c r="G13">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.374884794371406</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>38718</v>
       </c>
@@ -2608,20 +1271,19 @@
         <f t="shared" si="1"/>
         <v>133029.46317470097</v>
       </c>
-      <c r="E14" t="e">
-        <f>VLOOKUP(B14,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F14" t="e">
+      <c r="E14">
+        <v>42170126</v>
+      </c>
+      <c r="F14">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G14" t="e">
+        <v>31545.90127966442</v>
+      </c>
+      <c r="G14">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.359198947633546</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>38749</v>
       </c>
@@ -2636,20 +1298,19 @@
         <f t="shared" si="1"/>
         <v>133976.37369934731</v>
       </c>
-      <c r="E15" t="e">
-        <f>VLOOKUP(B15,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F15" t="e">
+      <c r="E15">
+        <v>42170126</v>
+      </c>
+      <c r="F15">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G15" t="e">
+        <v>31770.446618856986</v>
+      </c>
+      <c r="G15">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.366291785045046</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>38777</v>
       </c>
@@ -2664,20 +1325,19 @@
         <f t="shared" si="1"/>
         <v>135339.21532842648</v>
       </c>
-      <c r="E16" t="e">
-        <f>VLOOKUP(B16,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F16" t="e">
+      <c r="E16">
+        <v>42170126</v>
+      </c>
+      <c r="F16">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G16" t="e">
+        <v>32093.623653964536</v>
+      </c>
+      <c r="G16">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.376412649323147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>38808</v>
       </c>
@@ -2692,20 +1352,19 @@
         <f t="shared" si="1"/>
         <v>134950.4995853052</v>
       </c>
-      <c r="E17" t="e">
-        <f>VLOOKUP(B17,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F17" t="e">
+      <c r="E17">
+        <v>42170126</v>
+      </c>
+      <c r="F17">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G17" t="e">
+        <v>32001.445664474704</v>
+      </c>
+      <c r="G17">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.373536357776247</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>38838</v>
       </c>
@@ -2720,20 +1379,19 @@
         <f t="shared" si="1"/>
         <v>136950.13406697722</v>
       </c>
-      <c r="E18" t="e">
-        <f>VLOOKUP(B18,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F18" t="e">
+      <c r="E18">
+        <v>42170126</v>
+      </c>
+      <c r="F18">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G18" t="e">
+        <v>32475.62837895652</v>
+      </c>
+      <c r="G18">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.388245190973047</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>38869</v>
       </c>
@@ -2748,20 +1406,19 @@
         <f t="shared" si="1"/>
         <v>135949.0477902276</v>
       </c>
-      <c r="E19" t="e">
-        <f>VLOOKUP(B19,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F19" t="e">
+      <c r="E19">
+        <v>42170126</v>
+      </c>
+      <c r="F19">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G19" t="e">
+        <v>32238.236089270307</v>
+      </c>
+      <c r="G19">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.380908483252547</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>38899</v>
       </c>
@@ -2776,20 +1433,19 @@
         <f t="shared" si="1"/>
         <v>136992.01603426065</v>
       </c>
-      <c r="E20" t="e">
-        <f>VLOOKUP(B20,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F20" t="e">
+      <c r="E20">
+        <v>42170126</v>
+      </c>
+      <c r="F20">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G20" t="e">
+        <v>32485.560046526927</v>
+      </c>
+      <c r="G20">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.388550963323846</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>38930</v>
       </c>
@@ -2804,20 +1460,19 @@
         <f t="shared" si="1"/>
         <v>138720.57165835355</v>
       </c>
-      <c r="E21" t="e">
-        <f>VLOOKUP(B21,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F21" t="e">
+      <c r="E21">
+        <v>42170126</v>
+      </c>
+      <c r="F21">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G21" t="e">
+        <v>32895.460558584426</v>
+      </c>
+      <c r="G21">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.401089950291047</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>38961</v>
       </c>
@@ -2832,20 +1487,19 @@
         <f t="shared" si="1"/>
         <v>140077.04351579843</v>
       </c>
-      <c r="E22" t="e">
-        <f>VLOOKUP(B22,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F22" t="e">
+      <c r="E22">
+        <v>42170126</v>
+      </c>
+      <c r="F22">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G22" t="e">
+        <v>33217.127099833291</v>
+      </c>
+      <c r="G22">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.410820898387046</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>38991</v>
       </c>
@@ -2860,20 +1514,19 @@
         <f t="shared" si="1"/>
         <v>139965.93625237199</v>
       </c>
-      <c r="E23" t="e">
-        <f>VLOOKUP(B23,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F23" t="e">
+      <c r="E23">
+        <v>42170126</v>
+      </c>
+      <c r="F23">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G23" t="e">
+        <v>33190.779712721749</v>
+      </c>
+      <c r="G23">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.410027396837046</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>39022</v>
       </c>
@@ -2888,20 +1541,19 @@
         <f t="shared" si="1"/>
         <v>141703.32575310869</v>
       </c>
-      <c r="E24" t="e">
-        <f>VLOOKUP(B24,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F24" t="e">
+      <c r="E24">
+        <v>42170126</v>
+      </c>
+      <c r="F24">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G24" t="e">
+        <v>33602.775043429727</v>
+      </c>
+      <c r="G24">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.422363933119147</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>39052</v>
       </c>
@@ -2916,20 +1568,19 @@
         <f t="shared" si="1"/>
         <v>140691.4374849704</v>
       </c>
-      <c r="E25" t="e">
-        <f>VLOOKUP(B25,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F25" t="e">
+      <c r="E25">
+        <v>42170126</v>
+      </c>
+      <c r="F25">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G25" t="e">
+        <v>33362.821226801745</v>
+      </c>
+      <c r="G25">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.415197422045647</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>39083</v>
       </c>
@@ -2944,20 +1595,19 @@
         <f t="shared" si="1"/>
         <v>141755.98035485664</v>
       </c>
-      <c r="E26" t="e">
-        <f>VLOOKUP(B26,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F26" t="e">
+      <c r="E26">
+        <v>42658630</v>
+      </c>
+      <c r="F26">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G26" t="e">
+        <v>33230.317137436585</v>
+      </c>
+      <c r="G26">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.411217905011693</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>39114</v>
       </c>
@@ -2972,20 +1622,19 @@
         <f t="shared" si="1"/>
         <v>143484.21245765063</v>
       </c>
-      <c r="E27" t="e">
-        <f>VLOOKUP(B27,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F27" t="e">
+      <c r="E27">
+        <v>42658630</v>
+      </c>
+      <c r="F27">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G27" t="e">
+        <v>33635.447846696115</v>
+      </c>
+      <c r="G27">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.423335785272092</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>39142</v>
       </c>
@@ -3000,20 +1649,19 @@
         <f t="shared" si="1"/>
         <v>144456.32467089948</v>
       </c>
-      <c r="E28" t="e">
-        <f>VLOOKUP(B28,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F28" t="e">
+      <c r="E28">
+        <v>42658630</v>
+      </c>
+      <c r="F28">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G28" t="e">
+        <v>33863.329570335358</v>
+      </c>
+      <c r="G28">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.430087984294392</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>39173</v>
       </c>
@@ -3028,20 +1676,19 @@
         <f t="shared" si="1"/>
         <v>143246.86597689276</v>
       </c>
-      <c r="E29" t="e">
-        <f>VLOOKUP(B29,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F29" t="e">
+      <c r="E29">
+        <v>42658630</v>
+      </c>
+      <c r="F29">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G29" t="e">
+        <v>33579.809285223819</v>
+      </c>
+      <c r="G29">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.421680251199794</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>39203</v>
       </c>
@@ -3056,20 +1703,19 @@
         <f t="shared" si="1"/>
         <v>145566.2403650535</v>
       </c>
-      <c r="E30" t="e">
-        <f>VLOOKUP(B30,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F30" t="e">
+      <c r="E30">
+        <v>42658630</v>
+      </c>
+      <c r="F30">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G30" t="e">
+        <v>34123.515069530709</v>
+      </c>
+      <c r="G30">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.437742017094493</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>39234</v>
       </c>
@@ -3084,20 +1730,19 @@
         <f t="shared" si="1"/>
         <v>146589.85900107256</v>
       </c>
-      <c r="E31" t="e">
-        <f>VLOOKUP(B31,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F31" t="e">
+      <c r="E31">
+        <v>42658630</v>
+      </c>
+      <c r="F31">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G31" t="e">
+        <v>34363.470885275165</v>
+      </c>
+      <c r="G31">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.444749386283894</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>39264</v>
       </c>
@@ -3112,20 +1757,19 @@
         <f t="shared" si="1"/>
         <v>146657.72646060152</v>
       </c>
-      <c r="E32" t="e">
-        <f>VLOOKUP(B32,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F32" t="e">
+      <c r="E32">
+        <v>42658630</v>
+      </c>
+      <c r="F32">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G32" t="e">
+        <v>34379.380317793024</v>
+      </c>
+      <c r="G32">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+        <v>10.445212254277394</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>39295</v>
       </c>
@@ -3140,20 +1784,19 @@
         <f t="shared" si="1"/>
         <v>148479.13652055588</v>
       </c>
-      <c r="E33" t="e">
-        <f>VLOOKUP(B33,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F33" t="e">
+      <c r="E33">
+        <v>42658630</v>
+      </c>
+      <c r="F33">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G33" t="e">
+        <v>34806.353725038964</v>
+      </c>
+      <c r="G33">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+        <v>10.457555227402892</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>39326</v>
       </c>
@@ -3168,20 +1811,19 @@
         <f t="shared" si="1"/>
         <v>149299.76328671243</v>
       </c>
-      <c r="E34" t="e">
-        <f>VLOOKUP(B34,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F34" t="e">
+      <c r="E34">
+        <v>42658630</v>
+      </c>
+      <c r="F34">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G34" t="e">
+        <v>34998.724358169129</v>
+      </c>
+      <c r="G34">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+        <v>10.463066892897892</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>39356</v>
       </c>
@@ -3196,20 +1838,19 @@
         <f t="shared" si="1"/>
         <v>149496.04360482158</v>
       </c>
-      <c r="E35" t="e">
-        <f>VLOOKUP(B35,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F35" t="e">
+      <c r="E35">
+        <v>42658630</v>
+      </c>
+      <c r="F35">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G35" t="e">
+        <v>35044.736224492342</v>
+      </c>
+      <c r="G35">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+        <v>10.464380702140293</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>39387</v>
       </c>
@@ -3224,20 +1865,19 @@
         <f t="shared" si="1"/>
         <v>150598.00955236153</v>
       </c>
-      <c r="E36" t="e">
-        <f>VLOOKUP(B36,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F36" t="e">
+      <c r="E36">
+        <v>42658630</v>
+      </c>
+      <c r="F36">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G36" t="e">
+        <v>35303.058150803605</v>
+      </c>
+      <c r="G36">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+        <v>10.471724872336193</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>39417</v>
       </c>
@@ -3252,20 +1892,19 @@
         <f t="shared" si="1"/>
         <v>149788.73773690205</v>
       </c>
-      <c r="E37" t="e">
-        <f>VLOOKUP(B37,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F37" t="e">
+      <c r="E37">
+        <v>42658630</v>
+      </c>
+      <c r="F37">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G37" t="e">
+        <v>35113.349335621431</v>
+      </c>
+      <c r="G37">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+        <v>10.466336660101693</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>39448</v>
       </c>
@@ -3280,23 +1919,22 @@
         <f t="shared" si="1"/>
         <v>151187.57379320308</v>
       </c>
-      <c r="E38" t="e">
-        <f>VLOOKUP(B38,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F38" t="e">
+      <c r="E38">
+        <v>43134017</v>
+      </c>
+      <c r="F38">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G38" t="e">
+        <v>35050.659388668362</v>
+      </c>
+      <c r="G38">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.464549705086586</v>
       </c>
       <c r="H38">
         <v>10.825867333967221</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>39479</v>
       </c>
@@ -3311,23 +1949,22 @@
         <f t="shared" si="1"/>
         <v>151354.87672156346</v>
       </c>
-      <c r="E39" t="e">
-        <f>VLOOKUP(B39,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F39" t="e">
+      <c r="E39">
+        <v>43134017</v>
+      </c>
+      <c r="F39">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G39" t="e">
+        <v>35089.446160686457</v>
+      </c>
+      <c r="G39">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.465655685058186</v>
       </c>
       <c r="H39">
         <v>10.821969201776701</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>39508</v>
       </c>
@@ -3342,23 +1979,22 @@
         <f t="shared" si="1"/>
         <v>149251.31309052324</v>
       </c>
-      <c r="E40" t="e">
-        <f>VLOOKUP(B40,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F40" t="e">
+      <c r="E40">
+        <v>43134017</v>
+      </c>
+      <c r="F40">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G40" t="e">
+        <v>34601.7652588497</v>
+      </c>
+      <c r="G40">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.451659978786287</v>
       </c>
       <c r="H40">
         <v>10.820108597168071</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>39539</v>
       </c>
@@ -3373,23 +2009,22 @@
         <f t="shared" si="1"/>
         <v>152385.95671566014</v>
       </c>
-      <c r="E41" t="e">
-        <f>VLOOKUP(B41,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F41" t="e">
+      <c r="E41">
+        <v>43134017</v>
+      </c>
+      <c r="F41">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G41" t="e">
+        <v>35328.48719275558</v>
+      </c>
+      <c r="G41">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.472444920097486</v>
       </c>
       <c r="H41">
         <v>10.829742946313367</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>39569</v>
       </c>
@@ -3404,23 +2039,22 @@
         <f t="shared" si="1"/>
         <v>151056.86889922444</v>
       </c>
-      <c r="E42" t="e">
-        <f>VLOOKUP(B42,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F42" t="e">
+      <c r="E42">
+        <v>43134017</v>
+      </c>
+      <c r="F42">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G42" t="e">
+        <v>35020.357343306197</v>
+      </c>
+      <c r="G42">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.463684809765686</v>
       </c>
       <c r="H42">
         <v>10.823827156518615</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>39600</v>
       </c>
@@ -3435,23 +2069,22 @@
         <f t="shared" si="1"/>
         <v>151634.28173217046</v>
       </c>
-      <c r="E43" t="e">
-        <f>VLOOKUP(B43,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F43" t="e">
+      <c r="E43">
+        <v>43134017</v>
+      </c>
+      <c r="F43">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G43" t="e">
+        <v>35154.222184354046</v>
+      </c>
+      <c r="G43">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.467500009067885</v>
       </c>
       <c r="H43">
         <v>10.836154142790827</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>39630</v>
       </c>
@@ -3466,23 +2099,22 @@
         <f t="shared" si="1"/>
         <v>153396.8226447636</v>
       </c>
-      <c r="E44" t="e">
-        <f>VLOOKUP(B44,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F44" t="e">
+      <c r="E44">
+        <v>43134017</v>
+      </c>
+      <c r="F44">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G44" t="e">
+        <v>35562.841885272035</v>
+      </c>
+      <c r="G44">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.479056604468086</v>
       </c>
       <c r="H44">
         <v>10.839897642348799</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>39661</v>
       </c>
@@ -3497,23 +2129,22 @@
         <f t="shared" si="1"/>
         <v>152423.34581516727</v>
       </c>
-      <c r="E45" t="e">
-        <f>VLOOKUP(B45,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F45" t="e">
+      <c r="E45">
+        <v>43134017</v>
+      </c>
+      <c r="F45">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G45" t="e">
+        <v>35337.155316456447</v>
+      </c>
+      <c r="G45">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.472690247909886</v>
       </c>
       <c r="H45">
         <v>10.8444109041974</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>39692</v>
       </c>
@@ -3528,23 +2159,22 @@
         <f t="shared" si="1"/>
         <v>153185.01174033521</v>
       </c>
-      <c r="E46" t="e">
-        <f>VLOOKUP(B46,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F46" t="e">
+      <c r="E46">
+        <v>43134017</v>
+      </c>
+      <c r="F46">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G46" t="e">
+        <v>35513.736580651697</v>
+      </c>
+      <c r="G46">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.477674846553086</v>
       </c>
       <c r="H46">
         <v>10.839584155187378</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>39722</v>
       </c>
@@ -3559,23 +2189,22 @@
         <f t="shared" si="1"/>
         <v>152312.39922577876</v>
       </c>
-      <c r="E47" t="e">
-        <f>VLOOKUP(B47,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F47" t="e">
+      <c r="E47">
+        <v>43134017</v>
+      </c>
+      <c r="F47">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G47" t="e">
+        <v>35311.433949167949</v>
+      </c>
+      <c r="G47">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.471962098382987</v>
       </c>
       <c r="H47">
         <v>10.830423050220965</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>39753</v>
       </c>
@@ -3590,23 +2219,22 @@
         <f t="shared" si="1"/>
         <v>148647.6370051057</v>
       </c>
-      <c r="E48" t="e">
-        <f>VLOOKUP(B48,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F48" t="e">
+      <c r="E48">
+        <v>43134017</v>
+      </c>
+      <c r="F48">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G48" t="e">
+        <v>34461.811661340449</v>
+      </c>
+      <c r="G48">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.447607081576987</v>
       </c>
       <c r="H48">
         <v>10.817040099576738</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>39783</v>
       </c>
@@ -3621,23 +2249,22 @@
         <f t="shared" si="1"/>
         <v>150339.00694683348</v>
       </c>
-      <c r="E49" t="e">
-        <f>VLOOKUP(B49,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F49" t="e">
+      <c r="E49">
+        <v>43134017</v>
+      </c>
+      <c r="F49">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G49" t="e">
+        <v>34853.931398699431</v>
+      </c>
+      <c r="G49">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.458921218971087</v>
       </c>
       <c r="H49">
         <v>10.821590977020024</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>39814</v>
       </c>
@@ -3652,23 +2279,22 @@
         <f t="shared" si="1"/>
         <v>149085.91128584408</v>
       </c>
-      <c r="E50" t="e">
-        <f>VLOOKUP(B50,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F50" t="e">
+      <c r="E50">
+        <v>43608630</v>
+      </c>
+      <c r="F50">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G50" t="e">
+        <v>34187.249470080591</v>
+      </c>
+      <c r="G50">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.439608031022841</v>
       </c>
       <c r="H50">
         <v>10.81614980515544</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>39845</v>
       </c>
@@ -3683,23 +2309,22 @@
         <f t="shared" si="1"/>
         <v>152040.99650892935</v>
       </c>
-      <c r="E51" t="e">
-        <f>VLOOKUP(B51,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F51" t="e">
+      <c r="E51">
+        <v>43608630</v>
+      </c>
+      <c r="F51">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G51" t="e">
+        <v>34864.887181488928</v>
+      </c>
+      <c r="G51">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.459235503782644</v>
       </c>
       <c r="H51">
         <v>10.833584210055569</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>39873</v>
       </c>
@@ -3714,23 +2339,22 @@
         <f t="shared" si="1"/>
         <v>151372.3914120702</v>
       </c>
-      <c r="E52" t="e">
-        <f>VLOOKUP(B52,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F52" t="e">
+      <c r="E52">
+        <v>43608630</v>
+      </c>
+      <c r="F52">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G52" t="e">
+        <v>34711.567736035322</v>
+      </c>
+      <c r="G52">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.454828274532343</v>
       </c>
       <c r="H52">
         <v>10.833640268374779</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>39904</v>
       </c>
@@ -3745,23 +2369,22 @@
         <f t="shared" si="1"/>
         <v>152702.80768057873</v>
       </c>
-      <c r="E53" t="e">
-        <f>VLOOKUP(B53,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F53" t="e">
+      <c r="E53">
+        <v>43608630</v>
+      </c>
+      <c r="F53">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G53" t="e">
+        <v>35016.648695585885</v>
+      </c>
+      <c r="G53">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.463578904389843</v>
       </c>
       <c r="H53">
         <v>10.834417255655621</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>39934</v>
       </c>
@@ -3776,23 +2399,22 @@
         <f t="shared" si="1"/>
         <v>152608.12774095353</v>
       </c>
-      <c r="E54" t="e">
-        <f>VLOOKUP(B54,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F54" t="e">
+      <c r="E54">
+        <v>43608630</v>
+      </c>
+      <c r="F54">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G54" t="e">
+        <v>34994.937410543171</v>
+      </c>
+      <c r="G54">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.462958684596343</v>
       </c>
       <c r="H54">
         <v>10.841459794326221</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>39965</v>
       </c>
@@ -3807,23 +2429,22 @@
         <f t="shared" si="1"/>
         <v>152169.35449495696</v>
       </c>
-      <c r="E55" t="e">
-        <f>VLOOKUP(B55,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F55" t="e">
+      <c r="E55">
+        <v>43608630</v>
+      </c>
+      <c r="F55">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G55" t="e">
+        <v>34894.321260483754</v>
+      </c>
+      <c r="G55">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.460079380351743</v>
       </c>
       <c r="H55">
         <v>10.834374868494265</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>39995</v>
       </c>
@@ -3838,23 +2459,22 @@
         <f t="shared" si="1"/>
         <v>155851.28588845077</v>
       </c>
-      <c r="E56" t="e">
-        <f>VLOOKUP(B56,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F56" t="e">
+      <c r="E56">
+        <v>43608630</v>
+      </c>
+      <c r="F56">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G56" t="e">
+        <v>35738.633818226066</v>
+      </c>
+      <c r="G56">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.483987562415543</v>
       </c>
       <c r="H56">
         <v>10.854577588686901</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>40026</v>
       </c>
@@ -3869,23 +2489,22 @@
         <f t="shared" si="1"/>
         <v>152158.72029554576</v>
       </c>
-      <c r="E57" t="e">
-        <f>VLOOKUP(B57,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F57" t="e">
+      <c r="E57">
+        <v>43608630</v>
+      </c>
+      <c r="F57">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G57" t="e">
+        <v>34891.882706598612</v>
+      </c>
+      <c r="G57">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.460009493934441</v>
       </c>
       <c r="H57">
         <v>10.838387105995356</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>40057</v>
       </c>
@@ -3900,23 +2519,22 @@
         <f t="shared" si="1"/>
         <v>154162.06783188338</v>
       </c>
-      <c r="E58" t="e">
-        <f>VLOOKUP(B58,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F58" t="e">
+      <c r="E58">
+        <v>43608630</v>
+      </c>
+      <c r="F58">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G58" t="e">
+        <v>35351.27515628979</v>
+      </c>
+      <c r="G58">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.473089742987842</v>
       </c>
       <c r="H58">
         <v>10.841886416758975</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>40087</v>
       </c>
@@ -3931,23 +2549,22 @@
         <f t="shared" si="1"/>
         <v>154559.36276303884</v>
       </c>
-      <c r="E59" t="e">
-        <f>VLOOKUP(B59,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F59" t="e">
+      <c r="E59">
+        <v>43608630</v>
+      </c>
+      <c r="F59">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G59" t="e">
+        <v>35442.379814050299</v>
+      </c>
+      <c r="G59">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.475663552973844</v>
       </c>
       <c r="H59">
         <v>10.844436789663195</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>40118</v>
       </c>
@@ -3962,23 +2579,22 @@
         <f t="shared" si="1"/>
         <v>154347.44252574636</v>
       </c>
-      <c r="E60" t="e">
-        <f>VLOOKUP(B60,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F60" t="e">
+      <c r="E60">
+        <v>43608630</v>
+      </c>
+      <c r="F60">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G60" t="e">
+        <v>35393.78387391357</v>
+      </c>
+      <c r="G60">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.474291486920844</v>
       </c>
       <c r="H60">
         <v>10.852347466077704</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>40148</v>
       </c>
@@ -3993,23 +2609,22 @@
         <f t="shared" si="1"/>
         <v>156840.49664889241</v>
       </c>
-      <c r="E61" t="e">
-        <f>VLOOKUP(B61,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F61" t="e">
+      <c r="E61">
+        <v>43608630</v>
+      </c>
+      <c r="F61">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G61" t="e">
+        <v>35965.472120745915</v>
+      </c>
+      <c r="G61">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.490314649443041</v>
       </c>
       <c r="H61">
         <v>10.861009980720585</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>40179</v>
       </c>
@@ -4024,23 +2639,22 @@
         <f t="shared" si="1"/>
         <v>154759.68966140645</v>
       </c>
-      <c r="E62" t="e">
-        <f>VLOOKUP(B62,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F62" t="e">
+      <c r="E62">
+        <v>44086292</v>
+      </c>
+      <c r="F62">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G62" t="e">
+        <v>35103.811783809455</v>
+      </c>
+      <c r="G62">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.466065001386969</v>
       </c>
       <c r="H62">
         <v>10.860333865131429</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>40210</v>
       </c>
@@ -4055,23 +2669,22 @@
         <f t="shared" si="1"/>
         <v>157203.69058475166</v>
       </c>
-      <c r="E63" t="e">
-        <f>VLOOKUP(B63,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F63" t="e">
+      <c r="E63">
+        <v>44086292</v>
+      </c>
+      <c r="F63">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G63" t="e">
+        <v>35658.179323575605</v>
+      </c>
+      <c r="G63">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.481733833567869</v>
       </c>
       <c r="H63">
         <v>10.868608399249467</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>40238</v>
       </c>
@@ -4086,23 +2699,22 @@
         <f t="shared" si="1"/>
         <v>158116.61996218635</v>
       </c>
-      <c r="E64" t="e">
-        <f>VLOOKUP(B64,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F64" t="e">
+      <c r="E64">
+        <v>44086292</v>
+      </c>
+      <c r="F64">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G64" t="e">
+        <v>35865.257155713247</v>
+      </c>
+      <c r="G64">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.48752433863697</v>
       </c>
       <c r="H64">
         <v>10.868566455913616</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>40269</v>
       </c>
@@ -4117,23 +2729,22 @@
         <f t="shared" si="1"/>
         <v>159257.37797013068</v>
       </c>
-      <c r="E65" t="e">
-        <f>VLOOKUP(B65,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F65" t="e">
+      <c r="E65">
+        <v>44086292</v>
+      </c>
+      <c r="F65">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G65" t="e">
+        <v>36124.012872330175</v>
+      </c>
+      <c r="G65">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.494713099707969</v>
       </c>
       <c r="H65">
         <v>10.876618527072992</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>40299</v>
       </c>
@@ -4148,23 +2759,22 @@
         <f t="shared" si="1"/>
         <v>158944.78758800786</v>
       </c>
-      <c r="E66" t="e">
-        <f>VLOOKUP(B66,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F66" t="e">
+      <c r="E66">
+        <v>44086292</v>
+      </c>
+      <c r="F66">
         <f t="shared" si="2"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G66" t="e">
+        <v>36053.108659718506</v>
+      </c>
+      <c r="G66">
         <f t="shared" si="3"/>
-        <v>#N/A</v>
+        <v>10.49274837088767</v>
       </c>
       <c r="H66">
         <v>10.877461236046104</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>40330</v>
       </c>
@@ -4179,23 +2789,22 @@
         <f t="shared" ref="D67:D130" si="5">EXP(C67)</f>
         <v>159533.00778102753</v>
       </c>
-      <c r="E67" t="e">
-        <f>VLOOKUP(B67,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F67" t="e">
-        <f t="shared" ref="F67:F130" si="6">D67*1000000000/E67</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G67" t="e">
+      <c r="E67">
+        <v>44086292</v>
+      </c>
+      <c r="F67">
+        <f t="shared" ref="F67:F130" si="6">D67*10000000/E67</f>
+        <v>36186.533397054016</v>
+      </c>
+      <c r="G67">
         <f t="shared" ref="G67:G130" si="7">LN(F67)</f>
-        <v>#N/A</v>
+        <v>10.496442322996369</v>
       </c>
       <c r="H67">
         <v>10.878114822387875</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>40360</v>
       </c>
@@ -4210,23 +2819,22 @@
         <f t="shared" si="5"/>
         <v>159731.83719001233</v>
       </c>
-      <c r="E68" t="e">
-        <f>VLOOKUP(B68,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F68" t="e">
+      <c r="E68">
+        <v>44086292</v>
+      </c>
+      <c r="F68">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G68" t="e">
+        <v>36231.633449692781</v>
+      </c>
+      <c r="G68">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.49768786842877</v>
       </c>
       <c r="H68">
         <v>10.879100072900387</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>40391</v>
       </c>
@@ -4241,23 +2849,22 @@
         <f t="shared" si="5"/>
         <v>159736.76567371108</v>
       </c>
-      <c r="E69" t="e">
-        <f>VLOOKUP(B69,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F69" t="e">
+      <c r="E69">
+        <v>44086292</v>
+      </c>
+      <c r="F69">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G69" t="e">
+        <v>36232.751367184857</v>
+      </c>
+      <c r="G69">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.497718722688969</v>
       </c>
       <c r="H69">
         <v>10.887938912177946</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>40422</v>
       </c>
@@ -4272,23 +2879,22 @@
         <f t="shared" si="5"/>
         <v>161814.15504553381</v>
       </c>
-      <c r="E70" t="e">
-        <f>VLOOKUP(B70,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F70" t="e">
+      <c r="E70">
+        <v>44086292</v>
+      </c>
+      <c r="F70">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G70" t="e">
+        <v>36703.961187194836</v>
+      </c>
+      <c r="G70">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.510639962474169</v>
       </c>
       <c r="H70">
         <v>10.893440745274395</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>40452</v>
       </c>
@@ -4303,23 +2909,22 @@
         <f t="shared" si="5"/>
         <v>162772.97459974978</v>
       </c>
-      <c r="E71" t="e">
-        <f>VLOOKUP(B71,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F71" t="e">
+      <c r="E71">
+        <v>44086292</v>
+      </c>
+      <c r="F71">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G71" t="e">
+        <v>36921.448190686977</v>
+      </c>
+      <c r="G71">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.516547912947368</v>
       </c>
       <c r="H71">
         <v>10.906388962479243</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>40483</v>
       </c>
@@ -4334,23 +2939,22 @@
         <f t="shared" si="5"/>
         <v>162731.26964869892</v>
       </c>
-      <c r="E72" t="e">
-        <f>VLOOKUP(B72,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F72" t="e">
+      <c r="E72">
+        <v>44086292</v>
+      </c>
+      <c r="F72">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G72" t="e">
+        <v>36911.988345197853</v>
+      </c>
+      <c r="G72">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.51629166466787</v>
       </c>
       <c r="H72">
         <v>10.902345496187481</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>40513</v>
       </c>
@@ -4365,23 +2969,22 @@
         <f t="shared" si="5"/>
         <v>165899.6917471643</v>
       </c>
-      <c r="E73" t="e">
-        <f>VLOOKUP(B73,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F73" t="e">
+      <c r="E73">
+        <v>44086292</v>
+      </c>
+      <c r="F73">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G73" t="e">
+        <v>37630.674801855486</v>
+      </c>
+      <c r="G73">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.53557481597667</v>
       </c>
       <c r="H73">
         <v>10.914190320847265</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>40544</v>
       </c>
@@ -4396,23 +2999,22 @@
         <f t="shared" si="5"/>
         <v>166482.28818318434</v>
       </c>
-      <c r="E74" t="e">
-        <f>VLOOKUP(B74,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F74" t="e">
+      <c r="E74">
+        <v>44553416</v>
+      </c>
+      <c r="F74">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G74" t="e">
+        <v>37366.896442504956</v>
+      </c>
+      <c r="G74">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.528540469592814</v>
       </c>
       <c r="H74">
         <v>10.924858690307637</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>40575</v>
       </c>
@@ -4427,23 +3029,22 @@
         <f t="shared" si="5"/>
         <v>166726.64952927252</v>
       </c>
-      <c r="E75" t="e">
-        <f>VLOOKUP(B75,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F75" t="e">
+      <c r="E75">
+        <v>44553416</v>
+      </c>
+      <c r="F75">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G75" t="e">
+        <v>37421.743268635677</v>
+      </c>
+      <c r="G75">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.530007185291215</v>
       </c>
       <c r="H75">
         <v>10.921351431837401</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>40603</v>
       </c>
@@ -4458,23 +3059,22 @@
         <f t="shared" si="5"/>
         <v>168467.25766586588</v>
       </c>
-      <c r="E76" t="e">
-        <f>VLOOKUP(B76,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F76" t="e">
+      <c r="E76">
+        <v>44553416</v>
+      </c>
+      <c r="F76">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G76" t="e">
+        <v>37812.422209301723</v>
+      </c>
+      <c r="G76">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.540392957496415</v>
       </c>
       <c r="H76">
         <v>10.93315772847955</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>40634</v>
       </c>
@@ -4489,23 +3089,22 @@
         <f t="shared" si="5"/>
         <v>169031.32396022478</v>
       </c>
-      <c r="E77" t="e">
-        <f>VLOOKUP(B77,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F77" t="e">
+      <c r="E77">
+        <v>44553416</v>
+      </c>
+      <c r="F77">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G77" t="e">
+        <v>37939.02670902379</v>
+      </c>
+      <c r="G77">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.543735589734114</v>
       </c>
       <c r="H77">
         <v>10.937749639142789</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>40664</v>
       </c>
@@ -4520,23 +3119,22 @@
         <f t="shared" si="5"/>
         <v>169876.18194835199</v>
       </c>
-      <c r="E78" t="e">
-        <f>VLOOKUP(B78,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F78" t="e">
+      <c r="E78">
+        <v>44553416</v>
+      </c>
+      <c r="F78">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G78" t="e">
+        <v>38128.654814785019</v>
+      </c>
+      <c r="G78">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.548721373309414</v>
       </c>
       <c r="H78">
         <v>10.944651145596785</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>40695</v>
       </c>
@@ -4551,23 +3149,22 @@
         <f t="shared" si="5"/>
         <v>170526.7159483649</v>
       </c>
-      <c r="E79" t="e">
-        <f>VLOOKUP(B79,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F79" t="e">
+      <c r="E79">
+        <v>44553416</v>
+      </c>
+      <c r="F79">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G79" t="e">
+        <v>38274.666963441116</v>
+      </c>
+      <c r="G79">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.552543519336915</v>
       </c>
       <c r="H79">
         <v>10.951195878047892</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>40725</v>
       </c>
@@ -4582,23 +3179,22 @@
         <f t="shared" si="5"/>
         <v>171427.84209766888</v>
       </c>
-      <c r="E80" t="e">
-        <f>VLOOKUP(B80,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F80" t="e">
+      <c r="E80">
+        <v>44553416</v>
+      </c>
+      <c r="F80">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G80" t="e">
+        <v>38476.924440017996</v>
+      </c>
+      <c r="G80">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.557813975390415</v>
       </c>
       <c r="H80">
         <v>10.959292057535347</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>40756</v>
       </c>
@@ -4613,23 +3209,22 @@
         <f t="shared" si="5"/>
         <v>174720.89520892373</v>
       </c>
-      <c r="E81" t="e">
-        <f>VLOOKUP(B81,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F81" t="e">
+      <c r="E81">
+        <v>44553416</v>
+      </c>
+      <c r="F81">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G81" t="e">
+        <v>39216.049159715098</v>
+      </c>
+      <c r="G81">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.576841359329814</v>
       </c>
       <c r="H81">
         <v>10.967610004566355</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>40787</v>
       </c>
@@ -4644,23 +3239,22 @@
         <f t="shared" si="5"/>
         <v>173632.99795537451</v>
       </c>
-      <c r="E82" t="e">
-        <f>VLOOKUP(B82,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F82" t="e">
+      <c r="E82">
+        <v>44553416</v>
+      </c>
+      <c r="F82">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G82" t="e">
+        <v>38971.870968406671</v>
+      </c>
+      <c r="G82">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.570595407660317</v>
       </c>
       <c r="H82">
         <v>10.962387303142336</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>40817</v>
       </c>
@@ -4675,23 +3269,22 @@
         <f t="shared" si="5"/>
         <v>173872.38212906275</v>
       </c>
-      <c r="E83" t="e">
-        <f>VLOOKUP(B83,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F83" t="e">
+      <c r="E83">
+        <v>44553416</v>
+      </c>
+      <c r="F83">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G83" t="e">
+        <v>39025.600669780906</v>
+      </c>
+      <c r="G83">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.571973137187815</v>
       </c>
       <c r="H83">
         <v>10.972701800164629</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>40848</v>
       </c>
@@ -4706,23 +3299,22 @@
         <f t="shared" si="5"/>
         <v>174453.16522730378</v>
       </c>
-      <c r="E84" t="e">
-        <f>VLOOKUP(B84,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F84" t="e">
+      <c r="E84">
+        <v>44553416</v>
+      </c>
+      <c r="F84">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G84" t="e">
+        <v>39155.957250798412</v>
+      </c>
+      <c r="G84">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.575307854614417</v>
       </c>
       <c r="H84">
         <v>10.975277589897884</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>40878</v>
       </c>
@@ -4737,23 +3329,22 @@
         <f t="shared" si="5"/>
         <v>174693.91012166665</v>
       </c>
-      <c r="E85" t="e">
-        <f>VLOOKUP(B85,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F85" t="e">
+      <c r="E85">
+        <v>44553416</v>
+      </c>
+      <c r="F85">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G85" t="e">
+        <v>39209.992365493737</v>
+      </c>
+      <c r="G85">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.576686900578215</v>
       </c>
       <c r="H85">
         <v>10.968494742083706</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>40909</v>
       </c>
@@ -4768,23 +3359,22 @@
         <f t="shared" si="5"/>
         <v>176409.3057441593</v>
       </c>
-      <c r="E86" t="e">
-        <f>VLOOKUP(B86,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F86" t="e">
+      <c r="E86">
+        <v>45001571</v>
+      </c>
+      <c r="F86">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G86" t="e">
+        <v>39200.699403174011</v>
+      </c>
+      <c r="G86">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.576449867537093</v>
       </c>
       <c r="H86">
         <v>10.979552210191965</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>40940</v>
       </c>
@@ -4799,23 +3389,22 @@
         <f t="shared" si="5"/>
         <v>177000.00096193029</v>
       </c>
-      <c r="E87" t="e">
-        <f>VLOOKUP(B87,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F87" t="e">
+      <c r="E87">
+        <v>45001571</v>
+      </c>
+      <c r="F87">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G87" t="e">
+        <v>39331.960424655015</v>
+      </c>
+      <c r="G87">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.579792709712594</v>
       </c>
       <c r="H87">
         <v>10.973910801712357</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>40969</v>
       </c>
@@ -4830,23 +3419,22 @@
         <f t="shared" si="5"/>
         <v>178400.4672420315</v>
       </c>
-      <c r="E88" t="e">
-        <f>VLOOKUP(B88,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F88" t="e">
+      <c r="E88">
+        <v>45001571</v>
+      </c>
+      <c r="F88">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G88" t="e">
+        <v>39643.164289093707</v>
+      </c>
+      <c r="G88">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.587673810916293</v>
       </c>
       <c r="H88">
         <v>10.988345695387277</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>41000</v>
       </c>
@@ -4861,23 +3449,22 @@
         <f t="shared" si="5"/>
         <v>176854.90491992614</v>
       </c>
-      <c r="E89" t="e">
-        <f>VLOOKUP(B89,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F89" t="e">
+      <c r="E89">
+        <v>45001571</v>
+      </c>
+      <c r="F89">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G89" t="e">
+        <v>39299.717985384588</v>
+      </c>
+      <c r="G89">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.578972621887193</v>
       </c>
       <c r="H89">
         <v>10.984533862934741</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>41030</v>
       </c>
@@ -4892,23 +3479,22 @@
         <f t="shared" si="5"/>
         <v>178327.95932631815</v>
       </c>
-      <c r="E90" t="e">
-        <f>VLOOKUP(B90,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F90" t="e">
+      <c r="E90">
+        <v>45001571</v>
+      </c>
+      <c r="F90">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G90" t="e">
+        <v>39627.051981433746</v>
+      </c>
+      <c r="G90">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.587267294859194</v>
       </c>
       <c r="H90">
         <v>10.989823326276612</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>41061</v>
       </c>
@@ -4923,23 +3509,22 @@
         <f t="shared" si="5"/>
         <v>178447.93709055666</v>
       </c>
-      <c r="E91" t="e">
-        <f>VLOOKUP(B91,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F91" t="e">
+      <c r="E91">
+        <v>45001571</v>
+      </c>
+      <c r="F91">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G91" t="e">
+        <v>39653.712776062122</v>
+      </c>
+      <c r="G91">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.587939861419693</v>
       </c>
       <c r="H91">
         <v>10.997517205452656</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>41091</v>
       </c>
@@ -4954,23 +3539,22 @@
         <f t="shared" si="5"/>
         <v>177460.30159391143</v>
       </c>
-      <c r="E92" t="e">
-        <f>VLOOKUP(B92,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F92" t="e">
+      <c r="E92">
+        <v>45001571</v>
+      </c>
+      <c r="F92">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G92" t="e">
+        <v>39434.245883085154</v>
+      </c>
+      <c r="G92">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.582389902613492</v>
       </c>
       <c r="H92">
         <v>10.994454823859426</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>41122</v>
       </c>
@@ -4985,23 +3569,22 @@
         <f t="shared" si="5"/>
         <v>174957.17468647496</v>
       </c>
-      <c r="E93" t="e">
-        <f>VLOOKUP(B93,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F93" t="e">
+      <c r="E93">
+        <v>45001571</v>
+      </c>
+      <c r="F93">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G93" t="e">
+        <v>38878.014877852809</v>
+      </c>
+      <c r="G93">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.568184199602493</v>
       </c>
       <c r="H93">
         <v>10.974860948251314</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>41153</v>
       </c>
@@ -5016,23 +3599,22 @@
         <f t="shared" si="5"/>
         <v>178661.37675429237</v>
       </c>
-      <c r="E94" t="e">
-        <f>VLOOKUP(B94,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F94" t="e">
+      <c r="E94">
+        <v>45001571</v>
+      </c>
+      <c r="F94">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G94" t="e">
+        <v>39701.142156635462</v>
+      </c>
+      <c r="G94">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.589135235949993</v>
       </c>
       <c r="H94">
         <v>10.999405773833885</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>41183</v>
       </c>
@@ -5047,23 +3629,22 @@
         <f t="shared" si="5"/>
         <v>178827.29766877022</v>
       </c>
-      <c r="E95" t="e">
-        <f>VLOOKUP(B95,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F95" t="e">
+      <c r="E95">
+        <v>45001571</v>
+      </c>
+      <c r="F95">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G95" t="e">
+        <v>39738.012183790255</v>
+      </c>
+      <c r="G95">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.590063494315993</v>
       </c>
       <c r="H95">
         <v>10.993417009428375</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>41214</v>
       </c>
@@ -5078,23 +3659,22 @@
         <f t="shared" si="5"/>
         <v>179920.47182872857</v>
       </c>
-      <c r="E96" t="e">
-        <f>VLOOKUP(B96,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F96" t="e">
+      <c r="E96">
+        <v>45001571</v>
+      </c>
+      <c r="F96">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G96" t="e">
+        <v>39980.931294316048</v>
+      </c>
+      <c r="G96">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.596157901787993</v>
       </c>
       <c r="H96">
         <v>11.002252604382271</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>41244</v>
       </c>
@@ -5109,23 +3689,22 @@
         <f t="shared" si="5"/>
         <v>179010.25601236604</v>
       </c>
-      <c r="E97" t="e">
-        <f>VLOOKUP(B97,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F97" t="e">
+      <c r="E97">
+        <v>45001571</v>
+      </c>
+      <c r="F97">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G97" t="e">
+        <v>39778.668174132421</v>
+      </c>
+      <c r="G97">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.591086072061993</v>
       </c>
       <c r="H97">
         <v>11.002623382476669</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>41275</v>
       </c>
@@ -5140,23 +3719,22 @@
         <f t="shared" si="5"/>
         <v>182482.89376403837</v>
       </c>
-      <c r="E98" t="e">
-        <f>VLOOKUP(B98,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F98" t="e">
+      <c r="E98">
+        <v>45434942</v>
+      </c>
+      <c r="F98">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G98" t="e">
+        <v>40163.558206817645</v>
+      </c>
+      <c r="G98">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.600715351208166</v>
       </c>
       <c r="H98">
         <v>11.019389859393355</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>41306</v>
       </c>
@@ -5171,23 +3749,22 @@
         <f t="shared" si="5"/>
         <v>181022.51962800729</v>
       </c>
-      <c r="E99" t="e">
-        <f>VLOOKUP(B99,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F99" t="e">
+      <c r="E99">
+        <v>45434942</v>
+      </c>
+      <c r="F99">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G99" t="e">
+        <v>39842.137275757341</v>
+      </c>
+      <c r="G99">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.592680356739466</v>
       </c>
       <c r="H99">
         <v>11.01166521977866</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>41334</v>
       </c>
@@ -5202,23 +3779,22 @@
         <f t="shared" si="5"/>
         <v>180914.4153125835</v>
       </c>
-      <c r="E100" t="e">
-        <f>VLOOKUP(B100,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F100" t="e">
+      <c r="E100">
+        <v>45434942</v>
+      </c>
+      <c r="F100">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G100" t="e">
+        <v>39818.344064923316</v>
+      </c>
+      <c r="G100">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.592082991241766</v>
       </c>
       <c r="H100">
         <v>11.016248958229484</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>41365</v>
       </c>
@@ -5233,23 +3809,22 @@
         <f t="shared" si="5"/>
         <v>186688.4121665635</v>
       </c>
-      <c r="E101" t="e">
-        <f>VLOOKUP(B101,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F101" t="e">
+      <c r="E101">
+        <v>45434942</v>
+      </c>
+      <c r="F101">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G101" t="e">
+        <v>41089.171450150308</v>
+      </c>
+      <c r="G101">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.623499897404265</v>
       </c>
       <c r="H101">
         <v>11.031004997206857</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>41395</v>
       </c>
@@ -5264,23 +3839,22 @@
         <f t="shared" si="5"/>
         <v>188739.7000656481</v>
       </c>
-      <c r="E102" t="e">
-        <f>VLOOKUP(B102,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F102" t="e">
+      <c r="E102">
+        <v>45434942</v>
+      </c>
+      <c r="F102">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G102" t="e">
+        <v>41540.649499596169</v>
+      </c>
+      <c r="G102">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.634427732830165</v>
       </c>
       <c r="H102">
         <v>11.040203066299023</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>41426</v>
       </c>
@@ -5295,23 +3869,22 @@
         <f t="shared" si="5"/>
         <v>187306.71934438427</v>
       </c>
-      <c r="E103" t="e">
-        <f>VLOOKUP(B103,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F103" t="e">
+      <c r="E103">
+        <v>45434942</v>
+      </c>
+      <c r="F103">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G103" t="e">
+        <v>41225.257720012996</v>
+      </c>
+      <c r="G103">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.626806398954965</v>
       </c>
       <c r="H103">
         <v>11.045268674075816</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>41456</v>
       </c>
@@ -5326,23 +3899,22 @@
         <f t="shared" si="5"/>
         <v>189697.71800531997</v>
       </c>
-      <c r="E104" t="e">
-        <f>VLOOKUP(B104,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F104" t="e">
+      <c r="E104">
+        <v>45434942</v>
+      </c>
+      <c r="F104">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G104" t="e">
+        <v>41751.504382974665</v>
+      </c>
+      <c r="G104">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.639490762754965</v>
       </c>
       <c r="H104">
         <v>11.05054020597824</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>41487</v>
       </c>
@@ -5357,23 +3929,22 @@
         <f t="shared" si="5"/>
         <v>185964.86179758646</v>
       </c>
-      <c r="E105" t="e">
-        <f>VLOOKUP(B105,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F105" t="e">
+      <c r="E105">
+        <v>45434942</v>
+      </c>
+      <c r="F105">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G105" t="e">
+        <v>40929.921688375092</v>
+      </c>
+      <c r="G105">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.619616656178366</v>
       </c>
       <c r="H105">
         <v>11.037048989846921</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>41518</v>
       </c>
@@ -5388,23 +3959,22 @@
         <f t="shared" si="5"/>
         <v>188616.8379558622</v>
       </c>
-      <c r="E106" t="e">
-        <f>VLOOKUP(B106,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F106" t="e">
+      <c r="E106">
+        <v>45434942</v>
+      </c>
+      <c r="F106">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G106" t="e">
+        <v>41513.608173168177</v>
+      </c>
+      <c r="G106">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.633776560255965</v>
       </c>
       <c r="H106">
         <v>11.052330062593208</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>41548</v>
       </c>
@@ -5419,23 +3989,22 @@
         <f t="shared" si="5"/>
         <v>189756.05970453037</v>
       </c>
-      <c r="E107" t="e">
-        <f>VLOOKUP(B107,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F107" t="e">
+      <c r="E107">
+        <v>45434942</v>
+      </c>
+      <c r="F107">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G107" t="e">
+        <v>41764.345094691736</v>
+      </c>
+      <c r="G107">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.639798266346165</v>
       </c>
       <c r="H107">
         <v>11.051950768359012</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>41579</v>
       </c>
@@ -5450,23 +4019,22 @@
         <f t="shared" si="5"/>
         <v>190671.50450688761</v>
       </c>
-      <c r="E108" t="e">
-        <f>VLOOKUP(B108,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F108" t="e">
+      <c r="E108">
+        <v>45434942</v>
+      </c>
+      <c r="F108">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G108" t="e">
+        <v>41965.82984674826</v>
+      </c>
+      <c r="G108">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.644610991056267</v>
       </c>
       <c r="H108">
         <v>11.060414666299168</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>41609</v>
       </c>
@@ -5481,23 +4049,22 @@
         <f t="shared" si="5"/>
         <v>191991.74885837178</v>
       </c>
-      <c r="E109" t="e">
-        <f>VLOOKUP(B109,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F109" t="e">
+      <c r="E109">
+        <v>45434942</v>
+      </c>
+      <c r="F109">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G109" t="e">
+        <v>42256.408923856834</v>
+      </c>
+      <c r="G109">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.651511311786965</v>
       </c>
       <c r="H109">
         <v>11.064316661288125</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>41640</v>
       </c>
@@ -5512,23 +4079,22 @@
         <f t="shared" si="5"/>
         <v>192308.96294948776</v>
       </c>
-      <c r="E110" t="e">
-        <f>VLOOKUP(B110,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F110" t="e">
+      <c r="E110">
+        <v>45866010</v>
+      </c>
+      <c r="F110">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G110" t="e">
+        <v>41928.426507884113</v>
+      </c>
+      <c r="G110">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.643719312818265</v>
       </c>
       <c r="H110">
         <v>11.063337771525445</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>41671</v>
       </c>
@@ -5543,23 +4109,22 @@
         <f t="shared" si="5"/>
         <v>195201.67537595154</v>
       </c>
-      <c r="E111" t="e">
-        <f>VLOOKUP(B111,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F111" t="e">
+      <c r="E111">
+        <v>45866010</v>
+      </c>
+      <c r="F111">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G111" t="e">
+        <v>42559.114118701742</v>
+      </c>
+      <c r="G111">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.658649308918765</v>
       </c>
       <c r="H111">
         <v>11.07783545993599</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>41699</v>
       </c>
@@ -5574,23 +4139,22 @@
         <f t="shared" si="5"/>
         <v>193159.5469490095</v>
       </c>
-      <c r="E112" t="e">
-        <f>VLOOKUP(B112,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F112" t="e">
+      <c r="E112">
+        <v>45866010</v>
+      </c>
+      <c r="F112">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G112" t="e">
+        <v>42113.876255861258</v>
+      </c>
+      <c r="G112">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.648132567640564</v>
       </c>
       <c r="H112">
         <v>11.074631423616927</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>41730</v>
       </c>
@@ -5605,23 +4169,22 @@
         <f t="shared" si="5"/>
         <v>194441.55680205181</v>
       </c>
-      <c r="E113" t="e">
-        <f>VLOOKUP(B113,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F113" t="e">
+      <c r="E113">
+        <v>45866010</v>
+      </c>
+      <c r="F113">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G113" t="e">
+        <v>42393.388219740897</v>
+      </c>
+      <c r="G113">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.654747690846763</v>
       </c>
       <c r="H113">
         <v>11.075323820440696</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>41760</v>
       </c>
@@ -5636,23 +4199,22 @@
         <f t="shared" si="5"/>
         <v>194284.79733567612</v>
       </c>
-      <c r="E114" t="e">
-        <f>VLOOKUP(B114,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F114" t="e">
+      <c r="E114">
+        <v>45866010</v>
+      </c>
+      <c r="F114">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G114" t="e">
+        <v>42359.210521184672</v>
+      </c>
+      <c r="G114">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.653941162175864</v>
       </c>
       <c r="H114">
         <v>11.077151113506034</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>41791</v>
       </c>
@@ -5667,23 +4229,22 @@
         <f t="shared" si="5"/>
         <v>193382.41324110248</v>
       </c>
-      <c r="E115" t="e">
-        <f>VLOOKUP(B115,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F115" t="e">
+      <c r="E115">
+        <v>45866010</v>
+      </c>
+      <c r="F115">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G115" t="e">
+        <v>42162.466986141255</v>
+      </c>
+      <c r="G115">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.649285696354864</v>
       </c>
       <c r="H115">
         <v>11.084533792399172</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>41821</v>
       </c>
@@ -5698,23 +4259,22 @@
         <f t="shared" si="5"/>
         <v>195713.92583698969</v>
       </c>
-      <c r="E116" t="e">
-        <f>VLOOKUP(B116,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F116" t="e">
+      <c r="E116">
+        <v>45866010</v>
+      </c>
+      <c r="F116">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G116" t="e">
+        <v>42670.798230975335</v>
+      </c>
+      <c r="G116">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.661270083084064</v>
       </c>
       <c r="H116">
         <v>11.079152552671365</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>41852</v>
       </c>
@@ -5729,23 +4289,22 @@
         <f t="shared" si="5"/>
         <v>194388.50772154529</v>
       </c>
-      <c r="E117" t="e">
-        <f>VLOOKUP(B117,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F117" t="e">
+      <c r="E117">
+        <v>45866010</v>
+      </c>
+      <c r="F117">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G117" t="e">
+        <v>42381.822120900702</v>
+      </c>
+      <c r="G117">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.654474825728164</v>
       </c>
       <c r="H117">
         <v>11.088302441378708</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>41883</v>
       </c>
@@ -5760,23 +4319,22 @@
         <f t="shared" si="5"/>
         <v>197906.98715082908</v>
       </c>
-      <c r="E118" t="e">
-        <f>VLOOKUP(B118,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F118" t="e">
+      <c r="E118">
+        <v>45866010</v>
+      </c>
+      <c r="F118">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G118" t="e">
+        <v>43148.943444356526</v>
+      </c>
+      <c r="G118">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.672413210565365</v>
       </c>
       <c r="H118">
         <v>11.094596029882236</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>41913</v>
       </c>
@@ -5791,23 +4349,22 @@
         <f t="shared" si="5"/>
         <v>198713.48354956048</v>
       </c>
-      <c r="E119" t="e">
-        <f>VLOOKUP(B119,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F119" t="e">
+      <c r="E119">
+        <v>45866010</v>
+      </c>
+      <c r="F119">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G119" t="e">
+        <v>43324.780932450951</v>
+      </c>
+      <c r="G119">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.676480058193665</v>
       </c>
       <c r="H119">
         <v>11.096499428232512</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>41944</v>
       </c>
@@ -5822,23 +4379,22 @@
         <f t="shared" si="5"/>
         <v>196332.26778107349</v>
       </c>
-      <c r="E120" t="e">
-        <f>VLOOKUP(B120,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F120" t="e">
+      <c r="E120">
+        <v>45866010</v>
+      </c>
+      <c r="F120">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G120" t="e">
+        <v>42805.613084956261</v>
+      </c>
+      <c r="G120">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.664424519815665</v>
       </c>
       <c r="H120">
         <v>11.095717053636424</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>41974</v>
       </c>
@@ -5853,23 +4409,22 @@
         <f t="shared" si="5"/>
         <v>198972.76961583801</v>
       </c>
-      <c r="E121" t="e">
-        <f>VLOOKUP(B121,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F121" t="e">
+      <c r="E121">
+        <v>45866010</v>
+      </c>
+      <c r="F121">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G121" t="e">
+        <v>43381.312134157299</v>
+      </c>
+      <c r="G121">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.677784031368263</v>
       </c>
       <c r="H121">
         <v>11.102321825985925</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>42005</v>
       </c>
@@ -5884,23 +4439,22 @@
         <f t="shared" si="5"/>
         <v>198772.56687124301</v>
       </c>
-      <c r="E122" t="e">
-        <f>VLOOKUP(B122,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F122" t="e">
+      <c r="E122">
+        <v>46313898</v>
+      </c>
+      <c r="F122">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G122" t="e">
+        <v>42918.556946176934</v>
+      </c>
+      <c r="G122">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.667059574235717</v>
       </c>
       <c r="H122">
         <v>11.105052379495454</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>42036</v>
       </c>
@@ -5915,23 +4469,22 @@
         <f t="shared" si="5"/>
         <v>199862.19119601246</v>
       </c>
-      <c r="E123" t="e">
-        <f>VLOOKUP(B123,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F123" t="e">
+      <c r="E123">
+        <v>46313898</v>
+      </c>
+      <c r="F123">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G123" t="e">
+        <v>43153.826351652038</v>
+      </c>
+      <c r="G123">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.672526368168818</v>
       </c>
       <c r="H123">
         <v>11.107782920554685</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>42064</v>
       </c>
@@ -5946,23 +4499,22 @@
         <f t="shared" si="5"/>
         <v>198891.37410695892</v>
       </c>
-      <c r="E124" t="e">
-        <f>VLOOKUP(B124,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F124" t="e">
+      <c r="E124">
+        <v>46313898</v>
+      </c>
+      <c r="F124">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G124" t="e">
+        <v>42944.209556051384</v>
+      </c>
+      <c r="G124">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.667657100071017</v>
       </c>
       <c r="H124">
         <v>11.103408467828537</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>42095</v>
       </c>
@@ -5977,23 +4529,22 @@
         <f t="shared" si="5"/>
         <v>201078.28576606076</v>
       </c>
-      <c r="E125" t="e">
-        <f>VLOOKUP(B125,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F125" t="e">
+      <c r="E125">
+        <v>46313898</v>
+      </c>
+      <c r="F125">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G125" t="e">
+        <v>43416.402948000788</v>
+      </c>
+      <c r="G125">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.678592596794717</v>
       </c>
       <c r="H125">
         <v>11.109796792084504</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>42125</v>
       </c>
@@ -6008,23 +4559,22 @@
         <f t="shared" si="5"/>
         <v>200755.02435118295</v>
       </c>
-      <c r="E126" t="e">
-        <f>VLOOKUP(B126,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F126" t="e">
+      <c r="E126">
+        <v>46313898</v>
+      </c>
+      <c r="F126">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G126" t="e">
+        <v>43346.605019336297</v>
+      </c>
+      <c r="G126">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.676983663555617</v>
       </c>
       <c r="H126">
         <v>11.110735578519938</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>42156</v>
       </c>
@@ -6039,23 +4589,22 @@
         <f t="shared" si="5"/>
         <v>200312.57649326356</v>
       </c>
-      <c r="E127" t="e">
-        <f>VLOOKUP(B127,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F127" t="e">
+      <c r="E127">
+        <v>46313898</v>
+      </c>
+      <c r="F127">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G127" t="e">
+        <v>43251.072603144647</v>
+      </c>
+      <c r="G127">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.674777312125217</v>
       </c>
       <c r="H127">
         <v>11.108600657101643</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>42186</v>
       </c>
@@ -6070,23 +4619,22 @@
         <f t="shared" si="5"/>
         <v>203929.0948780989</v>
       </c>
-      <c r="E128" t="e">
-        <f>VLOOKUP(B128,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F128" t="e">
+      <c r="E128">
+        <v>46313898</v>
+      </c>
+      <c r="F128">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G128" t="e">
+        <v>44031.943689580803</v>
+      </c>
+      <c r="G128">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.692670642440017</v>
       </c>
       <c r="H128">
         <v>11.12152694385682</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>42217</v>
       </c>
@@ -6101,23 +4649,22 @@
         <f t="shared" si="5"/>
         <v>200986.87962106819</v>
       </c>
-      <c r="E129" t="e">
-        <f>VLOOKUP(B129,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F129" t="e">
+      <c r="E129">
+        <v>46313898</v>
+      </c>
+      <c r="F129">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G129" t="e">
+        <v>43396.666724331473</v>
+      </c>
+      <c r="G129">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.678137913552117</v>
       </c>
       <c r="H129">
         <v>11.122736849857557</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>42248</v>
       </c>
@@ -6132,23 +4679,22 @@
         <f t="shared" si="5"/>
         <v>203253.11278027776</v>
       </c>
-      <c r="E130" t="e">
-        <f>VLOOKUP(B130,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F130" t="e">
+      <c r="E130">
+        <v>46313898</v>
+      </c>
+      <c r="F130">
         <f t="shared" si="6"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G130" t="e">
+        <v>43885.987048699237</v>
+      </c>
+      <c r="G130">
         <f t="shared" si="7"/>
-        <v>#N/A</v>
+        <v>10.689350346483417</v>
       </c>
       <c r="H130">
         <v>11.122044224868148</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>42278</v>
       </c>
@@ -6163,23 +4709,22 @@
         <f t="shared" ref="D131:D194" si="9">EXP(C131)</f>
         <v>203271.06886403571</v>
       </c>
-      <c r="E131" t="e">
-        <f>VLOOKUP(B131,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F131" t="e">
-        <f t="shared" ref="F131:F194" si="10">D131*1000000000/E131</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G131" t="e">
+      <c r="E131">
+        <v>46313898</v>
+      </c>
+      <c r="F131">
+        <f t="shared" ref="F131:F194" si="10">D131*10000000/E131</f>
+        <v>43889.864088752736</v>
+      </c>
+      <c r="G131">
         <f t="shared" ref="G131:G194" si="11">LN(F131)</f>
-        <v>#N/A</v>
+        <v>10.689438686043918</v>
       </c>
       <c r="H131">
         <v>11.119438933366174</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>42309</v>
       </c>
@@ -6194,23 +4739,22 @@
         <f t="shared" si="9"/>
         <v>200838.00505973253</v>
       </c>
-      <c r="E132" t="e">
-        <f>VLOOKUP(B132,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F132" t="e">
+      <c r="E132">
+        <v>46313898</v>
+      </c>
+      <c r="F132">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G132" t="e">
+        <v>43364.52204038894</v>
+      </c>
+      <c r="G132">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
+        <v>10.677396921275017</v>
       </c>
       <c r="H132">
         <v>11.11436590589374</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>42339</v>
       </c>
@@ -6225,23 +4769,22 @@
         <f t="shared" si="9"/>
         <v>202147.42784544855</v>
       </c>
-      <c r="E133" t="e">
-        <f>VLOOKUP(B133,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F133" t="e">
+      <c r="E133">
+        <v>46313898</v>
+      </c>
+      <c r="F133">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G133" t="e">
+        <v>43647.24986988755</v>
+      </c>
+      <c r="G133">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
+        <v>10.683895555156617</v>
       </c>
       <c r="H133">
         <v>11.113954127832017</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>42370</v>
       </c>
@@ -6256,23 +4799,22 @@
         <f t="shared" si="9"/>
         <v>202375.77753724545</v>
       </c>
-      <c r="E134" t="e">
-        <f>VLOOKUP(B134,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F134" t="e">
+      <c r="E134">
+        <v>46830116</v>
+      </c>
+      <c r="F134">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G134" t="e">
+        <v>43214.878548933222</v>
+      </c>
+      <c r="G134">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
+        <v>10.673940125791333</v>
       </c>
       <c r="H134">
         <v>11.122558951759261</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>42401</v>
       </c>
@@ -6287,23 +4829,22 @@
         <f t="shared" si="9"/>
         <v>205838.00573606091</v>
       </c>
-      <c r="E135" t="e">
-        <f>VLOOKUP(B135,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F135" t="e">
+      <c r="E135">
+        <v>46830116</v>
+      </c>
+      <c r="F135">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G135" t="e">
+        <v>43954.19514571796</v>
+      </c>
+      <c r="G135">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
+        <v>10.690903351247833</v>
       </c>
       <c r="H135">
         <v>11.126803667748604</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>42430</v>
       </c>
@@ -6318,23 +4859,22 @@
         <f t="shared" si="9"/>
         <v>204284.61835588186</v>
       </c>
-      <c r="E136" t="e">
-        <f>VLOOKUP(B136,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F136" t="e">
+      <c r="E136">
+        <v>46830116</v>
+      </c>
+      <c r="F136">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G136" t="e">
+        <v>43622.488220161969</v>
+      </c>
+      <c r="G136">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
+        <v>10.683328081231933</v>
       </c>
       <c r="H136">
         <v>11.128483078893526</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>42461</v>
       </c>
@@ -6349,23 +4889,22 @@
         <f t="shared" si="9"/>
         <v>204298.7159475197</v>
       </c>
-      <c r="E137" t="e">
-        <f>VLOOKUP(B137,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F137" t="e">
+      <c r="E137">
+        <v>46830116</v>
+      </c>
+      <c r="F137">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G137" t="e">
+        <v>43625.498588882358</v>
+      </c>
+      <c r="G137">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
+        <v>10.683397088410933</v>
       </c>
       <c r="H137">
         <v>11.12326766424288</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>42491</v>
       </c>
@@ -6380,23 +4919,22 @@
         <f t="shared" si="9"/>
         <v>205292.73304479331</v>
       </c>
-      <c r="E138" t="e">
-        <f>VLOOKUP(B138,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F138" t="e">
+      <c r="E138">
+        <v>46830116</v>
+      </c>
+      <c r="F138">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G138" t="e">
+        <v>43837.758814177039</v>
+      </c>
+      <c r="G138">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
+        <v>10.688250798375734</v>
       </c>
       <c r="H138">
         <v>11.133602366006153</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>42522</v>
       </c>
@@ -6411,23 +4949,22 @@
         <f t="shared" si="9"/>
         <v>205333.73473572228</v>
       </c>
-      <c r="E139" t="e">
-        <f>VLOOKUP(B139,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F139" t="e">
+      <c r="E139">
+        <v>46830116</v>
+      </c>
+      <c r="F139">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G139" t="e">
+        <v>43846.514225102983</v>
+      </c>
+      <c r="G139">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
+        <v>10.688450501484434</v>
       </c>
       <c r="H139">
         <v>11.136869480529329</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>42552</v>
       </c>
@@ -6442,23 +4979,22 @@
         <f t="shared" si="9"/>
         <v>200634.77454812292</v>
       </c>
-      <c r="E140" t="e">
-        <f>VLOOKUP(B140,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F140" t="e">
+      <c r="E140">
+        <v>46830116</v>
+      </c>
+      <c r="F140">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G140" t="e">
+        <v>42843.108598774968</v>
+      </c>
+      <c r="G140">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
+        <v>10.665300084925732</v>
       </c>
       <c r="H140">
         <v>11.117038566943004</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>42583</v>
       </c>
@@ -6473,23 +5009,22 @@
         <f t="shared" si="9"/>
         <v>207723.66115468749</v>
       </c>
-      <c r="E141" t="e">
-        <f>VLOOKUP(B141,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F141" t="e">
+      <c r="E141">
+        <v>46830116</v>
+      </c>
+      <c r="F141">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G141" t="e">
+        <v>44356.853857608956</v>
+      </c>
+      <c r="G141">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
+        <v>10.700022515991733</v>
       </c>
       <c r="H141">
         <v>11.146208835066556</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>42614</v>
       </c>
@@ -6504,23 +5039,22 @@
         <f t="shared" si="9"/>
         <v>208288.42870390284</v>
       </c>
-      <c r="E142" t="e">
-        <f>VLOOKUP(B142,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F142" t="e">
+      <c r="E142">
+        <v>46830116</v>
+      </c>
+      <c r="F142">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G142" t="e">
+        <v>44477.45307825051</v>
+      </c>
+      <c r="G142">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
+        <v>10.702737667353633</v>
       </c>
       <c r="H142">
         <v>11.14737872559831</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>42644</v>
       </c>
@@ -6535,23 +5069,22 @@
         <f t="shared" si="9"/>
         <v>205542.99904128932</v>
       </c>
-      <c r="E143" t="e">
-        <f>VLOOKUP(B143,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F143" t="e">
+      <c r="E143">
+        <v>46830116</v>
+      </c>
+      <c r="F143">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G143" t="e">
+        <v>43891.200064780816</v>
+      </c>
+      <c r="G143">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
+        <v>10.689469124864432</v>
       </c>
       <c r="H143">
         <v>11.140953225789751</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>42675</v>
       </c>
@@ -6566,23 +5099,22 @@
         <f t="shared" si="9"/>
         <v>206692.44170141383</v>
       </c>
-      <c r="E144" t="e">
-        <f>VLOOKUP(B144,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F144" t="e">
+      <c r="E144">
+        <v>46830116</v>
+      </c>
+      <c r="F144">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G144" t="e">
+        <v>44136.649523015025</v>
+      </c>
+      <c r="G144">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
+        <v>10.695045771243633</v>
       </c>
       <c r="H144">
         <v>11.141937516978262</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>42705</v>
       </c>
@@ -6597,23 +5129,22 @@
         <f t="shared" si="9"/>
         <v>208275.83071959246</v>
       </c>
-      <c r="E145" t="e">
-        <f>VLOOKUP(B145,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F145" t="e">
+      <c r="E145">
+        <v>46830116</v>
+      </c>
+      <c r="F145">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G145" t="e">
+        <v>44474.762932381476</v>
+      </c>
+      <c r="G145">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
+        <v>10.702677182163033</v>
       </c>
       <c r="H145">
         <v>11.141941042970751</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>42736</v>
       </c>
@@ -6628,23 +5159,22 @@
         <f t="shared" si="9"/>
         <v>205810.14343099305</v>
       </c>
-      <c r="E146" t="e">
-        <f>VLOOKUP(B146,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F146" t="e">
+      <c r="E146">
+        <v>47419200</v>
+      </c>
+      <c r="F146">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G146" t="e">
+        <v>43402.280812622957</v>
+      </c>
+      <c r="G146">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
+        <v>10.678267271993864</v>
       </c>
       <c r="H146">
         <v>11.138104266683857</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>42767</v>
       </c>
@@ -6659,23 +5189,22 @@
         <f t="shared" si="9"/>
         <v>207828.07292208954</v>
       </c>
-      <c r="E147" t="e">
-        <f>VLOOKUP(B147,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F147" t="e">
+      <c r="E147">
+        <v>47419200</v>
+      </c>
+      <c r="F147">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G147" t="e">
+        <v>43827.831958803516</v>
+      </c>
+      <c r="G147">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
+        <v>10.688024327411963</v>
       </c>
       <c r="H147">
         <v>11.143415298977336</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>42795</v>
       </c>
@@ -6690,23 +5219,22 @@
         <f t="shared" si="9"/>
         <v>206067.64272805204</v>
       </c>
-      <c r="E148" t="e">
-        <f>VLOOKUP(B148,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F148" t="e">
+      <c r="E148">
+        <v>47419200</v>
+      </c>
+      <c r="F148">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G148" t="e">
+        <v>43456.583562787237</v>
+      </c>
+      <c r="G148">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
+        <v>10.679517639647864</v>
       </c>
       <c r="H148">
         <v>11.135214596479107</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>42826</v>
       </c>
@@ -6721,23 +5249,22 @@
         <f t="shared" si="9"/>
         <v>205877.52732294277</v>
       </c>
-      <c r="E149" t="e">
-        <f>VLOOKUP(B149,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F149" t="e">
+      <c r="E149">
+        <v>47419200</v>
+      </c>
+      <c r="F149">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G149" t="e">
+        <v>43416.491067530194</v>
+      </c>
+      <c r="G149">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
+        <v>10.678594626429463</v>
       </c>
       <c r="H149">
         <v>11.141083995322287</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>42856</v>
       </c>
@@ -6752,23 +5279,22 @@
         <f t="shared" si="9"/>
         <v>206987.07897083068</v>
       </c>
-      <c r="E150" t="e">
-        <f>VLOOKUP(B150,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F150" t="e">
+      <c r="E150">
+        <v>47419200</v>
+      </c>
+      <c r="F150">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G150" t="e">
+        <v>43650.478913779792</v>
+      </c>
+      <c r="G150">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
+        <v>10.683969532886364</v>
       </c>
       <c r="H150">
         <v>11.141031822633783</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>42887</v>
       </c>
@@ -6783,23 +5309,22 @@
         <f t="shared" si="9"/>
         <v>209744.6288726675</v>
       </c>
-      <c r="E151" t="e">
-        <f>VLOOKUP(B151,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F151" t="e">
+      <c r="E151">
+        <v>47419200</v>
+      </c>
+      <c r="F151">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G151" t="e">
+        <v>44232.00494159908</v>
+      </c>
+      <c r="G151">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
+        <v>10.697203899737763</v>
       </c>
       <c r="H151">
         <v>11.157301061466677</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>42917</v>
       </c>
@@ -6814,23 +5339,22 @@
         <f t="shared" si="9"/>
         <v>207157.82691248017</v>
       </c>
-      <c r="E152" t="e">
-        <f>VLOOKUP(B152,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F152" t="e">
+      <c r="E152">
+        <v>47419200</v>
+      </c>
+      <c r="F152">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G152" t="e">
+        <v>43686.487100684993</v>
+      </c>
+      <c r="G152">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
+        <v>10.684794113601464</v>
       </c>
       <c r="H152">
         <v>11.147389021362017</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>42948</v>
       </c>
@@ -6845,23 +5369,22 @@
         <f t="shared" si="9"/>
         <v>209534.15567828948</v>
       </c>
-      <c r="E153" t="e">
-        <f>VLOOKUP(B153,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F153" t="e">
+      <c r="E153">
+        <v>47419200</v>
+      </c>
+      <c r="F153">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G153" t="e">
+        <v>44187.619293090029</v>
+      </c>
+      <c r="G153">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
+        <v>10.696199922337463</v>
       </c>
       <c r="H153">
         <v>11.152704082174399</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>42979</v>
       </c>
@@ -6876,23 +5399,22 @@
         <f t="shared" si="9"/>
         <v>209704.38554532145</v>
       </c>
-      <c r="E154" t="e">
-        <f>VLOOKUP(B154,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F154" t="e">
+      <c r="E154">
+        <v>47419200</v>
+      </c>
+      <c r="F154">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G154" t="e">
+        <v>44223.518225807573</v>
+      </c>
+      <c r="G154">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
+        <v>10.697012013114664</v>
       </c>
       <c r="H154">
         <v>11.14966695682512</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>43009</v>
       </c>
@@ -6907,23 +5429,22 @@
         <f t="shared" si="9"/>
         <v>208456.11893276565</v>
       </c>
-      <c r="E155" t="e">
-        <f>VLOOKUP(B155,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F155" t="e">
+      <c r="E155">
+        <v>47419200</v>
+      </c>
+      <c r="F155">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G155" t="e">
+        <v>43960.27746836</v>
+      </c>
+      <c r="G155">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
+        <v>10.691041720334763</v>
       </c>
       <c r="H155">
         <v>11.147408614533658</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>43040</v>
       </c>
@@ -6938,23 +5459,22 @@
         <f t="shared" si="9"/>
         <v>209151.49837833687</v>
       </c>
-      <c r="E156" t="e">
-        <f>VLOOKUP(B156,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F156" t="e">
+      <c r="E156">
+        <v>47419200</v>
+      </c>
+      <c r="F156">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G156" t="e">
+        <v>44106.922592185627</v>
+      </c>
+      <c r="G156">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
+        <v>10.694372023995163</v>
       </c>
       <c r="H156">
         <v>11.147446034305824</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>43070</v>
       </c>
@@ -6969,23 +5489,22 @@
         <f t="shared" si="9"/>
         <v>211697.3864913203</v>
       </c>
-      <c r="E157" t="e">
-        <f>VLOOKUP(B157,[1]Nacional_1950_2017!$A$2:$C$69,3,0)</f>
-        <v>#N/A</v>
-      </c>
-      <c r="F157" t="e">
+      <c r="E157">
+        <v>47419200</v>
+      </c>
+      <c r="F157">
         <f t="shared" si="10"/>
-        <v>#N/A</v>
-      </c>
-      <c r="G157" t="e">
+        <v>44643.812314699593</v>
+      </c>
+      <c r="G157">
         <f t="shared" si="11"/>
-        <v>#N/A</v>
+        <v>10.706470994723663</v>
       </c>
       <c r="H157">
         <v>11.168411705682324</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>43101</v>
       </c>
@@ -7001,22 +5520,21 @@
         <v>208371.92931692087</v>
       </c>
       <c r="E158">
-        <f>VLOOKUP(B158,[2]Hoja1!$A$2:$C$54,3,0)</f>
         <v>48258494</v>
       </c>
       <c r="F158">
         <f t="shared" si="10"/>
-        <v>4317829.0917433286</v>
+        <v>43178.290917433289</v>
       </c>
       <c r="G158">
         <f t="shared" si="11"/>
-        <v>15.278263308852843</v>
+        <v>10.673093122864753</v>
       </c>
       <c r="H158">
         <v>11.154061619903645</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>43132</v>
       </c>
@@ -7032,22 +5550,21 @@
         <v>210177.39353091837</v>
       </c>
       <c r="E159">
-        <f>VLOOKUP(B159,[2]Hoja1!$A$2:$C$54,3,0)</f>
         <v>48258494</v>
       </c>
       <c r="F159">
         <f t="shared" si="10"/>
-        <v>4355241.4530573282</v>
+        <v>43552.414530573289</v>
       </c>
       <c r="G159">
         <f t="shared" si="11"/>
-        <v>15.286890609454542</v>
+        <v>10.681720423466452</v>
       </c>
       <c r="H159">
         <v>11.155412949428232</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>43160</v>
       </c>
@@ -7063,22 +5580,21 @@
         <v>212181.82733577312</v>
       </c>
       <c r="E160">
-        <f>VLOOKUP(B160,[2]Hoja1!$A$2:$C$54,3,0)</f>
         <v>48258494</v>
       </c>
       <c r="F160">
         <f t="shared" si="10"/>
-        <v>4396776.8106433889</v>
+        <v>43967.76810643389</v>
       </c>
       <c r="G160">
         <f t="shared" si="11"/>
-        <v>15.296382287412142</v>
+        <v>10.691212101424052</v>
       </c>
       <c r="H160">
         <v>11.174061013689279</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>43191</v>
       </c>
@@ -7094,22 +5610,21 @@
         <v>211688.25276477117</v>
       </c>
       <c r="E161">
-        <f>VLOOKUP(B161,[2]Hoja1!$A$2:$C$54,3,0)</f>
         <v>48258494</v>
       </c>
       <c r="F161">
         <f t="shared" si="10"/>
-        <v>4386549.0863592047</v>
+        <v>43865.490863592051</v>
       </c>
       <c r="G161">
         <f t="shared" si="11"/>
-        <v>15.294053390812643</v>
+        <v>10.688883204824553</v>
       </c>
       <c r="H161">
         <v>11.161625373486585</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>43221</v>
       </c>
@@ -7125,22 +5640,21 @@
         <v>213264.71426338574</v>
       </c>
       <c r="E162">
-        <f>VLOOKUP(B162,[2]Hoja1!$A$2:$C$54,3,0)</f>
         <v>48258494</v>
       </c>
       <c r="F162">
         <f t="shared" si="10"/>
-        <v>4419216.1127818404</v>
+        <v>44192.161127818399</v>
       </c>
       <c r="G162">
         <f t="shared" si="11"/>
-        <v>15.301472888276145</v>
+        <v>10.696302702288053</v>
       </c>
       <c r="H162">
         <v>11.165543861291615</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>43252</v>
       </c>
@@ -7156,22 +5670,21 @@
         <v>214466.16616037401</v>
       </c>
       <c r="E163">
-        <f>VLOOKUP(B163,[2]Hoja1!$A$2:$C$54,3,0)</f>
         <v>48258494</v>
       </c>
       <c r="F163">
         <f t="shared" si="10"/>
-        <v>4444112.2874736618</v>
+        <v>44441.122874736619</v>
       </c>
       <c r="G163">
         <f t="shared" si="11"/>
-        <v>15.307090696630741</v>
+        <v>10.701920510642651</v>
       </c>
       <c r="H163">
         <v>11.175719663844509</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>43282</v>
       </c>
@@ -7187,22 +5700,21 @@
         <v>213170.61397645649</v>
       </c>
       <c r="E164">
-        <f>VLOOKUP(B164,[2]Hoja1!$A$2:$C$54,3,0)</f>
         <v>48258494</v>
       </c>
       <c r="F164">
         <f t="shared" si="10"/>
-        <v>4417266.1910348153</v>
+        <v>44172.661910348157</v>
       </c>
       <c r="G164">
         <f t="shared" si="11"/>
-        <v>15.301031553882742</v>
+        <v>10.695861367894652</v>
       </c>
       <c r="H164">
         <v>11.17397713379491</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>43313</v>
       </c>
@@ -7218,22 +5730,21 @@
         <v>215896.40884396111</v>
       </c>
       <c r="E165">
-        <f>VLOOKUP(B165,[2]Hoja1!$A$2:$C$54,3,0)</f>
         <v>48258494</v>
       </c>
       <c r="F165">
         <f t="shared" si="10"/>
-        <v>4473749.4055235349</v>
+        <v>44737.494055235358</v>
       </c>
       <c r="G165">
         <f t="shared" si="11"/>
-        <v>15.313737408181343</v>
+        <v>10.708567222193253</v>
       </c>
       <c r="H165">
         <v>11.177497208969454</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>43344</v>
       </c>
@@ -7249,22 +5760,21 @@
         <v>214981.10476109822</v>
       </c>
       <c r="E166">
-        <f>VLOOKUP(B166,[2]Hoja1!$A$2:$C$54,3,0)</f>
         <v>48258494</v>
       </c>
       <c r="F166">
         <f t="shared" si="10"/>
-        <v>4454782.7116423948</v>
+        <v>44547.827116423941</v>
       </c>
       <c r="G166">
         <f t="shared" si="11"/>
-        <v>15.309488843655444</v>
+        <v>10.704318657667352</v>
       </c>
       <c r="H166">
         <v>11.181812899817777</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>43374</v>
       </c>
@@ -7280,22 +5790,21 @@
         <v>215563.20783441013</v>
       </c>
       <c r="E167">
-        <f>VLOOKUP(B167,[2]Hoja1!$A$2:$C$54,3,0)</f>
         <v>48258494</v>
       </c>
       <c r="F167">
         <f t="shared" si="10"/>
-        <v>4466844.9005973982</v>
+        <v>44668.449005973984</v>
       </c>
       <c r="G167">
         <f t="shared" si="11"/>
-        <v>15.312192878575742</v>
+        <v>10.707022692587651</v>
       </c>
       <c r="H167">
         <v>11.18014521110385</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>43405</v>
       </c>
@@ -7311,22 +5820,21 @@
         <v>216396.99388373308</v>
       </c>
       <c r="E168">
-        <f>VLOOKUP(B168,[2]Hoja1!$A$2:$C$54,3,0)</f>
         <v>48258494</v>
       </c>
       <c r="F168">
         <f t="shared" si="10"/>
-        <v>4484122.3989238683</v>
+        <v>44841.223989238679</v>
       </c>
       <c r="G168">
         <f t="shared" si="11"/>
-        <v>15.316053359617843</v>
+        <v>10.710883173629751</v>
       </c>
       <c r="H168">
         <v>11.184865420843131</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>43435</v>
       </c>
@@ -7342,22 +5850,21 @@
         <v>215901.55573421984</v>
       </c>
       <c r="E169">
-        <f>VLOOKUP(B169,[2]Hoja1!$A$2:$C$54,3,0)</f>
         <v>48258494</v>
       </c>
       <c r="F169">
         <f t="shared" si="10"/>
-        <v>4473856.0580489691</v>
+        <v>44738.560580489699</v>
       </c>
       <c r="G169">
         <f t="shared" si="11"/>
-        <v>15.313761247526042</v>
+        <v>10.708591061537952</v>
       </c>
       <c r="H169">
         <v>11.188060018270987</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>43466</v>
       </c>
@@ -7373,22 +5880,21 @@
         <v>217371.64530518645</v>
       </c>
       <c r="E170">
-        <f>VLOOKUP(B170,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>49266526</v>
+        <v>49395678</v>
       </c>
       <c r="F170">
         <f t="shared" si="10"/>
-        <v>4412156.9543017186</v>
+        <v>44006.207446972679</v>
       </c>
       <c r="G170">
         <f t="shared" si="11"/>
-        <v>15.299874233133863</v>
+        <v>10.692085981290074</v>
       </c>
       <c r="H170">
         <v>11.191648759693285</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>43497</v>
       </c>
@@ -7404,22 +5910,21 @@
         <v>219298.80281661134</v>
       </c>
       <c r="E171">
-        <f>VLOOKUP(B171,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>49266526</v>
+        <v>49395678</v>
       </c>
       <c r="F171">
         <f t="shared" si="10"/>
-        <v>4451273.9302262012</v>
+        <v>44396.354437449227</v>
       </c>
       <c r="G171">
         <f t="shared" si="11"/>
-        <v>15.308700889628463</v>
+        <v>10.700912637784674</v>
       </c>
       <c r="H171">
         <v>11.190758574223915</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>43525</v>
       </c>
@@ -7435,22 +5940,21 @@
         <v>216347.74137933442</v>
       </c>
       <c r="E172">
-        <f>VLOOKUP(B172,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>49266526</v>
+        <v>49395678</v>
       </c>
       <c r="F172">
         <f t="shared" si="10"/>
-        <v>4391374.000661918</v>
+        <v>43798.921310349142</v>
       </c>
       <c r="G172">
         <f t="shared" si="11"/>
-        <v>15.295152720287463</v>
+        <v>10.687364468443674</v>
       </c>
       <c r="H172">
         <v>11.189419060633849</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>43556</v>
       </c>
@@ -7466,22 +5970,21 @@
         <v>219034.64816740583</v>
       </c>
       <c r="E173">
-        <f>VLOOKUP(B173,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>49266526</v>
+        <v>49395678</v>
       </c>
       <c r="F173">
         <f t="shared" si="10"/>
-        <v>4445912.1832013456</v>
+        <v>44342.877157674775</v>
       </c>
       <c r="G173">
         <f t="shared" si="11"/>
-        <v>15.307495621444664</v>
+        <v>10.699707369600874</v>
       </c>
       <c r="H173">
         <v>11.200222838687612</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>43586</v>
       </c>
@@ -7497,22 +6000,21 @@
         <v>221095.67723531576</v>
       </c>
       <c r="E174">
-        <f>VLOOKUP(B174,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>49266526</v>
+        <v>49395678</v>
       </c>
       <c r="F174">
         <f t="shared" si="10"/>
-        <v>4487746.451521988</v>
+        <v>44760.126024652556</v>
       </c>
       <c r="G174">
         <f t="shared" si="11"/>
-        <v>15.316861229829865</v>
+        <v>10.709072977986075</v>
       </c>
       <c r="H174">
         <v>11.203581884341308</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>43617</v>
       </c>
@@ -7528,22 +6030,21 @@
         <v>218613.89087572767</v>
       </c>
       <c r="E175">
-        <f>VLOOKUP(B175,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>49266526</v>
+        <v>49395678</v>
       </c>
       <c r="F175">
         <f t="shared" si="10"/>
-        <v>4437371.75370814</v>
+        <v>44257.696164374473</v>
       </c>
       <c r="G175">
         <f t="shared" si="11"/>
-        <v>15.305572811775365</v>
+        <v>10.697784559931575</v>
       </c>
       <c r="H175">
         <v>11.202337520008705</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>43647</v>
       </c>
@@ -7559,22 +6060,21 @@
         <v>221915.9657630072</v>
       </c>
       <c r="E176">
-        <f>VLOOKUP(B176,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>49266526</v>
+        <v>49395678</v>
       </c>
       <c r="F176">
         <f t="shared" si="10"/>
-        <v>4504396.4691768037</v>
+        <v>44926.190862894364</v>
       </c>
       <c r="G176">
         <f t="shared" si="11"/>
-        <v>15.320564470943765</v>
+        <v>10.712776219099975</v>
       </c>
       <c r="H176">
         <v>11.211138536571827</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>43678</v>
       </c>
@@ -7590,22 +6090,21 @@
         <v>221875.62485432558</v>
       </c>
       <c r="E177">
-        <f>VLOOKUP(B177,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>49266526</v>
+        <v>49395678</v>
       </c>
       <c r="F177">
         <f t="shared" si="10"/>
-        <v>4503577.6391931027</v>
+        <v>44918.023972527633</v>
       </c>
       <c r="G177">
         <f t="shared" si="11"/>
-        <v>15.320382669802664</v>
+        <v>10.712594417958874</v>
       </c>
       <c r="H177">
         <v>11.208470423126608</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>43709</v>
       </c>
@@ -7621,22 +6120,21 @@
         <v>220150.25025999165</v>
       </c>
       <c r="E178">
-        <f>VLOOKUP(B178,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>49266526</v>
+        <v>49395678</v>
       </c>
       <c r="F178">
         <f t="shared" si="10"/>
-        <v>4468556.4039971409</v>
+        <v>44568.727300390863</v>
       </c>
       <c r="G178">
         <f t="shared" si="11"/>
-        <v>15.312575962303564</v>
+        <v>10.704787710459774</v>
       </c>
       <c r="H178">
         <v>11.207950944406583</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>43739</v>
       </c>
@@ -7652,22 +6150,21 @@
         <v>222720.95008343188</v>
       </c>
       <c r="E179">
-        <f>VLOOKUP(B179,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>49266526</v>
+        <v>49395678</v>
       </c>
       <c r="F179">
         <f t="shared" si="10"/>
-        <v>4520735.845743048</v>
+        <v>45089.157412401932</v>
       </c>
       <c r="G179">
         <f t="shared" si="11"/>
-        <v>15.324185336289064</v>
+        <v>10.716397084445275</v>
       </c>
       <c r="H179">
         <v>11.215747704038442</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>43770</v>
       </c>
@@ -7683,22 +6180,21 @@
         <v>222095.43034112785</v>
       </c>
       <c r="E180">
-        <f>VLOOKUP(B180,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>49266526</v>
+        <v>49395678</v>
       </c>
       <c r="F180">
         <f t="shared" si="10"/>
-        <v>4508039.1976720225</v>
+        <v>44962.522903547921</v>
       </c>
       <c r="G180">
         <f t="shared" si="11"/>
-        <v>15.321372849239765</v>
+        <v>10.713584597395975</v>
       </c>
       <c r="H180">
         <v>11.217962125350629</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>43800</v>
       </c>
@@ -7714,22 +6210,21 @@
         <v>223175.61309013772</v>
       </c>
       <c r="E181">
-        <f>VLOOKUP(B181,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>49266526</v>
+        <v>49395678</v>
       </c>
       <c r="F181">
         <f t="shared" si="10"/>
-        <v>4529964.4852193901</v>
+        <v>45181.202511308315</v>
       </c>
       <c r="G181">
         <f t="shared" si="11"/>
-        <v>15.326224657521065</v>
+        <v>10.718436405677275</v>
       </c>
       <c r="H181">
         <v>11.221017508458294</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>43831</v>
       </c>
@@ -7745,19 +6240,18 @@
         <v>225975.1462714927</v>
       </c>
       <c r="E182">
-        <f>VLOOKUP(B182,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>50390790</v>
+        <v>50407647</v>
       </c>
       <c r="F182">
         <f t="shared" si="10"/>
-        <v>4484453.335053741</v>
+        <v>44829.536731102075</v>
       </c>
       <c r="G182">
         <f t="shared" si="11"/>
-        <v>15.316127158655691</v>
-      </c>
-    </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.35">
+        <v>10.7106225031925</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>43862</v>
       </c>
@@ -7773,19 +6267,18 @@
         <v>226551.88323723862</v>
       </c>
       <c r="E183">
-        <f>VLOOKUP(B183,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>50390790</v>
+        <v>50407647</v>
       </c>
       <c r="F183">
         <f t="shared" si="10"/>
-        <v>4495898.6203081682</v>
+        <v>44943.951309062024</v>
       </c>
       <c r="G183">
         <f t="shared" si="11"/>
-        <v>15.318676121437592</v>
-      </c>
-    </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.35">
+        <v>10.713171465974401</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>43891</v>
       </c>
@@ -7801,19 +6294,18 @@
         <v>203469.71401378702</v>
       </c>
       <c r="E184">
-        <f>VLOOKUP(B184,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>50390790</v>
+        <v>50407647</v>
       </c>
       <c r="F184">
         <f t="shared" si="10"/>
-        <v>4037835.3666173322</v>
+        <v>40364.850597725184</v>
       </c>
       <c r="G184">
         <f t="shared" si="11"/>
-        <v>15.211219306002791</v>
-      </c>
-    </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.35">
+        <v>10.6057146505396</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>43922</v>
       </c>
@@ -7829,19 +6321,18 @@
         <v>174485.54433390935</v>
       </c>
       <c r="E185">
-        <f>VLOOKUP(B185,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>50390790</v>
+        <v>50407647</v>
       </c>
       <c r="F185">
         <f t="shared" si="10"/>
-        <v>3462647.5261433558</v>
+        <v>34614.895699041328</v>
       </c>
       <c r="G185">
         <f t="shared" si="11"/>
-        <v>15.057544035398491</v>
-      </c>
-    </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.35">
+        <v>10.4520393799353</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>43952</v>
       </c>
@@ -7857,19 +6348,18 @@
         <v>182600.1765429868</v>
       </c>
       <c r="E186">
-        <f>VLOOKUP(B186,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>50390790</v>
+        <v>50407647</v>
       </c>
       <c r="F186">
         <f t="shared" si="10"/>
-        <v>3623681.5605190308</v>
+        <v>36224.697523172785</v>
       </c>
       <c r="G186">
         <f t="shared" si="11"/>
-        <v>15.103001072670292</v>
-      </c>
-    </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.35">
+        <v>10.497496417207101</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>43983</v>
       </c>
@@ -7885,19 +6375,18 @@
         <v>191813.48169248214</v>
       </c>
       <c r="E187">
-        <f>VLOOKUP(B187,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>50390790</v>
+        <v>50407647</v>
       </c>
       <c r="F187">
         <f t="shared" si="10"/>
-        <v>3806518.6454207627</v>
+        <v>38052.456940210308</v>
       </c>
       <c r="G187">
         <f t="shared" si="11"/>
-        <v>15.152225588027392</v>
-      </c>
-    </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
+        <v>10.546720932564201</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>44013</v>
       </c>
@@ -7913,19 +6402,18 @@
         <v>198250.19677950008</v>
       </c>
       <c r="E188">
-        <f>VLOOKUP(B188,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>50390790</v>
+        <v>50407647</v>
       </c>
       <c r="F188">
         <f t="shared" si="10"/>
-        <v>3934254.5885766051</v>
+        <v>39329.389205471161</v>
       </c>
       <c r="G188">
         <f t="shared" si="11"/>
-        <v>15.185231990777892</v>
-      </c>
-    </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.35">
+        <v>10.579727335314701</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>44044</v>
       </c>
@@ -7941,19 +6429,18 @@
         <v>199017.99485274244</v>
       </c>
       <c r="E189">
-        <f>VLOOKUP(B189,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>50390790</v>
+        <v>50407647</v>
       </c>
       <c r="F189">
         <f t="shared" si="10"/>
-        <v>3949491.4616885833</v>
+        <v>39481.706982423209</v>
       </c>
       <c r="G189">
         <f t="shared" si="11"/>
-        <v>15.189097384712792</v>
-      </c>
-    </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.35">
+        <v>10.583592729249601</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>44075</v>
       </c>
@@ -7969,19 +6456,18 @@
         <v>206606.37499733624</v>
       </c>
       <c r="E190">
-        <f>VLOOKUP(B190,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>50390790</v>
+        <v>50407647</v>
       </c>
       <c r="F190">
         <f t="shared" si="10"/>
-        <v>4100082.0784380687</v>
+        <v>40987.109554496019</v>
       </c>
       <c r="G190">
         <f t="shared" si="11"/>
-        <v>15.226517550605392</v>
-      </c>
-    </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.35">
+        <v>10.621012895142201</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>44105</v>
       </c>
@@ -7997,19 +6483,18 @@
         <v>212813.11796833118</v>
       </c>
       <c r="E191">
-        <f>VLOOKUP(B191,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>50390790</v>
+        <v>50407647</v>
       </c>
       <c r="F191">
         <f t="shared" si="10"/>
-        <v>4223254.2488087844</v>
+        <v>42218.419353780031</v>
       </c>
       <c r="G191">
         <f t="shared" si="11"/>
-        <v>15.256116537836391</v>
-      </c>
-    </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.35">
+        <v>10.6506118823732</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>44136</v>
       </c>
@@ -8025,19 +6510,18 @@
         <v>214719.01227527257</v>
       </c>
       <c r="E192">
-        <f>VLOOKUP(B192,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>50390790</v>
+        <v>50407647</v>
       </c>
       <c r="F192">
         <f t="shared" si="10"/>
-        <v>4261076.5236122031</v>
+        <v>42596.515619003716</v>
       </c>
       <c r="G192">
         <f t="shared" si="11"/>
-        <v>15.265032391394291</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.6595277359311</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>44166</v>
       </c>
@@ -8053,19 +6537,18 @@
         <v>218767.25435629967</v>
       </c>
       <c r="E193">
-        <f>VLOOKUP(B193,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>50390790</v>
+        <v>50407647</v>
       </c>
       <c r="F193">
         <f t="shared" si="10"/>
-        <v>4341413.4677447937</v>
+        <v>43399.616402705658</v>
       </c>
       <c r="G193">
         <f t="shared" si="11"/>
-        <v>15.283710536865291</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.6782058814021</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>44197</v>
       </c>
@@ -8081,19 +6564,18 @@
         <v>217508.95726918193</v>
       </c>
       <c r="E194">
-        <f>VLOOKUP(B194,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>51115637</v>
+        <v>51117378</v>
       </c>
       <c r="F194">
         <f t="shared" si="10"/>
-        <v>4255233.2326247236</v>
+        <v>42550.883042002257</v>
       </c>
       <c r="G194">
         <f t="shared" si="11"/>
-        <v>15.263660132265235</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.65845588682971</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>44228</v>
       </c>
@@ -8109,19 +6591,18 @@
         <v>221921.49038160787</v>
       </c>
       <c r="E195">
-        <f>VLOOKUP(B195,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>51115637</v>
+        <v>51117378</v>
       </c>
       <c r="F195">
-        <f t="shared" ref="F195:F253" si="14">D195*1000000000/E195</f>
-        <v>4341557.7581789279</v>
+        <f t="shared" ref="F195:F253" si="14">D195*10000000/E195</f>
+        <v>43414.098896388597</v>
       </c>
       <c r="G195">
         <f t="shared" ref="G195:G253" si="15">LN(F195)</f>
-        <v>15.283743772132436</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.678539526696911</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>44256</v>
       </c>
@@ -8137,19 +6618,18 @@
         <v>226063.74977166264</v>
       </c>
       <c r="E196">
-        <f>VLOOKUP(B196,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>51115637</v>
+        <v>51117378</v>
       </c>
       <c r="F196">
         <f t="shared" si="14"/>
-        <v>4422594.7878075475</v>
+        <v>44224.441592380317</v>
       </c>
       <c r="G196">
         <f t="shared" si="15"/>
-        <v>15.302237137868936</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.697032892433411</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>44287</v>
       </c>
@@ -8165,19 +6645,18 @@
         <v>219705.48891183452</v>
       </c>
       <c r="E197">
-        <f>VLOOKUP(B197,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>51115637</v>
+        <v>51117378</v>
       </c>
       <c r="F197">
         <f t="shared" si="14"/>
-        <v>4298205.046565976</v>
+        <v>42980.586545701641</v>
       </c>
       <c r="G197">
         <f t="shared" si="15"/>
-        <v>15.273708062484037</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.668503817048512</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>44317</v>
       </c>
@@ -8193,19 +6672,18 @@
         <v>207515.85609799196</v>
       </c>
       <c r="E198">
-        <f>VLOOKUP(B198,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>51115637</v>
+        <v>51117378</v>
       </c>
       <c r="F198">
         <f t="shared" si="14"/>
-        <v>4059733.3473119382</v>
+        <v>40595.950773921148</v>
       </c>
       <c r="G198">
         <f t="shared" si="15"/>
-        <v>15.216627851419036</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.611423605983511</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>44348</v>
       </c>
@@ -8221,19 +6699,18 @@
         <v>223318.78920326702</v>
       </c>
       <c r="E199">
-        <f>VLOOKUP(B199,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>51115637</v>
+        <v>51117378</v>
       </c>
       <c r="F199">
         <f t="shared" si="14"/>
-        <v>4368893.7927794391</v>
+        <v>43687.449932049924</v>
       </c>
       <c r="G199">
         <f t="shared" si="15"/>
-        <v>15.290020398363536</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.684816152928011</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>44378</v>
       </c>
@@ -8249,19 +6726,18 @@
         <v>225631.85611299242</v>
       </c>
       <c r="E200">
-        <f>VLOOKUP(B200,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>51115637</v>
+        <v>51117378</v>
       </c>
       <c r="F200">
         <f t="shared" si="14"/>
-        <v>4414145.4426752506</v>
+        <v>44139.951018808599</v>
       </c>
       <c r="G200">
         <f t="shared" si="15"/>
-        <v>15.300324815567535</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.69512057013201</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>44409</v>
       </c>
@@ -8277,19 +6753,18 @@
         <v>223614.9458140317</v>
       </c>
       <c r="E201">
-        <f>VLOOKUP(B201,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>51115637</v>
+        <v>51117378</v>
       </c>
       <c r="F201">
         <f t="shared" si="14"/>
-        <v>4374687.6482050233</v>
+        <v>43745.386512984231</v>
       </c>
       <c r="G201">
         <f t="shared" si="15"/>
-        <v>15.291345680529135</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.68614143509361</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>44440</v>
       </c>
@@ -8305,19 +6780,18 @@
         <v>236190.41819077337</v>
       </c>
       <c r="E202">
-        <f>VLOOKUP(B202,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>51115637</v>
+        <v>51117378</v>
       </c>
       <c r="F202">
         <f t="shared" si="14"/>
-        <v>4620707.7139774933</v>
+        <v>46205.503379060909</v>
       </c>
       <c r="G202">
         <f t="shared" si="15"/>
-        <v>15.346058436169935</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.74085419073441</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>44470</v>
       </c>
@@ -8333,19 +6807,18 @@
         <v>235723.98542333118</v>
       </c>
       <c r="E203">
-        <f>VLOOKUP(B203,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>51115637</v>
+        <v>51117378</v>
       </c>
       <c r="F203">
         <f t="shared" si="14"/>
-        <v>4611582.6635072781</v>
+        <v>46114.255982247603</v>
       </c>
       <c r="G203">
         <f t="shared" si="15"/>
-        <v>15.344081667011135</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.73887742157561</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>44501</v>
       </c>
@@ -8361,19 +6834,18 @@
         <v>239205.46366939761</v>
       </c>
       <c r="E204">
-        <f>VLOOKUP(B204,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>51115637</v>
+        <v>51117378</v>
       </c>
       <c r="F204">
         <f t="shared" si="14"/>
-        <v>4679692.5111076599</v>
+        <v>46795.331260808722</v>
       </c>
       <c r="G204">
         <f t="shared" si="15"/>
-        <v>15.358742962980536</v>
-      </c>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.753538717545011</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>44531</v>
       </c>
@@ -8389,19 +6861,18 @@
         <v>242983.27955008188</v>
       </c>
       <c r="E205">
-        <f>VLOOKUP(B205,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>51115637</v>
+        <v>51117378</v>
       </c>
       <c r="F205">
         <f t="shared" si="14"/>
-        <v>4753599.7555910703</v>
+        <v>47534.378533672418</v>
       </c>
       <c r="G205">
         <f t="shared" si="15"/>
-        <v>15.374412732274935</v>
-      </c>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.76920848683941</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>44562</v>
       </c>
@@ -8417,19 +6888,18 @@
         <v>236223.37569835974</v>
       </c>
       <c r="E206">
-        <f>VLOOKUP(B206,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>51643565</v>
+        <v>51682692</v>
       </c>
       <c r="F206">
         <f t="shared" si="14"/>
-        <v>4574110.5537226126</v>
+        <v>45706.476686307236</v>
       </c>
       <c r="G206">
         <f t="shared" si="15"/>
-        <v>15.335922823303951</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.729995288641744</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>44593</v>
       </c>
@@ -8445,19 +6915,18 @@
         <v>239168.90996647952</v>
       </c>
       <c r="E207">
-        <f>VLOOKUP(B207,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>51643565</v>
+        <v>51682692</v>
       </c>
       <c r="F207">
         <f t="shared" si="14"/>
-        <v>4631146.396777208</v>
+        <v>46276.403320183003</v>
       </c>
       <c r="G207">
         <f t="shared" si="15"/>
-        <v>15.348314997309851</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.742387462647644</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>44621</v>
       </c>
@@ -8473,19 +6942,18 @@
         <v>243310.84171998603</v>
       </c>
       <c r="E208">
-        <f>VLOOKUP(B208,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>51643565</v>
+        <v>51682692</v>
       </c>
       <c r="F208">
         <f t="shared" si="14"/>
-        <v>4711348.678581466</v>
+        <v>47077.818957260592</v>
       </c>
       <c r="G208">
         <f t="shared" si="15"/>
-        <v>15.365484768651951</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.759557233989744</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>44652</v>
       </c>
@@ -8501,19 +6969,18 @@
         <v>243561.39715128616</v>
       </c>
       <c r="E209">
-        <f>VLOOKUP(B209,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>51643565</v>
+        <v>51682692</v>
       </c>
       <c r="F209">
         <f t="shared" si="14"/>
-        <v>4716200.3078464111</v>
+        <v>47126.298520070544</v>
       </c>
       <c r="G209">
         <f t="shared" si="15"/>
-        <v>15.366514013835451</v>
-      </c>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.760586479173243</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>44682</v>
       </c>
@@ -8529,19 +6996,18 @@
         <v>243835.07435677788</v>
       </c>
       <c r="E210">
-        <f>VLOOKUP(B210,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>51643565</v>
+        <v>51682692</v>
       </c>
       <c r="F210">
         <f t="shared" si="14"/>
-        <v>4721499.6555094114</v>
+        <v>47179.25187735536</v>
       </c>
       <c r="G210">
         <f t="shared" si="15"/>
-        <v>15.36763703072315</v>
-      </c>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.761709496060943</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>44713</v>
       </c>
@@ -8557,19 +7023,18 @@
         <v>242913.05378743328</v>
       </c>
       <c r="E211">
-        <f>VLOOKUP(B211,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>51643565</v>
+        <v>51682692</v>
       </c>
       <c r="F211">
         <f t="shared" si="14"/>
-        <v>4703646.1132656755</v>
+        <v>47000.851617294487</v>
       </c>
       <c r="G211">
         <f t="shared" si="15"/>
-        <v>15.363848534707151</v>
-      </c>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.757921000044943</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>44743</v>
       </c>
@@ -8585,19 +7050,18 @@
         <v>241208.99511660927</v>
       </c>
       <c r="E212">
-        <f>VLOOKUP(B212,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>51643565</v>
+        <v>51682692</v>
       </c>
       <c r="F212">
         <f t="shared" si="14"/>
-        <v>4670649.5788315395</v>
+        <v>46671.136077162788</v>
       </c>
       <c r="G212">
         <f t="shared" si="15"/>
-        <v>15.35680871608165</v>
-      </c>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.750881181419443</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>44774</v>
       </c>
@@ -8613,19 +7077,18 @@
         <v>245506.69044520461</v>
       </c>
       <c r="E213">
-        <f>VLOOKUP(B213,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>51643565</v>
+        <v>51682692</v>
       </c>
       <c r="F213">
         <f t="shared" si="14"/>
-        <v>4753867.9881066428</v>
+        <v>47502.690154995144</v>
       </c>
       <c r="G213">
         <f t="shared" si="15"/>
-        <v>15.374469157923251</v>
-      </c>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.768541623261044</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>44805</v>
       </c>
@@ -8641,19 +7104,18 @@
         <v>248893.16459047468</v>
       </c>
       <c r="E214">
-        <f>VLOOKUP(B214,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>51643565</v>
+        <v>51682692</v>
       </c>
       <c r="F214">
         <f t="shared" si="14"/>
-        <v>4819441.9690134618</v>
+        <v>48157.933528399546</v>
       </c>
       <c r="G214">
         <f t="shared" si="15"/>
-        <v>15.388168705260851</v>
-      </c>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.782241170598644</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>44835</v>
       </c>
@@ -8669,19 +7131,18 @@
         <v>247351.60544038925</v>
       </c>
       <c r="E215">
-        <f>VLOOKUP(B215,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>51643565</v>
+        <v>51682692</v>
       </c>
       <c r="F215">
         <f t="shared" si="14"/>
-        <v>4789591.993511471</v>
+        <v>47859.659756188637</v>
       </c>
       <c r="G215">
         <f t="shared" si="15"/>
-        <v>15.381955786951551</v>
-      </c>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.776028252289343</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>44866</v>
       </c>
@@ -8697,19 +7158,18 @@
         <v>241142.97686669181</v>
       </c>
       <c r="E216">
-        <f>VLOOKUP(B216,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>51643565</v>
+        <v>51682692</v>
       </c>
       <c r="F216">
         <f t="shared" si="14"/>
-        <v>4669371.2346677035</v>
+        <v>46658.362313381782</v>
       </c>
       <c r="G216">
         <f t="shared" si="15"/>
-        <v>15.35653498132295</v>
-      </c>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.750607446660743</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>44896</v>
       </c>
@@ -8725,19 +7185,18 @@
         <v>245003.50639385392</v>
       </c>
       <c r="E217">
-        <f>VLOOKUP(B217,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>51643565</v>
+        <v>51682692</v>
       </c>
       <c r="F217">
         <f t="shared" si="14"/>
-        <v>4744124.5853932416</v>
+        <v>47405.329891456488</v>
       </c>
       <c r="G217">
         <f t="shared" si="15"/>
-        <v>15.37241748099135</v>
-      </c>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.766489946329143</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>44927</v>
       </c>
@@ -8753,19 +7212,18 @@
         <v>246326.80001164234</v>
       </c>
       <c r="E218">
-        <f>VLOOKUP(B218,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>52117067</v>
+        <v>52215503</v>
       </c>
       <c r="F218">
         <f t="shared" si="14"/>
-        <v>4726413.326591121</v>
+        <v>47175.031524955783</v>
       </c>
       <c r="G218">
         <f t="shared" si="15"/>
-        <v>15.368677190922348</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.761620038492083</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>44958</v>
       </c>
@@ -8781,19 +7239,18 @@
         <v>245522.47343433532</v>
       </c>
       <c r="E219">
-        <f>VLOOKUP(B219,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>52117067</v>
+        <v>52215503</v>
       </c>
       <c r="F219">
         <f t="shared" si="14"/>
-        <v>4710980.2520992849</v>
+        <v>47020.99172238852</v>
       </c>
       <c r="G219">
         <f t="shared" si="15"/>
-        <v>15.365406565803148</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.758349413372882</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>44986</v>
       </c>
@@ -8809,19 +7266,18 @@
         <v>246204.66925834905</v>
       </c>
       <c r="E220">
-        <f>VLOOKUP(B220,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>52117067</v>
+        <v>52215503</v>
       </c>
       <c r="F220">
         <f t="shared" si="14"/>
-        <v>4724069.9339114586</v>
+        <v>47151.641775498952</v>
       </c>
       <c r="G220">
         <f t="shared" si="15"/>
-        <v>15.368181260150747</v>
-      </c>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.761124107720482</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>45017</v>
       </c>
@@ -8837,19 +7293,18 @@
         <v>240795.38710251602</v>
       </c>
       <c r="E221">
-        <f>VLOOKUP(B221,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>52117067</v>
+        <v>52215503</v>
       </c>
       <c r="F221">
         <f t="shared" si="14"/>
-        <v>4620278.9405343169</v>
+        <v>46115.68849629123</v>
       </c>
       <c r="G221">
         <f t="shared" si="15"/>
-        <v>15.345965637974349</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.738908485544084</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>45047</v>
       </c>
@@ -8865,19 +7320,18 @@
         <v>243804.64214415458</v>
       </c>
       <c r="E222">
-        <f>VLOOKUP(B222,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>52117067</v>
+        <v>52215503</v>
       </c>
       <c r="F222">
         <f t="shared" si="14"/>
-        <v>4678019.2397272587</v>
+        <v>46692.00297546776</v>
       </c>
       <c r="G222">
         <f t="shared" si="15"/>
-        <v>15.358385338928247</v>
-      </c>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.751328186497981</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>45078</v>
       </c>
@@ -8893,19 +7347,18 @@
         <v>248874.58595074082</v>
       </c>
       <c r="E223">
-        <f>VLOOKUP(B223,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>52117067</v>
+        <v>52215503</v>
       </c>
       <c r="F223">
         <f t="shared" si="14"/>
-        <v>4775299.1539362874</v>
+        <v>47662.96820902804</v>
       </c>
       <c r="G223">
         <f t="shared" si="15"/>
-        <v>15.378967179973548</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.771910027543283</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>45108</v>
       </c>
@@ -8921,19 +7374,18 @@
         <v>241322.14946175093</v>
       </c>
       <c r="E224">
-        <f>VLOOKUP(B224,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>52117067</v>
+        <v>52215503</v>
       </c>
       <c r="F224">
         <f t="shared" si="14"/>
-        <v>4630386.2314767437</v>
+        <v>46216.570864356305</v>
       </c>
       <c r="G224">
         <f t="shared" si="15"/>
-        <v>15.348150841908648</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.741093689478383</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>45139</v>
       </c>
@@ -8949,19 +7401,18 @@
         <v>245266.12435163982</v>
       </c>
       <c r="E225">
-        <f>VLOOKUP(B225,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>52117067</v>
+        <v>52215503</v>
       </c>
       <c r="F225">
         <f t="shared" si="14"/>
-        <v>4706061.5354973795</v>
+        <v>46971.897283387239</v>
       </c>
       <c r="G225">
         <f t="shared" si="15"/>
-        <v>15.364361924150248</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.757304771719983</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>45170</v>
       </c>
@@ -8977,19 +7428,18 @@
         <v>245973.33347366931</v>
       </c>
       <c r="E226">
-        <f>VLOOKUP(B226,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>52117067</v>
+        <v>52215503</v>
       </c>
       <c r="F226">
         <f t="shared" si="14"/>
-        <v>4719631.1617779508</v>
+        <v>47107.337733329754</v>
       </c>
       <c r="G226">
         <f t="shared" si="15"/>
-        <v>15.367241210817248</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.760184058386983</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>45200</v>
       </c>
@@ -9005,19 +7455,18 @@
         <v>243559.37457944377</v>
       </c>
       <c r="E227">
-        <f>VLOOKUP(B227,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>52117067</v>
+        <v>52215503</v>
       </c>
       <c r="F227">
         <f t="shared" si="14"/>
-        <v>4673313.150554765</v>
+        <v>46645.030802335423</v>
       </c>
       <c r="G227">
         <f t="shared" si="15"/>
-        <v>15.357378832181748</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.750321679751483</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>45231</v>
       </c>
@@ -9033,19 +7482,18 @@
         <v>249022.30881691439</v>
       </c>
       <c r="E228">
-        <f>VLOOKUP(B228,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>52117067</v>
+        <v>52215503</v>
       </c>
       <c r="F228">
         <f t="shared" si="14"/>
-        <v>4778133.5971365077</v>
+        <v>47691.259206468698</v>
       </c>
       <c r="G228">
         <f t="shared" si="15"/>
-        <v>15.379560567367848</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.772503414937583</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
         <v>45261</v>
       </c>
@@ -9061,19 +7509,18 @@
         <v>245982.15829653159</v>
       </c>
       <c r="E229">
-        <f>VLOOKUP(B229,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>52117067</v>
+        <v>52215503</v>
       </c>
       <c r="F229">
         <f t="shared" si="14"/>
-        <v>4719800.4887061585</v>
+        <v>47109.027810482185</v>
       </c>
       <c r="G229">
         <f t="shared" si="15"/>
-        <v>15.367277087326448</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.760219934896183</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>45292</v>
       </c>
@@ -9089,19 +7536,18 @@
         <v>248248.02515142027</v>
       </c>
       <c r="E230">
-        <f>VLOOKUP(B230,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>52613753</v>
+        <v>52695952</v>
       </c>
       <c r="F230">
         <f t="shared" si="14"/>
-        <v>4718310.5366275674</v>
+        <v>47109.50570765289</v>
       </c>
       <c r="G230">
         <f t="shared" si="15"/>
-        <v>15.366961356331768</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.760230079337045</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>45323</v>
       </c>
@@ -9117,19 +7563,18 @@
         <v>247408.63827367732</v>
       </c>
       <c r="E231">
-        <f>VLOOKUP(B231,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>52613753</v>
+        <v>52695952</v>
       </c>
       <c r="F231">
         <f t="shared" si="14"/>
-        <v>4702356.782525613</v>
+        <v>46950.217024958074</v>
       </c>
       <c r="G231">
         <f t="shared" si="15"/>
-        <v>15.363574384090269</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.756843107095547</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>45352</v>
       </c>
@@ -9145,19 +7590,18 @@
         <v>244524.63724520797</v>
       </c>
       <c r="E232">
-        <f>VLOOKUP(B232,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>52613753</v>
+        <v>52695952</v>
       </c>
       <c r="F232">
         <f t="shared" si="14"/>
-        <v>4647542.1976685068</v>
+        <v>46402.92621437183</v>
       </c>
       <c r="G232">
         <f t="shared" si="15"/>
-        <v>15.351849078185468</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.745117801190746</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>45383</v>
       </c>
@@ -9173,19 +7617,18 @@
         <v>251001.21120981759</v>
       </c>
       <c r="E233">
-        <f>VLOOKUP(B233,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>52613753</v>
+        <v>52695952</v>
       </c>
       <c r="F233">
         <f t="shared" si="14"/>
-        <v>4770638.7949519129</v>
+        <v>47631.972036451218</v>
       </c>
       <c r="G233">
         <f t="shared" si="15"/>
-        <v>15.377990773175268</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.771259496180544</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>45413</v>
       </c>
@@ -9201,19 +7644,18 @@
         <v>250075.18179619333</v>
       </c>
       <c r="E234">
-        <f>VLOOKUP(B234,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>52613753</v>
+        <v>52695952</v>
       </c>
       <c r="F234">
         <f t="shared" si="14"/>
-        <v>4753038.2749201208</v>
+        <v>47456.241381917403</v>
       </c>
       <c r="G234">
         <f t="shared" si="15"/>
-        <v>15.374294608355669</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.767563331360947</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>45444</v>
       </c>
@@ -9229,19 +7671,18 @@
         <v>244821.91496781298</v>
       </c>
       <c r="E235">
-        <f>VLOOKUP(B235,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>52613753</v>
+        <v>52695952</v>
       </c>
       <c r="F235">
         <f t="shared" si="14"/>
-        <v>4653192.3880779417</v>
+        <v>46459.339982663754</v>
       </c>
       <c r="G235">
         <f t="shared" si="15"/>
-        <v>15.353064077076668</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.746332800081946</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>45474</v>
       </c>
@@ -9257,19 +7698,18 @@
         <v>248974.43596693745</v>
       </c>
       <c r="E236">
-        <f>VLOOKUP(B236,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>52613753</v>
+        <v>52695952</v>
       </c>
       <c r="F236">
         <f t="shared" si="14"/>
-        <v>4732117.0182810845</v>
+        <v>47247.355160589461</v>
       </c>
       <c r="G236">
         <f t="shared" si="15"/>
-        <v>15.369883232912668</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.763151955917946</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>45505</v>
       </c>
@@ -9285,19 +7725,18 @@
         <v>248172.55962663537</v>
       </c>
       <c r="E237">
-        <f>VLOOKUP(B237,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>52613753</v>
+        <v>52695952</v>
       </c>
       <c r="F237">
         <f t="shared" si="14"/>
-        <v>4716876.205858863</v>
+        <v>47095.184773706213</v>
       </c>
       <c r="G237">
         <f t="shared" si="15"/>
-        <v>15.366657317669068</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.759926040674344</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>45536</v>
       </c>
@@ -9313,19 +7752,18 @@
         <v>247567.09582400933</v>
       </c>
       <c r="E238">
-        <f>VLOOKUP(B238,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>52613753</v>
+        <v>52695952</v>
       </c>
       <c r="F238">
         <f t="shared" si="14"/>
-        <v>4705368.4960282026</v>
+        <v>46980.287181074047</v>
       </c>
       <c r="G238">
         <f t="shared" si="15"/>
-        <v>15.364214648025769</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.757483371031046</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>45566</v>
       </c>
@@ -9341,19 +7779,18 @@
         <v>252124.44489641525</v>
       </c>
       <c r="E239">
-        <f>VLOOKUP(B239,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>52613753</v>
+        <v>52695952</v>
       </c>
       <c r="F239">
         <f t="shared" si="14"/>
-        <v>4791987.465642591</v>
+        <v>47845.125731178596</v>
       </c>
       <c r="G239">
         <f t="shared" si="15"/>
-        <v>15.382455803090068</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.775724526095345</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>45597</v>
       </c>
@@ -9369,19 +7806,18 @@
         <v>249550.56122534114</v>
       </c>
       <c r="E240">
-        <f>VLOOKUP(B240,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>52613753</v>
+        <v>52695952</v>
       </c>
       <c r="F240">
         <f t="shared" si="14"/>
-        <v>4743067.1069091214</v>
+        <v>47356.685239378763</v>
       </c>
       <c r="G240">
         <f t="shared" si="15"/>
-        <v>15.372194553380568</v>
-      </c>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.765463276385846</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>45627</v>
       </c>
@@ -9397,19 +7833,18 @@
         <v>254084.22425747427</v>
       </c>
       <c r="E241">
-        <f>VLOOKUP(B241,[2]Hoja1!$A$2:$C$54,3,0)</f>
-        <v>52613753</v>
+        <v>52695952</v>
       </c>
       <c r="F241">
         <f t="shared" si="14"/>
-        <v>4829235.8892830601</v>
+        <v>48217.028939428645</v>
       </c>
       <c r="G241">
         <f t="shared" si="15"/>
-        <v>15.390198812137069</v>
-      </c>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.783467535142346</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>45658</v>
       </c>
@@ -9425,19 +7860,18 @@
         <v>253676.58798477723</v>
       </c>
       <c r="E242">
-        <f>VLOOKUP(B242,[2]Hoja1!$A$2:$C$54,3,0)</f>
         <v>53057212</v>
       </c>
       <c r="F242">
         <f t="shared" si="14"/>
-        <v>4781189.5578828612</v>
+        <v>47811.895578828611</v>
       </c>
       <c r="G242">
         <f t="shared" si="15"/>
-        <v>15.380199934988527</v>
-      </c>
-    </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.775029749000435</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
         <v>45689</v>
       </c>
@@ -9453,19 +7887,18 @@
         <v>253920.14000880052</v>
       </c>
       <c r="E243">
-        <f>VLOOKUP(B243,[2]Hoja1!$A$2:$C$54,3,0)</f>
         <v>53057212</v>
       </c>
       <c r="F243">
         <f t="shared" si="14"/>
-        <v>4785779.9239206258</v>
+        <v>47857.799239206259</v>
       </c>
       <c r="G243">
         <f t="shared" si="15"/>
-        <v>15.381159563092027</v>
-      </c>
-    </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.775989377103935</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" s="1">
         <v>45717</v>
       </c>
@@ -9481,19 +7914,18 @@
         <v>251677.4997005793</v>
       </c>
       <c r="E244">
-        <f>VLOOKUP(B244,[2]Hoja1!$A$2:$C$54,3,0)</f>
         <v>53057212</v>
       </c>
       <c r="F244">
         <f t="shared" si="14"/>
-        <v>4743511.5833183872</v>
+        <v>47435.115833183867</v>
       </c>
       <c r="G244">
         <f t="shared" si="15"/>
-        <v>15.372288259747027</v>
-      </c>
-    </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.767118073758935</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
         <v>45748</v>
       </c>
@@ -9509,19 +7941,18 @@
         <v>254111.64637492789</v>
       </c>
       <c r="E245">
-        <f>VLOOKUP(B245,[2]Hoja1!$A$2:$C$54,3,0)</f>
         <v>53057212</v>
       </c>
       <c r="F245">
         <f t="shared" si="14"/>
-        <v>4789389.3553043818</v>
+        <v>47893.89355304381</v>
       </c>
       <c r="G245">
         <f t="shared" si="15"/>
-        <v>15.381913478025426</v>
-      </c>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.776743292037334</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
         <v>45778</v>
       </c>
@@ -9537,19 +7968,18 @@
         <v>255007.01317412505</v>
       </c>
       <c r="E246">
-        <f>VLOOKUP(B246,[2]Hoja1!$A$2:$C$54,3,0)</f>
         <v>53057212</v>
       </c>
       <c r="F246">
         <f t="shared" si="14"/>
-        <v>4806264.8518758407</v>
+        <v>48062.648518758404</v>
       </c>
       <c r="G246">
         <f t="shared" si="15"/>
-        <v>15.385430802348527</v>
-      </c>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.780260616360435</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
         <v>45809</v>
       </c>
@@ -9565,19 +7995,18 @@
         <v>252856.74739302776</v>
       </c>
       <c r="E247">
-        <f>VLOOKUP(B247,[2]Hoja1!$A$2:$C$54,3,0)</f>
         <v>53057212</v>
       </c>
       <c r="F247">
         <f t="shared" si="14"/>
-        <v>4765737.5474804016</v>
+        <v>47657.375474804023</v>
       </c>
       <c r="G247">
         <f t="shared" si="15"/>
-        <v>15.376962867453626</v>
-      </c>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.771792681465534</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
         <v>45839</v>
       </c>
@@ -9593,19 +8022,18 @@
         <v>260186.45683465493</v>
       </c>
       <c r="E248">
-        <f>VLOOKUP(B248,[2]Hoja1!$A$2:$C$54,3,0)</f>
         <v>53057212</v>
       </c>
       <c r="F248">
         <f t="shared" si="14"/>
-        <v>4903884.8259621132</v>
+        <v>49038.848259621132</v>
       </c>
       <c r="G248">
         <f t="shared" si="15"/>
-        <v>15.405538270588726</v>
-      </c>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.800368084600635</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
         <v>45870</v>
       </c>
@@ -9621,19 +8049,18 @@
         <v>254164.82241786242</v>
       </c>
       <c r="E249">
-        <f>VLOOKUP(B249,[2]Hoja1!$A$2:$C$54,3,0)</f>
         <v>53057212</v>
       </c>
       <c r="F249">
         <f t="shared" si="14"/>
-        <v>4790391.5949798198</v>
+        <v>47903.915949798189</v>
       </c>
       <c r="G249">
         <f t="shared" si="15"/>
-        <v>15.382122718650926</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.776952532662834</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
         <v>45901</v>
       </c>
@@ -9649,19 +8076,18 @@
         <v>257287.10814581267</v>
       </c>
       <c r="E250">
-        <f>VLOOKUP(B250,[2]Hoja1!$A$2:$C$54,3,0)</f>
         <v>53057212</v>
       </c>
       <c r="F250">
         <f t="shared" si="14"/>
-        <v>4849239.1222104291</v>
+        <v>48492.391222104299</v>
       </c>
       <c r="G250">
         <f t="shared" si="15"/>
-        <v>15.394332368587927</v>
-      </c>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.789162182599835</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" s="1">
         <v>45931</v>
       </c>
@@ -9677,19 +8103,18 @@
         <v>258608.09110557404</v>
       </c>
       <c r="E251">
-        <f>VLOOKUP(B251,[2]Hoja1!$A$2:$C$54,3,0)</f>
         <v>53057212</v>
       </c>
       <c r="F251">
         <f t="shared" si="14"/>
-        <v>4874136.4530343963</v>
+        <v>48741.364530343963</v>
       </c>
       <c r="G251">
         <f t="shared" si="15"/>
-        <v>15.399453508884227</v>
-      </c>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.794283322896135</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>45962</v>
       </c>
@@ -9705,19 +8130,18 @@
         <v>255823.63195847839</v>
       </c>
       <c r="E252">
-        <f>VLOOKUP(B252,[2]Hoja1!$A$2:$C$54,3,0)</f>
         <v>53057212</v>
       </c>
       <c r="F252">
         <f t="shared" si="14"/>
-        <v>4821656.1390085556</v>
+        <v>48216.561390085546</v>
       </c>
       <c r="G252">
         <f t="shared" si="15"/>
-        <v>15.388628024315427</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10.783457838327335</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>45992</v>
       </c>
@@ -9733,16 +8157,15 @@
         <v>258107.48835843022</v>
       </c>
       <c r="E253">
-        <f>VLOOKUP(B253,[2]Hoja1!$A$2:$C$54,3,0)</f>
         <v>53057212</v>
       </c>
       <c r="F253">
         <f t="shared" si="14"/>
-        <v>4864701.3031598832</v>
+        <v>48647.013031598835</v>
       </c>
       <c r="G253">
         <f t="shared" si="15"/>
-        <v>15.397515874627926</v>
+        <v>10.792345688639834</v>
       </c>
     </row>
   </sheetData>

--- a/Datos/PIB mensual per capita.xlsx
+++ b/Datos/PIB mensual per capita.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Disco C\Repositorios Git\Monetary-Policy-Shocks-and-Central-bank-information-in-Colombia\Datos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Disco C\Repositorios Git\Labor-Market-and-Compositional-Analysis\Compositional Data and Labor MArket\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7439396A-9292-4B5D-A46D-54918C37A183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7A7F776-CE3B-4920-9D20-286E4909DF22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9535A740-7E69-41C9-8479-535D748B30AD}"/>
   </bookViews>
@@ -951,12 +951,12 @@
         <v>41671878</v>
       </c>
       <c r="F2">
-        <f>D2*10000000/E2</f>
-        <v>29957.645918779323</v>
+        <f>D2*1000000000/E2</f>
+        <v>2995764.5918779317</v>
       </c>
       <c r="G2">
         <f>LN(F2)</f>
-        <v>10.307539860404505</v>
+        <v>14.912710046392595</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -978,12 +978,12 @@
         <v>41671878</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F66" si="2">D3*10000000/E3</f>
-        <v>30326.466263442286</v>
+        <f t="shared" ref="F3:F66" si="2">D3*1000000000/E3</f>
+        <v>3032646.6263442286</v>
       </c>
       <c r="G3">
         <f t="shared" ref="G3:G66" si="3">LN(F3)</f>
-        <v>10.319776084282006</v>
+        <v>14.924946270270096</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1006,11 +1006,11 @@
       </c>
       <c r="F4">
         <f t="shared" si="2"/>
-        <v>30424.750759417158</v>
+        <v>3042475.0759417154</v>
       </c>
       <c r="G4">
         <f t="shared" si="3"/>
-        <v>10.323011725855606</v>
+        <v>14.928181911843696</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1033,11 +1033,11 @@
       </c>
       <c r="F5">
         <f t="shared" si="2"/>
-        <v>31133.219806798592</v>
+        <v>3113321.9806798594</v>
       </c>
       <c r="G5">
         <f t="shared" si="3"/>
-        <v>10.346030689079605</v>
+        <v>14.951200875067695</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1060,11 +1060,11 @@
       </c>
       <c r="F6">
         <f t="shared" si="2"/>
-        <v>30776.89355159512</v>
+        <v>3077689.3551595123</v>
       </c>
       <c r="G6">
         <f t="shared" si="3"/>
-        <v>10.334519478050003</v>
+        <v>14.939689664038095</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1087,11 +1087,11 @@
       </c>
       <c r="F7">
         <f t="shared" si="2"/>
-        <v>31039.414563661383</v>
+        <v>3103941.4563661381</v>
       </c>
       <c r="G7">
         <f t="shared" si="3"/>
-        <v>10.343013113412505</v>
+        <v>14.948183299400595</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -1114,11 +1114,11 @@
       </c>
       <c r="F8">
         <f t="shared" si="2"/>
-        <v>30624.673974498612</v>
+        <v>3062467.3974498617</v>
       </c>
       <c r="G8">
         <f t="shared" si="3"/>
-        <v>10.329561302059703</v>
+        <v>14.934731488047795</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -1141,11 +1141,11 @@
       </c>
       <c r="F9">
         <f t="shared" si="2"/>
-        <v>31049.089067486962</v>
+        <v>3104908.9067486962</v>
       </c>
       <c r="G9">
         <f t="shared" si="3"/>
-        <v>10.343324749330206</v>
+        <v>14.948494935318296</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -1168,11 +1168,11 @@
       </c>
       <c r="F10">
         <f t="shared" si="2"/>
-        <v>30977.609835925603</v>
+        <v>3097760.9835925605</v>
       </c>
       <c r="G10">
         <f t="shared" si="3"/>
-        <v>10.341019959152206</v>
+        <v>14.946190145140296</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -1195,11 +1195,11 @@
       </c>
       <c r="F11">
         <f t="shared" si="2"/>
-        <v>31070.024953377564</v>
+        <v>3107002.4953377559</v>
       </c>
       <c r="G11">
         <f t="shared" si="3"/>
-        <v>10.343998805520906</v>
+        <v>14.949168991508996</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -1222,11 +1222,11 @@
       </c>
       <c r="F12">
         <f t="shared" si="2"/>
-        <v>31236.769223060408</v>
+        <v>3123676.9223060408</v>
       </c>
       <c r="G12">
         <f t="shared" si="3"/>
-        <v>10.349351180649803</v>
+        <v>14.954521366637895</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -1249,11 +1249,11 @@
       </c>
       <c r="F13">
         <f t="shared" si="2"/>
-        <v>32044.626691802419</v>
+        <v>3204462.6691802419</v>
       </c>
       <c r="G13">
         <f t="shared" si="3"/>
-        <v>10.374884794371406</v>
+        <v>14.980054980359496</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -1276,11 +1276,11 @@
       </c>
       <c r="F14">
         <f t="shared" si="2"/>
-        <v>31545.90127966442</v>
+        <v>3154590.1279664417</v>
       </c>
       <c r="G14">
         <f t="shared" si="3"/>
-        <v>10.359198947633546</v>
+        <v>14.964369133621638</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -1303,11 +1303,11 @@
       </c>
       <c r="F15">
         <f t="shared" si="2"/>
-        <v>31770.446618856986</v>
+        <v>3177044.6618856988</v>
       </c>
       <c r="G15">
         <f t="shared" si="3"/>
-        <v>10.366291785045046</v>
+        <v>14.971461971033138</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -1330,11 +1330,11 @@
       </c>
       <c r="F16">
         <f t="shared" si="2"/>
-        <v>32093.623653964536</v>
+        <v>3209362.3653964535</v>
       </c>
       <c r="G16">
         <f t="shared" si="3"/>
-        <v>10.376412649323147</v>
+        <v>14.981582835311238</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -1357,11 +1357,11 @@
       </c>
       <c r="F17">
         <f t="shared" si="2"/>
-        <v>32001.445664474704</v>
+        <v>3200144.5664474703</v>
       </c>
       <c r="G17">
         <f t="shared" si="3"/>
-        <v>10.373536357776247</v>
+        <v>14.978706543764339</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1384,11 +1384,11 @@
       </c>
       <c r="F18">
         <f t="shared" si="2"/>
-        <v>32475.62837895652</v>
+        <v>3247562.8378956518</v>
       </c>
       <c r="G18">
         <f t="shared" si="3"/>
-        <v>10.388245190973047</v>
+        <v>14.993415376961138</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="F19">
         <f t="shared" si="2"/>
-        <v>32238.236089270307</v>
+        <v>3223823.6089270306</v>
       </c>
       <c r="G19">
         <f t="shared" si="3"/>
-        <v>10.380908483252547</v>
+        <v>14.986078669240639</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -1438,11 +1438,11 @@
       </c>
       <c r="F20">
         <f t="shared" si="2"/>
-        <v>32485.560046526927</v>
+        <v>3248556.0046526929</v>
       </c>
       <c r="G20">
         <f t="shared" si="3"/>
-        <v>10.388550963323846</v>
+        <v>14.993721149311938</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -1465,11 +1465,11 @@
       </c>
       <c r="F21">
         <f t="shared" si="2"/>
-        <v>32895.460558584426</v>
+        <v>3289546.0558584421</v>
       </c>
       <c r="G21">
         <f t="shared" si="3"/>
-        <v>10.401089950291047</v>
+        <v>15.006260136279138</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -1492,11 +1492,11 @@
       </c>
       <c r="F22">
         <f t="shared" si="2"/>
-        <v>33217.127099833291</v>
+        <v>3321712.7099833288</v>
       </c>
       <c r="G22">
         <f t="shared" si="3"/>
-        <v>10.410820898387046</v>
+        <v>15.015991084375138</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -1519,11 +1519,11 @@
       </c>
       <c r="F23">
         <f t="shared" si="2"/>
-        <v>33190.779712721749</v>
+        <v>3319077.9712721747</v>
       </c>
       <c r="G23">
         <f t="shared" si="3"/>
-        <v>10.410027396837046</v>
+        <v>15.015197582825138</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -1546,11 +1546,11 @@
       </c>
       <c r="F24">
         <f t="shared" si="2"/>
-        <v>33602.775043429727</v>
+        <v>3360277.5043429723</v>
       </c>
       <c r="G24">
         <f t="shared" si="3"/>
-        <v>10.422363933119147</v>
+        <v>15.027534119107239</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -1573,11 +1573,11 @@
       </c>
       <c r="F25">
         <f t="shared" si="2"/>
-        <v>33362.821226801745</v>
+        <v>3336282.1226801742</v>
       </c>
       <c r="G25">
         <f t="shared" si="3"/>
-        <v>10.415197422045647</v>
+        <v>15.020367608033739</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -1600,11 +1600,11 @@
       </c>
       <c r="F26">
         <f t="shared" si="2"/>
-        <v>33230.317137436585</v>
+        <v>3323031.7137436587</v>
       </c>
       <c r="G26">
         <f t="shared" si="3"/>
-        <v>10.411217905011693</v>
+        <v>15.016388090999785</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -1627,11 +1627,11 @@
       </c>
       <c r="F27">
         <f t="shared" si="2"/>
-        <v>33635.447846696115</v>
+        <v>3363544.7846696116</v>
       </c>
       <c r="G27">
         <f t="shared" si="3"/>
-        <v>10.423335785272092</v>
+        <v>15.028505971260184</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -1654,11 +1654,11 @@
       </c>
       <c r="F28">
         <f t="shared" si="2"/>
-        <v>33863.329570335358</v>
+        <v>3386332.9570335359</v>
       </c>
       <c r="G28">
         <f t="shared" si="3"/>
-        <v>10.430087984294392</v>
+        <v>15.035258170282484</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -1681,11 +1681,11 @@
       </c>
       <c r="F29">
         <f t="shared" si="2"/>
-        <v>33579.809285223819</v>
+        <v>3357980.9285223824</v>
       </c>
       <c r="G29">
         <f t="shared" si="3"/>
-        <v>10.421680251199794</v>
+        <v>15.026850437187885</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -1708,11 +1708,11 @@
       </c>
       <c r="F30">
         <f t="shared" si="2"/>
-        <v>34123.515069530709</v>
+        <v>3412351.5069530713</v>
       </c>
       <c r="G30">
         <f t="shared" si="3"/>
-        <v>10.437742017094493</v>
+        <v>15.042912203082585</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -1735,11 +1735,11 @@
       </c>
       <c r="F31">
         <f t="shared" si="2"/>
-        <v>34363.470885275165</v>
+        <v>3436347.0885275165</v>
       </c>
       <c r="G31">
         <f t="shared" si="3"/>
-        <v>10.444749386283894</v>
+        <v>15.049919572271985</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -1762,11 +1762,11 @@
       </c>
       <c r="F32">
         <f t="shared" si="2"/>
-        <v>34379.380317793024</v>
+        <v>3437938.0317793032</v>
       </c>
       <c r="G32">
         <f t="shared" si="3"/>
-        <v>10.445212254277394</v>
+        <v>15.050382440265485</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
@@ -1789,11 +1789,11 @@
       </c>
       <c r="F33">
         <f t="shared" si="2"/>
-        <v>34806.353725038964</v>
+        <v>3480635.3725038962</v>
       </c>
       <c r="G33">
         <f t="shared" si="3"/>
-        <v>10.457555227402892</v>
+        <v>15.062725413390984</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
@@ -1816,11 +1816,11 @@
       </c>
       <c r="F34">
         <f t="shared" si="2"/>
-        <v>34998.724358169129</v>
+        <v>3499872.4358169129</v>
       </c>
       <c r="G34">
         <f t="shared" si="3"/>
-        <v>10.463066892897892</v>
+        <v>15.068237078885984</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
@@ -1843,11 +1843,11 @@
       </c>
       <c r="F35">
         <f t="shared" si="2"/>
-        <v>35044.736224492342</v>
+        <v>3504473.6224492337</v>
       </c>
       <c r="G35">
         <f t="shared" si="3"/>
-        <v>10.464380702140293</v>
+        <v>15.069550888128385</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
@@ -1870,11 +1870,11 @@
       </c>
       <c r="F36">
         <f t="shared" si="2"/>
-        <v>35303.058150803605</v>
+        <v>3530305.815080361</v>
       </c>
       <c r="G36">
         <f t="shared" si="3"/>
-        <v>10.471724872336193</v>
+        <v>15.076895058324284</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
@@ -1897,11 +1897,11 @@
       </c>
       <c r="F37">
         <f t="shared" si="2"/>
-        <v>35113.349335621431</v>
+        <v>3511334.9335621437</v>
       </c>
       <c r="G37">
         <f t="shared" si="3"/>
-        <v>10.466336660101693</v>
+        <v>15.071506846089784</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
@@ -1924,11 +1924,11 @@
       </c>
       <c r="F38">
         <f t="shared" si="2"/>
-        <v>35050.659388668362</v>
+        <v>3505065.938866836</v>
       </c>
       <c r="G38">
         <f t="shared" si="3"/>
-        <v>10.464549705086586</v>
+        <v>15.069719891074678</v>
       </c>
       <c r="H38">
         <v>10.825867333967221</v>
@@ -1954,11 +1954,11 @@
       </c>
       <c r="F39">
         <f t="shared" si="2"/>
-        <v>35089.446160686457</v>
+        <v>3508944.6160686463</v>
       </c>
       <c r="G39">
         <f t="shared" si="3"/>
-        <v>10.465655685058186</v>
+        <v>15.070825871046278</v>
       </c>
       <c r="H39">
         <v>10.821969201776701</v>
@@ -1984,11 +1984,11 @@
       </c>
       <c r="F40">
         <f t="shared" si="2"/>
-        <v>34601.7652588497</v>
+        <v>3460176.5258849701</v>
       </c>
       <c r="G40">
         <f t="shared" si="3"/>
-        <v>10.451659978786287</v>
+        <v>15.056830164774379</v>
       </c>
       <c r="H40">
         <v>10.820108597168071</v>
@@ -2014,11 +2014,11 @@
       </c>
       <c r="F41">
         <f t="shared" si="2"/>
-        <v>35328.48719275558</v>
+        <v>3532848.7192755574</v>
       </c>
       <c r="G41">
         <f t="shared" si="3"/>
-        <v>10.472444920097486</v>
+        <v>15.077615106085577</v>
       </c>
       <c r="H41">
         <v>10.829742946313367</v>
@@ -2044,11 +2044,11 @@
       </c>
       <c r="F42">
         <f t="shared" si="2"/>
-        <v>35020.357343306197</v>
+        <v>3502035.7343306197</v>
       </c>
       <c r="G42">
         <f t="shared" si="3"/>
-        <v>10.463684809765686</v>
+        <v>15.068854995753778</v>
       </c>
       <c r="H42">
         <v>10.823827156518615</v>
@@ -2074,11 +2074,11 @@
       </c>
       <c r="F43">
         <f t="shared" si="2"/>
-        <v>35154.222184354046</v>
+        <v>3515422.2184354048</v>
       </c>
       <c r="G43">
         <f t="shared" si="3"/>
-        <v>10.467500009067885</v>
+        <v>15.072670195055977</v>
       </c>
       <c r="H43">
         <v>10.836154142790827</v>
@@ -2104,11 +2104,11 @@
       </c>
       <c r="F44">
         <f t="shared" si="2"/>
-        <v>35562.841885272035</v>
+        <v>3556284.1885272032</v>
       </c>
       <c r="G44">
         <f t="shared" si="3"/>
-        <v>10.479056604468086</v>
+        <v>15.084226790456178</v>
       </c>
       <c r="H44">
         <v>10.839897642348799</v>
@@ -2134,11 +2134,11 @@
       </c>
       <c r="F45">
         <f t="shared" si="2"/>
-        <v>35337.155316456447</v>
+        <v>3533715.5316456449</v>
       </c>
       <c r="G45">
         <f t="shared" si="3"/>
-        <v>10.472690247909886</v>
+        <v>15.077860433897978</v>
       </c>
       <c r="H45">
         <v>10.8444109041974</v>
@@ -2164,11 +2164,11 @@
       </c>
       <c r="F46">
         <f t="shared" si="2"/>
-        <v>35513.736580651697</v>
+        <v>3551373.6580651696</v>
       </c>
       <c r="G46">
         <f t="shared" si="3"/>
-        <v>10.477674846553086</v>
+        <v>15.082845032541178</v>
       </c>
       <c r="H46">
         <v>10.839584155187378</v>
@@ -2194,11 +2194,11 @@
       </c>
       <c r="F47">
         <f t="shared" si="2"/>
-        <v>35311.433949167949</v>
+        <v>3531143.3949167952</v>
       </c>
       <c r="G47">
         <f t="shared" si="3"/>
-        <v>10.471962098382987</v>
+        <v>15.077132284371078</v>
       </c>
       <c r="H47">
         <v>10.830423050220965</v>
@@ -2224,11 +2224,11 @@
       </c>
       <c r="F48">
         <f t="shared" si="2"/>
-        <v>34461.811661340449</v>
+        <v>3446181.1661340441</v>
       </c>
       <c r="G48">
         <f t="shared" si="3"/>
-        <v>10.447607081576987</v>
+        <v>15.052777267565078</v>
       </c>
       <c r="H48">
         <v>10.817040099576738</v>
@@ -2254,11 +2254,11 @@
       </c>
       <c r="F49">
         <f t="shared" si="2"/>
-        <v>34853.931398699431</v>
+        <v>3485393.1398699423</v>
       </c>
       <c r="G49">
         <f t="shared" si="3"/>
-        <v>10.458921218971087</v>
+        <v>15.064091404959179</v>
       </c>
       <c r="H49">
         <v>10.821590977020024</v>
@@ -2284,11 +2284,11 @@
       </c>
       <c r="F50">
         <f t="shared" si="2"/>
-        <v>34187.249470080591</v>
+        <v>3418724.9470080598</v>
       </c>
       <c r="G50">
         <f t="shared" si="3"/>
-        <v>10.439608031022841</v>
+        <v>15.044778217010933</v>
       </c>
       <c r="H50">
         <v>10.81614980515544</v>
@@ -2314,11 +2314,11 @@
       </c>
       <c r="F51">
         <f t="shared" si="2"/>
-        <v>34864.887181488928</v>
+        <v>3486488.7181488927</v>
       </c>
       <c r="G51">
         <f t="shared" si="3"/>
-        <v>10.459235503782644</v>
+        <v>15.064405689770734</v>
       </c>
       <c r="H51">
         <v>10.833584210055569</v>
@@ -2344,11 +2344,11 @@
       </c>
       <c r="F52">
         <f t="shared" si="2"/>
-        <v>34711.567736035322</v>
+        <v>3471156.773603532</v>
       </c>
       <c r="G52">
         <f t="shared" si="3"/>
-        <v>10.454828274532343</v>
+        <v>15.059998460520433</v>
       </c>
       <c r="H52">
         <v>10.833640268374779</v>
@@ -2374,11 +2374,11 @@
       </c>
       <c r="F53">
         <f t="shared" si="2"/>
-        <v>35016.648695585885</v>
+        <v>3501664.8695585877</v>
       </c>
       <c r="G53">
         <f t="shared" si="3"/>
-        <v>10.463578904389843</v>
+        <v>15.068749090377933</v>
       </c>
       <c r="H53">
         <v>10.834417255655621</v>
@@ -2404,11 +2404,11 @@
       </c>
       <c r="F54">
         <f t="shared" si="2"/>
-        <v>34994.937410543171</v>
+        <v>3499493.7410543174</v>
       </c>
       <c r="G54">
         <f t="shared" si="3"/>
-        <v>10.462958684596343</v>
+        <v>15.068128870584433</v>
       </c>
       <c r="H54">
         <v>10.841459794326221</v>
@@ -2434,11 +2434,11 @@
       </c>
       <c r="F55">
         <f t="shared" si="2"/>
-        <v>34894.321260483754</v>
+        <v>3489432.1260483754</v>
       </c>
       <c r="G55">
         <f t="shared" si="3"/>
-        <v>10.460079380351743</v>
+        <v>15.065249566339833</v>
       </c>
       <c r="H55">
         <v>10.834374868494265</v>
@@ -2464,11 +2464,11 @@
       </c>
       <c r="F56">
         <f t="shared" si="2"/>
-        <v>35738.633818226066</v>
+        <v>3573863.3818226065</v>
       </c>
       <c r="G56">
         <f t="shared" si="3"/>
-        <v>10.483987562415543</v>
+        <v>15.089157748403633</v>
       </c>
       <c r="H56">
         <v>10.854577588686901</v>
@@ -2494,11 +2494,11 @@
       </c>
       <c r="F57">
         <f t="shared" si="2"/>
-        <v>34891.882706598612</v>
+        <v>3489188.2706598612</v>
       </c>
       <c r="G57">
         <f t="shared" si="3"/>
-        <v>10.460009493934441</v>
+        <v>15.065179679922533</v>
       </c>
       <c r="H57">
         <v>10.838387105995356</v>
@@ -2524,11 +2524,11 @@
       </c>
       <c r="F58">
         <f t="shared" si="2"/>
-        <v>35351.27515628979</v>
+        <v>3535127.5156289791</v>
       </c>
       <c r="G58">
         <f t="shared" si="3"/>
-        <v>10.473089742987842</v>
+        <v>15.078259928975934</v>
       </c>
       <c r="H58">
         <v>10.841886416758975</v>
@@ -2554,11 +2554,11 @@
       </c>
       <c r="F59">
         <f t="shared" si="2"/>
-        <v>35442.379814050299</v>
+        <v>3544237.98140503</v>
       </c>
       <c r="G59">
         <f t="shared" si="3"/>
-        <v>10.475663552973844</v>
+        <v>15.080833738961934</v>
       </c>
       <c r="H59">
         <v>10.844436789663195</v>
@@ -2584,11 +2584,11 @@
       </c>
       <c r="F60">
         <f t="shared" si="2"/>
-        <v>35393.78387391357</v>
+        <v>3539378.3873913568</v>
       </c>
       <c r="G60">
         <f t="shared" si="3"/>
-        <v>10.474291486920844</v>
+        <v>15.079461672908934</v>
       </c>
       <c r="H60">
         <v>10.852347466077704</v>
@@ -2614,11 +2614,11 @@
       </c>
       <c r="F61">
         <f t="shared" si="2"/>
-        <v>35965.472120745915</v>
+        <v>3596547.2120745918</v>
       </c>
       <c r="G61">
         <f t="shared" si="3"/>
-        <v>10.490314649443041</v>
+        <v>15.095484835431133</v>
       </c>
       <c r="H61">
         <v>10.861009980720585</v>
@@ -2644,11 +2644,11 @@
       </c>
       <c r="F62">
         <f t="shared" si="2"/>
-        <v>35103.811783809455</v>
+        <v>3510381.1783809452</v>
       </c>
       <c r="G62">
         <f t="shared" si="3"/>
-        <v>10.466065001386969</v>
+        <v>15.071235187375061</v>
       </c>
       <c r="H62">
         <v>10.860333865131429</v>
@@ -2674,11 +2674,11 @@
       </c>
       <c r="F63">
         <f t="shared" si="2"/>
-        <v>35658.179323575605</v>
+        <v>3565817.9323575604</v>
       </c>
       <c r="G63">
         <f t="shared" si="3"/>
-        <v>10.481733833567869</v>
+        <v>15.086904019555961</v>
       </c>
       <c r="H63">
         <v>10.868608399249467</v>
@@ -2704,11 +2704,11 @@
       </c>
       <c r="F64">
         <f t="shared" si="2"/>
-        <v>35865.257155713247</v>
+        <v>3586525.7155713243</v>
       </c>
       <c r="G64">
         <f t="shared" si="3"/>
-        <v>10.48752433863697</v>
+        <v>15.092694524625061</v>
       </c>
       <c r="H64">
         <v>10.868566455913616</v>
@@ -2734,11 +2734,11 @@
       </c>
       <c r="F65">
         <f t="shared" si="2"/>
-        <v>36124.012872330175</v>
+        <v>3612401.2872330179</v>
       </c>
       <c r="G65">
         <f t="shared" si="3"/>
-        <v>10.494713099707969</v>
+        <v>15.099883285696061</v>
       </c>
       <c r="H65">
         <v>10.876618527072992</v>
@@ -2764,11 +2764,11 @@
       </c>
       <c r="F66">
         <f t="shared" si="2"/>
-        <v>36053.108659718506</v>
+        <v>3605310.8659718507</v>
       </c>
       <c r="G66">
         <f t="shared" si="3"/>
-        <v>10.49274837088767</v>
+        <v>15.097918556875761</v>
       </c>
       <c r="H66">
         <v>10.877461236046104</v>
@@ -2793,12 +2793,12 @@
         <v>44086292</v>
       </c>
       <c r="F67">
-        <f t="shared" ref="F67:F130" si="6">D67*10000000/E67</f>
-        <v>36186.533397054016</v>
+        <f t="shared" ref="F67:F130" si="6">D67*1000000000/E67</f>
+        <v>3618653.3397054016</v>
       </c>
       <c r="G67">
         <f t="shared" ref="G67:G130" si="7">LN(F67)</f>
-        <v>10.496442322996369</v>
+        <v>15.101612508984461</v>
       </c>
       <c r="H67">
         <v>10.878114822387875</v>
@@ -2824,11 +2824,11 @@
       </c>
       <c r="F68">
         <f t="shared" si="6"/>
-        <v>36231.633449692781</v>
+        <v>3623163.3449692787</v>
       </c>
       <c r="G68">
         <f t="shared" si="7"/>
-        <v>10.49768786842877</v>
+        <v>15.102858054416862</v>
       </c>
       <c r="H68">
         <v>10.879100072900387</v>
@@ -2854,11 +2854,11 @@
       </c>
       <c r="F69">
         <f t="shared" si="6"/>
-        <v>36232.751367184857</v>
+        <v>3623275.136718486</v>
       </c>
       <c r="G69">
         <f t="shared" si="7"/>
-        <v>10.497718722688969</v>
+        <v>15.102888908677061</v>
       </c>
       <c r="H69">
         <v>10.887938912177946</v>
@@ -2884,11 +2884,11 @@
       </c>
       <c r="F70">
         <f t="shared" si="6"/>
-        <v>36703.961187194836</v>
+        <v>3670396.1187194833</v>
       </c>
       <c r="G70">
         <f t="shared" si="7"/>
-        <v>10.510639962474169</v>
+        <v>15.115810148462261</v>
       </c>
       <c r="H70">
         <v>10.893440745274395</v>
@@ -2914,11 +2914,11 @@
       </c>
       <c r="F71">
         <f t="shared" si="6"/>
-        <v>36921.448190686977</v>
+        <v>3692144.8190686977</v>
       </c>
       <c r="G71">
         <f t="shared" si="7"/>
-        <v>10.516547912947368</v>
+        <v>15.12171809893546</v>
       </c>
       <c r="H71">
         <v>10.906388962479243</v>
@@ -2944,11 +2944,11 @@
       </c>
       <c r="F72">
         <f t="shared" si="6"/>
-        <v>36911.988345197853</v>
+        <v>3691198.8345197844</v>
       </c>
       <c r="G72">
         <f t="shared" si="7"/>
-        <v>10.51629166466787</v>
+        <v>15.121461850655962</v>
       </c>
       <c r="H72">
         <v>10.902345496187481</v>
@@ -2974,11 +2974,11 @@
       </c>
       <c r="F73">
         <f t="shared" si="6"/>
-        <v>37630.674801855486</v>
+        <v>3763067.4801855478</v>
       </c>
       <c r="G73">
         <f t="shared" si="7"/>
-        <v>10.53557481597667</v>
+        <v>15.140745001964762</v>
       </c>
       <c r="H73">
         <v>10.914190320847265</v>
@@ -3004,11 +3004,11 @@
       </c>
       <c r="F74">
         <f t="shared" si="6"/>
-        <v>37366.896442504956</v>
+        <v>3736689.6442504958</v>
       </c>
       <c r="G74">
         <f t="shared" si="7"/>
-        <v>10.528540469592814</v>
+        <v>15.133710655580906</v>
       </c>
       <c r="H74">
         <v>10.924858690307637</v>
@@ -3034,11 +3034,11 @@
       </c>
       <c r="F75">
         <f t="shared" si="6"/>
-        <v>37421.743268635677</v>
+        <v>3742174.3268635683</v>
       </c>
       <c r="G75">
         <f t="shared" si="7"/>
-        <v>10.530007185291215</v>
+        <v>15.135177371279307</v>
       </c>
       <c r="H75">
         <v>10.921351431837401</v>
@@ -3064,11 +3064,11 @@
       </c>
       <c r="F76">
         <f t="shared" si="6"/>
-        <v>37812.422209301723</v>
+        <v>3781242.2209301721</v>
       </c>
       <c r="G76">
         <f t="shared" si="7"/>
-        <v>10.540392957496415</v>
+        <v>15.145563143484507</v>
       </c>
       <c r="H76">
         <v>10.93315772847955</v>
@@ -3094,11 +3094,11 @@
       </c>
       <c r="F77">
         <f t="shared" si="6"/>
-        <v>37939.02670902379</v>
+        <v>3793902.6709023789</v>
       </c>
       <c r="G77">
         <f t="shared" si="7"/>
-        <v>10.543735589734114</v>
+        <v>15.148905775722206</v>
       </c>
       <c r="H77">
         <v>10.937749639142789</v>
@@ -3124,11 +3124,11 @@
       </c>
       <c r="F78">
         <f t="shared" si="6"/>
-        <v>38128.654814785019</v>
+        <v>3812865.481478502</v>
       </c>
       <c r="G78">
         <f t="shared" si="7"/>
-        <v>10.548721373309414</v>
+        <v>15.153891559297506</v>
       </c>
       <c r="H78">
         <v>10.944651145596785</v>
@@ -3154,11 +3154,11 @@
       </c>
       <c r="F79">
         <f t="shared" si="6"/>
-        <v>38274.666963441116</v>
+        <v>3827466.696344112</v>
       </c>
       <c r="G79">
         <f t="shared" si="7"/>
-        <v>10.552543519336915</v>
+        <v>15.157713705325007</v>
       </c>
       <c r="H79">
         <v>10.951195878047892</v>
@@ -3184,11 +3184,11 @@
       </c>
       <c r="F80">
         <f t="shared" si="6"/>
-        <v>38476.924440017996</v>
+        <v>3847692.4440017994</v>
       </c>
       <c r="G80">
         <f t="shared" si="7"/>
-        <v>10.557813975390415</v>
+        <v>15.162984161378507</v>
       </c>
       <c r="H80">
         <v>10.959292057535347</v>
@@ -3214,11 +3214,11 @@
       </c>
       <c r="F81">
         <f t="shared" si="6"/>
-        <v>39216.049159715098</v>
+        <v>3921604.9159715096</v>
       </c>
       <c r="G81">
         <f t="shared" si="7"/>
-        <v>10.576841359329814</v>
+        <v>15.182011545317906</v>
       </c>
       <c r="H81">
         <v>10.967610004566355</v>
@@ -3244,11 +3244,11 @@
       </c>
       <c r="F82">
         <f t="shared" si="6"/>
-        <v>38971.870968406671</v>
+        <v>3897187.0968406666</v>
       </c>
       <c r="G82">
         <f t="shared" si="7"/>
-        <v>10.570595407660317</v>
+        <v>15.175765593648407</v>
       </c>
       <c r="H82">
         <v>10.962387303142336</v>
@@ -3274,11 +3274,11 @@
       </c>
       <c r="F83">
         <f t="shared" si="6"/>
-        <v>39025.600669780906</v>
+        <v>3902560.0669780909</v>
       </c>
       <c r="G83">
         <f t="shared" si="7"/>
-        <v>10.571973137187815</v>
+        <v>15.177143323175907</v>
       </c>
       <c r="H83">
         <v>10.972701800164629</v>
@@ -3304,11 +3304,11 @@
       </c>
       <c r="F84">
         <f t="shared" si="6"/>
-        <v>39155.957250798412</v>
+        <v>3915595.725079841</v>
       </c>
       <c r="G84">
         <f t="shared" si="7"/>
-        <v>10.575307854614417</v>
+        <v>15.180478040602507</v>
       </c>
       <c r="H84">
         <v>10.975277589897884</v>
@@ -3334,11 +3334,11 @@
       </c>
       <c r="F85">
         <f t="shared" si="6"/>
-        <v>39209.992365493737</v>
+        <v>3920999.2365493737</v>
       </c>
       <c r="G85">
         <f t="shared" si="7"/>
-        <v>10.576686900578215</v>
+        <v>15.181857086566307</v>
       </c>
       <c r="H85">
         <v>10.968494742083706</v>
@@ -3364,11 +3364,11 @@
       </c>
       <c r="F86">
         <f t="shared" si="6"/>
-        <v>39200.699403174011</v>
+        <v>3920069.9403174017</v>
       </c>
       <c r="G86">
         <f t="shared" si="7"/>
-        <v>10.576449867537093</v>
+        <v>15.181620053525185</v>
       </c>
       <c r="H86">
         <v>10.979552210191965</v>
@@ -3394,11 +3394,11 @@
       </c>
       <c r="F87">
         <f t="shared" si="6"/>
-        <v>39331.960424655015</v>
+        <v>3933196.0424655015</v>
       </c>
       <c r="G87">
         <f t="shared" si="7"/>
-        <v>10.579792709712594</v>
+        <v>15.184962895700686</v>
       </c>
       <c r="H87">
         <v>10.973910801712357</v>
@@ -3424,11 +3424,11 @@
       </c>
       <c r="F88">
         <f t="shared" si="6"/>
-        <v>39643.164289093707</v>
+        <v>3964316.4289093707</v>
       </c>
       <c r="G88">
         <f t="shared" si="7"/>
-        <v>10.587673810916293</v>
+        <v>15.192843996904385</v>
       </c>
       <c r="H88">
         <v>10.988345695387277</v>
@@ -3454,11 +3454,11 @@
       </c>
       <c r="F89">
         <f t="shared" si="6"/>
-        <v>39299.717985384588</v>
+        <v>3929971.7985384581</v>
       </c>
       <c r="G89">
         <f t="shared" si="7"/>
-        <v>10.578972621887193</v>
+        <v>15.184142807875284</v>
       </c>
       <c r="H89">
         <v>10.984533862934741</v>
@@ -3484,11 +3484,11 @@
       </c>
       <c r="F90">
         <f t="shared" si="6"/>
-        <v>39627.051981433746</v>
+        <v>3962705.1981433751</v>
       </c>
       <c r="G90">
         <f t="shared" si="7"/>
-        <v>10.587267294859194</v>
+        <v>15.192437480847286</v>
       </c>
       <c r="H90">
         <v>10.989823326276612</v>
@@ -3514,11 +3514,11 @@
       </c>
       <c r="F91">
         <f t="shared" si="6"/>
-        <v>39653.712776062122</v>
+        <v>3965371.2776062121</v>
       </c>
       <c r="G91">
         <f t="shared" si="7"/>
-        <v>10.587939861419693</v>
+        <v>15.193110047407785</v>
       </c>
       <c r="H91">
         <v>10.997517205452656</v>
@@ -3544,11 +3544,11 @@
       </c>
       <c r="F92">
         <f t="shared" si="6"/>
-        <v>39434.245883085154</v>
+        <v>3943424.5883085155</v>
       </c>
       <c r="G92">
         <f t="shared" si="7"/>
-        <v>10.582389902613492</v>
+        <v>15.187560088601584</v>
       </c>
       <c r="H92">
         <v>10.994454823859426</v>
@@ -3574,11 +3574,11 @@
       </c>
       <c r="F93">
         <f t="shared" si="6"/>
-        <v>38878.014877852809</v>
+        <v>3887801.4877852811</v>
       </c>
       <c r="G93">
         <f t="shared" si="7"/>
-        <v>10.568184199602493</v>
+        <v>15.173354385590585</v>
       </c>
       <c r="H93">
         <v>10.974860948251314</v>
@@ -3604,11 +3604,11 @@
       </c>
       <c r="F94">
         <f t="shared" si="6"/>
-        <v>39701.142156635462</v>
+        <v>3970114.2156635458</v>
       </c>
       <c r="G94">
         <f t="shared" si="7"/>
-        <v>10.589135235949993</v>
+        <v>15.194305421938084</v>
       </c>
       <c r="H94">
         <v>10.999405773833885</v>
@@ -3634,11 +3634,11 @@
       </c>
       <c r="F95">
         <f t="shared" si="6"/>
-        <v>39738.012183790255</v>
+        <v>3973801.2183790253</v>
       </c>
       <c r="G95">
         <f t="shared" si="7"/>
-        <v>10.590063494315993</v>
+        <v>15.195233680304085</v>
       </c>
       <c r="H95">
         <v>10.993417009428375</v>
@@ -3664,11 +3664,11 @@
       </c>
       <c r="F96">
         <f t="shared" si="6"/>
-        <v>39980.931294316048</v>
+        <v>3998093.1294316049</v>
       </c>
       <c r="G96">
         <f t="shared" si="7"/>
-        <v>10.596157901787993</v>
+        <v>15.201328087776085</v>
       </c>
       <c r="H96">
         <v>11.002252604382271</v>
@@ -3694,11 +3694,11 @@
       </c>
       <c r="F97">
         <f t="shared" si="6"/>
-        <v>39778.668174132421</v>
+        <v>3977866.8174132416</v>
       </c>
       <c r="G97">
         <f t="shared" si="7"/>
-        <v>10.591086072061993</v>
+        <v>15.196256258050084</v>
       </c>
       <c r="H97">
         <v>11.002623382476669</v>
@@ -3724,11 +3724,11 @@
       </c>
       <c r="F98">
         <f t="shared" si="6"/>
-        <v>40163.558206817645</v>
+        <v>4016355.8206817647</v>
       </c>
       <c r="G98">
         <f t="shared" si="7"/>
-        <v>10.600715351208166</v>
+        <v>15.205885537196258</v>
       </c>
       <c r="H98">
         <v>11.019389859393355</v>
@@ -3754,11 +3754,11 @@
       </c>
       <c r="F99">
         <f t="shared" si="6"/>
-        <v>39842.137275757341</v>
+        <v>3984213.7275757343</v>
       </c>
       <c r="G99">
         <f t="shared" si="7"/>
-        <v>10.592680356739466</v>
+        <v>15.197850542727558</v>
       </c>
       <c r="H99">
         <v>11.01166521977866</v>
@@ -3784,11 +3784,11 @@
       </c>
       <c r="F100">
         <f t="shared" si="6"/>
-        <v>39818.344064923316</v>
+        <v>3981834.4064923315</v>
       </c>
       <c r="G100">
         <f t="shared" si="7"/>
-        <v>10.592082991241766</v>
+        <v>15.197253177229857</v>
       </c>
       <c r="H100">
         <v>11.016248958229484</v>
@@ -3814,11 +3814,11 @@
       </c>
       <c r="F101">
         <f t="shared" si="6"/>
-        <v>41089.171450150308</v>
+        <v>4108917.1450150306</v>
       </c>
       <c r="G101">
         <f t="shared" si="7"/>
-        <v>10.623499897404265</v>
+        <v>15.228670083392357</v>
       </c>
       <c r="H101">
         <v>11.031004997206857</v>
@@ -3844,11 +3844,11 @@
       </c>
       <c r="F102">
         <f t="shared" si="6"/>
-        <v>41540.649499596169</v>
+        <v>4154064.9499596166</v>
       </c>
       <c r="G102">
         <f t="shared" si="7"/>
-        <v>10.634427732830165</v>
+        <v>15.239597918818257</v>
       </c>
       <c r="H102">
         <v>11.040203066299023</v>
@@ -3874,11 +3874,11 @@
       </c>
       <c r="F103">
         <f t="shared" si="6"/>
-        <v>41225.257720012996</v>
+        <v>4122525.7720013</v>
       </c>
       <c r="G103">
         <f t="shared" si="7"/>
-        <v>10.626806398954965</v>
+        <v>15.231976584943057</v>
       </c>
       <c r="H103">
         <v>11.045268674075816</v>
@@ -3904,11 +3904,11 @@
       </c>
       <c r="F104">
         <f t="shared" si="6"/>
-        <v>41751.504382974665</v>
+        <v>4175150.4382974664</v>
       </c>
       <c r="G104">
         <f t="shared" si="7"/>
-        <v>10.639490762754965</v>
+        <v>15.244660948743057</v>
       </c>
       <c r="H104">
         <v>11.05054020597824</v>
@@ -3934,11 +3934,11 @@
       </c>
       <c r="F105">
         <f t="shared" si="6"/>
-        <v>40929.921688375092</v>
+        <v>4092992.16883751</v>
       </c>
       <c r="G105">
         <f t="shared" si="7"/>
-        <v>10.619616656178366</v>
+        <v>15.224786842166457</v>
       </c>
       <c r="H105">
         <v>11.037048989846921</v>
@@ -3964,11 +3964,11 @@
       </c>
       <c r="F106">
         <f t="shared" si="6"/>
-        <v>41513.608173168177</v>
+        <v>4151360.8173168171</v>
       </c>
       <c r="G106">
         <f t="shared" si="7"/>
-        <v>10.633776560255965</v>
+        <v>15.238946746244057</v>
       </c>
       <c r="H106">
         <v>11.052330062593208</v>
@@ -3994,11 +3994,11 @@
       </c>
       <c r="F107">
         <f t="shared" si="6"/>
-        <v>41764.345094691736</v>
+        <v>4176434.5094691738</v>
       </c>
       <c r="G107">
         <f t="shared" si="7"/>
-        <v>10.639798266346165</v>
+        <v>15.244968452334257</v>
       </c>
       <c r="H107">
         <v>11.051950768359012</v>
@@ -4024,11 +4024,11 @@
       </c>
       <c r="F108">
         <f t="shared" si="6"/>
-        <v>41965.82984674826</v>
+        <v>4196582.9846748253</v>
       </c>
       <c r="G108">
         <f t="shared" si="7"/>
-        <v>10.644610991056267</v>
+        <v>15.249781177044358</v>
       </c>
       <c r="H108">
         <v>11.060414666299168</v>
@@ -4054,11 +4054,11 @@
       </c>
       <c r="F109">
         <f t="shared" si="6"/>
-        <v>42256.408923856834</v>
+        <v>4225640.892385684</v>
       </c>
       <c r="G109">
         <f t="shared" si="7"/>
-        <v>10.651511311786965</v>
+        <v>15.256681497775057</v>
       </c>
       <c r="H109">
         <v>11.064316661288125</v>
@@ -4084,11 +4084,11 @@
       </c>
       <c r="F110">
         <f t="shared" si="6"/>
-        <v>41928.426507884113</v>
+        <v>4192842.6507884106</v>
       </c>
       <c r="G110">
         <f t="shared" si="7"/>
-        <v>10.643719312818265</v>
+        <v>15.248889498806356</v>
       </c>
       <c r="H110">
         <v>11.063337771525445</v>
@@ -4114,11 +4114,11 @@
       </c>
       <c r="F111">
         <f t="shared" si="6"/>
-        <v>42559.114118701742</v>
+        <v>4255911.4118701741</v>
       </c>
       <c r="G111">
         <f t="shared" si="7"/>
-        <v>10.658649308918765</v>
+        <v>15.263819494906857</v>
       </c>
       <c r="H111">
         <v>11.07783545993599</v>
@@ -4144,11 +4144,11 @@
       </c>
       <c r="F112">
         <f t="shared" si="6"/>
-        <v>42113.876255861258</v>
+        <v>4211387.625586126</v>
       </c>
       <c r="G112">
         <f t="shared" si="7"/>
-        <v>10.648132567640564</v>
+        <v>15.253302753628656</v>
       </c>
       <c r="H112">
         <v>11.074631423616927</v>
@@ -4174,11 +4174,11 @@
       </c>
       <c r="F113">
         <f t="shared" si="6"/>
-        <v>42393.388219740897</v>
+        <v>4239338.8219740894</v>
       </c>
       <c r="G113">
         <f t="shared" si="7"/>
-        <v>10.654747690846763</v>
+        <v>15.259917876834855</v>
       </c>
       <c r="H113">
         <v>11.075323820440696</v>
@@ -4204,11 +4204,11 @@
       </c>
       <c r="F114">
         <f t="shared" si="6"/>
-        <v>42359.210521184672</v>
+        <v>4235921.0521184672</v>
       </c>
       <c r="G114">
         <f t="shared" si="7"/>
-        <v>10.653941162175864</v>
+        <v>15.259111348163955</v>
       </c>
       <c r="H114">
         <v>11.077151113506034</v>
@@ -4234,11 +4234,11 @@
       </c>
       <c r="F115">
         <f t="shared" si="6"/>
-        <v>42162.466986141255</v>
+        <v>4216246.6986141251</v>
       </c>
       <c r="G115">
         <f t="shared" si="7"/>
-        <v>10.649285696354864</v>
+        <v>15.254455882342956</v>
       </c>
       <c r="H115">
         <v>11.084533792399172</v>
@@ -4264,11 +4264,11 @@
       </c>
       <c r="F116">
         <f t="shared" si="6"/>
-        <v>42670.798230975335</v>
+        <v>4267079.8230975335</v>
       </c>
       <c r="G116">
         <f t="shared" si="7"/>
-        <v>10.661270083084064</v>
+        <v>15.266440269072156</v>
       </c>
       <c r="H116">
         <v>11.079152552671365</v>
@@ -4294,11 +4294,11 @@
       </c>
       <c r="F117">
         <f t="shared" si="6"/>
-        <v>42381.822120900702</v>
+        <v>4238182.2120900704</v>
       </c>
       <c r="G117">
         <f t="shared" si="7"/>
-        <v>10.654474825728164</v>
+        <v>15.259645011716255</v>
       </c>
       <c r="H117">
         <v>11.088302441378708</v>
@@ -4324,11 +4324,11 @@
       </c>
       <c r="F118">
         <f t="shared" si="6"/>
-        <v>43148.943444356526</v>
+        <v>4314894.3444356527</v>
       </c>
       <c r="G118">
         <f t="shared" si="7"/>
-        <v>10.672413210565365</v>
+        <v>15.277583396553457</v>
       </c>
       <c r="H118">
         <v>11.094596029882236</v>
@@ -4354,11 +4354,11 @@
       </c>
       <c r="F119">
         <f t="shared" si="6"/>
-        <v>43324.780932450951</v>
+        <v>4332478.0932450956</v>
       </c>
       <c r="G119">
         <f t="shared" si="7"/>
-        <v>10.676480058193665</v>
+        <v>15.281650244181757</v>
       </c>
       <c r="H119">
         <v>11.096499428232512</v>
@@ -4384,11 +4384,11 @@
       </c>
       <c r="F120">
         <f t="shared" si="6"/>
-        <v>42805.613084956261</v>
+        <v>4280561.3084956268</v>
       </c>
       <c r="G120">
         <f t="shared" si="7"/>
-        <v>10.664424519815665</v>
+        <v>15.269594705803756</v>
       </c>
       <c r="H120">
         <v>11.095717053636424</v>
@@ -4414,11 +4414,11 @@
       </c>
       <c r="F121">
         <f t="shared" si="6"/>
-        <v>43381.312134157299</v>
+        <v>4338131.2134157298</v>
       </c>
       <c r="G121">
         <f t="shared" si="7"/>
-        <v>10.677784031368263</v>
+        <v>15.282954217356355</v>
       </c>
       <c r="H121">
         <v>11.102321825985925</v>
@@ -4444,11 +4444,11 @@
       </c>
       <c r="F122">
         <f t="shared" si="6"/>
-        <v>42918.556946176934</v>
+        <v>4291855.6946176933</v>
       </c>
       <c r="G122">
         <f t="shared" si="7"/>
-        <v>10.667059574235717</v>
+        <v>15.272229760223809</v>
       </c>
       <c r="H122">
         <v>11.105052379495454</v>
@@ -4474,11 +4474,11 @@
       </c>
       <c r="F123">
         <f t="shared" si="6"/>
-        <v>43153.826351652038</v>
+        <v>4315382.6351652043</v>
       </c>
       <c r="G123">
         <f t="shared" si="7"/>
-        <v>10.672526368168818</v>
+        <v>15.277696554156909</v>
       </c>
       <c r="H123">
         <v>11.107782920554685</v>
@@ -4504,11 +4504,11 @@
       </c>
       <c r="F124">
         <f t="shared" si="6"/>
-        <v>42944.209556051384</v>
+        <v>4294420.9556051381</v>
       </c>
       <c r="G124">
         <f t="shared" si="7"/>
-        <v>10.667657100071017</v>
+        <v>15.272827286059108</v>
       </c>
       <c r="H124">
         <v>11.103408467828537</v>
@@ -4534,11 +4534,11 @@
       </c>
       <c r="F125">
         <f t="shared" si="6"/>
-        <v>43416.402948000788</v>
+        <v>4341640.2948000785</v>
       </c>
       <c r="G125">
         <f t="shared" si="7"/>
-        <v>10.678592596794717</v>
+        <v>15.283762782782809</v>
       </c>
       <c r="H125">
         <v>11.109796792084504</v>
@@ -4564,11 +4564,11 @@
       </c>
       <c r="F126">
         <f t="shared" si="6"/>
-        <v>43346.605019336297</v>
+        <v>4334660.5019336296</v>
       </c>
       <c r="G126">
         <f t="shared" si="7"/>
-        <v>10.676983663555617</v>
+        <v>15.282153849543709</v>
       </c>
       <c r="H126">
         <v>11.110735578519938</v>
@@ -4594,11 +4594,11 @@
       </c>
       <c r="F127">
         <f t="shared" si="6"/>
-        <v>43251.072603144647</v>
+        <v>4325107.2603144646</v>
       </c>
       <c r="G127">
         <f t="shared" si="7"/>
-        <v>10.674777312125217</v>
+        <v>15.279947498113309</v>
       </c>
       <c r="H127">
         <v>11.108600657101643</v>
@@ -4624,11 +4624,11 @@
       </c>
       <c r="F128">
         <f t="shared" si="6"/>
-        <v>44031.943689580803</v>
+        <v>4403194.3689580802</v>
       </c>
       <c r="G128">
         <f t="shared" si="7"/>
-        <v>10.692670642440017</v>
+        <v>15.297840828428109</v>
       </c>
       <c r="H128">
         <v>11.12152694385682</v>
@@ -4654,11 +4654,11 @@
       </c>
       <c r="F129">
         <f t="shared" si="6"/>
-        <v>43396.666724331473</v>
+        <v>4339666.6724331472</v>
       </c>
       <c r="G129">
         <f t="shared" si="7"/>
-        <v>10.678137913552117</v>
+        <v>15.283308099540209</v>
       </c>
       <c r="H129">
         <v>11.122736849857557</v>
@@ -4684,11 +4684,11 @@
       </c>
       <c r="F130">
         <f t="shared" si="6"/>
-        <v>43885.987048699237</v>
+        <v>4388598.7048699241</v>
       </c>
       <c r="G130">
         <f t="shared" si="7"/>
-        <v>10.689350346483417</v>
+        <v>15.294520532471509</v>
       </c>
       <c r="H130">
         <v>11.122044224868148</v>
@@ -4713,12 +4713,12 @@
         <v>46313898</v>
       </c>
       <c r="F131">
-        <f t="shared" ref="F131:F194" si="10">D131*10000000/E131</f>
-        <v>43889.864088752736</v>
+        <f t="shared" ref="F131:F194" si="10">D131*1000000000/E131</f>
+        <v>4388986.4088752735</v>
       </c>
       <c r="G131">
         <f t="shared" ref="G131:G194" si="11">LN(F131)</f>
-        <v>10.689438686043918</v>
+        <v>15.294608872032009</v>
       </c>
       <c r="H131">
         <v>11.119438933366174</v>
@@ -4744,11 +4744,11 @@
       </c>
       <c r="F132">
         <f t="shared" si="10"/>
-        <v>43364.52204038894</v>
+        <v>4336452.2040388938</v>
       </c>
       <c r="G132">
         <f t="shared" si="11"/>
-        <v>10.677396921275017</v>
+        <v>15.282567107263109</v>
       </c>
       <c r="H132">
         <v>11.11436590589374</v>
@@ -4774,11 +4774,11 @@
       </c>
       <c r="F133">
         <f t="shared" si="10"/>
-        <v>43647.24986988755</v>
+        <v>4364724.9869887549</v>
       </c>
       <c r="G133">
         <f t="shared" si="11"/>
-        <v>10.683895555156617</v>
+        <v>15.289065741144709</v>
       </c>
       <c r="H133">
         <v>11.113954127832017</v>
@@ -4804,11 +4804,11 @@
       </c>
       <c r="F134">
         <f t="shared" si="10"/>
-        <v>43214.878548933222</v>
+        <v>4321487.8548933221</v>
       </c>
       <c r="G134">
         <f t="shared" si="11"/>
-        <v>10.673940125791333</v>
+        <v>15.279110311779425</v>
       </c>
       <c r="H134">
         <v>11.122558951759261</v>
@@ -4834,11 +4834,11 @@
       </c>
       <c r="F135">
         <f t="shared" si="10"/>
-        <v>43954.19514571796</v>
+        <v>4395419.5145717962</v>
       </c>
       <c r="G135">
         <f t="shared" si="11"/>
-        <v>10.690903351247833</v>
+        <v>15.296073537235925</v>
       </c>
       <c r="H135">
         <v>11.126803667748604</v>
@@ -4864,11 +4864,11 @@
       </c>
       <c r="F136">
         <f t="shared" si="10"/>
-        <v>43622.488220161969</v>
+        <v>4362248.8220161963</v>
       </c>
       <c r="G136">
         <f t="shared" si="11"/>
-        <v>10.683328081231933</v>
+        <v>15.288498267220024</v>
       </c>
       <c r="H136">
         <v>11.128483078893526</v>
@@ -4894,11 +4894,11 @@
       </c>
       <c r="F137">
         <f t="shared" si="10"/>
-        <v>43625.498588882358</v>
+        <v>4362549.8588882349</v>
       </c>
       <c r="G137">
         <f t="shared" si="11"/>
-        <v>10.683397088410933</v>
+        <v>15.288567274399025</v>
       </c>
       <c r="H137">
         <v>11.12326766424288</v>
@@ -4924,11 +4924,11 @@
       </c>
       <c r="F138">
         <f t="shared" si="10"/>
-        <v>43837.758814177039</v>
+        <v>4383775.8814177038</v>
       </c>
       <c r="G138">
         <f t="shared" si="11"/>
-        <v>10.688250798375734</v>
+        <v>15.293420984363825</v>
       </c>
       <c r="H138">
         <v>11.133602366006153</v>
@@ -4954,11 +4954,11 @@
       </c>
       <c r="F139">
         <f t="shared" si="10"/>
-        <v>43846.514225102983</v>
+        <v>4384651.422510298</v>
       </c>
       <c r="G139">
         <f t="shared" si="11"/>
-        <v>10.688450501484434</v>
+        <v>15.293620687472526</v>
       </c>
       <c r="H139">
         <v>11.136869480529329</v>
@@ -4984,11 +4984,11 @@
       </c>
       <c r="F140">
         <f t="shared" si="10"/>
-        <v>42843.108598774968</v>
+        <v>4284310.859877496</v>
       </c>
       <c r="G140">
         <f t="shared" si="11"/>
-        <v>10.665300084925732</v>
+        <v>15.270470270913824</v>
       </c>
       <c r="H140">
         <v>11.117038566943004</v>
@@ -5014,11 +5014,11 @@
       </c>
       <c r="F141">
         <f t="shared" si="10"/>
-        <v>44356.853857608956</v>
+        <v>4435685.3857608959</v>
       </c>
       <c r="G141">
         <f t="shared" si="11"/>
-        <v>10.700022515991733</v>
+        <v>15.305192701979825</v>
       </c>
       <c r="H141">
         <v>11.146208835066556</v>
@@ -5044,11 +5044,11 @@
       </c>
       <c r="F142">
         <f t="shared" si="10"/>
-        <v>44477.45307825051</v>
+        <v>4447745.3078250512</v>
       </c>
       <c r="G142">
         <f t="shared" si="11"/>
-        <v>10.702737667353633</v>
+        <v>15.307907853341725</v>
       </c>
       <c r="H142">
         <v>11.14737872559831</v>
@@ -5074,11 +5074,11 @@
       </c>
       <c r="F143">
         <f t="shared" si="10"/>
-        <v>43891.200064780816</v>
+        <v>4389120.0064780815</v>
       </c>
       <c r="G143">
         <f t="shared" si="11"/>
-        <v>10.689469124864432</v>
+        <v>15.294639310852524</v>
       </c>
       <c r="H143">
         <v>11.140953225789751</v>
@@ -5104,11 +5104,11 @@
       </c>
       <c r="F144">
         <f t="shared" si="10"/>
-        <v>44136.649523015025</v>
+        <v>4413664.9523015032</v>
       </c>
       <c r="G144">
         <f t="shared" si="11"/>
-        <v>10.695045771243633</v>
+        <v>15.300215957231725</v>
       </c>
       <c r="H144">
         <v>11.141937516978262</v>
@@ -5134,11 +5134,11 @@
       </c>
       <c r="F145">
         <f t="shared" si="10"/>
-        <v>44474.762932381476</v>
+        <v>4447476.2932381472</v>
       </c>
       <c r="G145">
         <f t="shared" si="11"/>
-        <v>10.702677182163033</v>
+        <v>15.307847368151124</v>
       </c>
       <c r="H145">
         <v>11.141941042970751</v>
@@ -5164,11 +5164,11 @@
       </c>
       <c r="F146">
         <f t="shared" si="10"/>
-        <v>43402.280812622957</v>
+        <v>4340228.0812622961</v>
       </c>
       <c r="G146">
         <f t="shared" si="11"/>
-        <v>10.678267271993864</v>
+        <v>15.283437457981956</v>
       </c>
       <c r="H146">
         <v>11.138104266683857</v>
@@ -5194,11 +5194,11 @@
       </c>
       <c r="F147">
         <f t="shared" si="10"/>
-        <v>43827.831958803516</v>
+        <v>4382783.1958803507</v>
       </c>
       <c r="G147">
         <f t="shared" si="11"/>
-        <v>10.688024327411963</v>
+        <v>15.293194513400055</v>
       </c>
       <c r="H147">
         <v>11.143415298977336</v>
@@ -5224,11 +5224,11 @@
       </c>
       <c r="F148">
         <f t="shared" si="10"/>
-        <v>43456.583562787237</v>
+        <v>4345658.3562787231</v>
       </c>
       <c r="G148">
         <f t="shared" si="11"/>
-        <v>10.679517639647864</v>
+        <v>15.284687825635956</v>
       </c>
       <c r="H148">
         <v>11.135214596479107</v>
@@ -5254,11 +5254,11 @@
       </c>
       <c r="F149">
         <f t="shared" si="10"/>
-        <v>43416.491067530194</v>
+        <v>4341649.1067530196</v>
       </c>
       <c r="G149">
         <f t="shared" si="11"/>
-        <v>10.678594626429463</v>
+        <v>15.283764812417555</v>
       </c>
       <c r="H149">
         <v>11.141083995322287</v>
@@ -5284,11 +5284,11 @@
       </c>
       <c r="F150">
         <f t="shared" si="10"/>
-        <v>43650.478913779792</v>
+        <v>4365047.8913779799</v>
       </c>
       <c r="G150">
         <f t="shared" si="11"/>
-        <v>10.683969532886364</v>
+        <v>15.289139718874456</v>
       </c>
       <c r="H150">
         <v>11.141031822633783</v>
@@ -5314,11 +5314,11 @@
       </c>
       <c r="F151">
         <f t="shared" si="10"/>
-        <v>44232.00494159908</v>
+        <v>4423200.494159908</v>
       </c>
       <c r="G151">
         <f t="shared" si="11"/>
-        <v>10.697203899737763</v>
+        <v>15.302374085725855</v>
       </c>
       <c r="H151">
         <v>11.157301061466677</v>
@@ -5344,11 +5344,11 @@
       </c>
       <c r="F152">
         <f t="shared" si="10"/>
-        <v>43686.487100684993</v>
+        <v>4368648.7100684997</v>
       </c>
       <c r="G152">
         <f t="shared" si="11"/>
-        <v>10.684794113601464</v>
+        <v>15.289964299589556</v>
       </c>
       <c r="H152">
         <v>11.147389021362017</v>
@@ -5374,11 +5374,11 @@
       </c>
       <c r="F153">
         <f t="shared" si="10"/>
-        <v>44187.619293090029</v>
+        <v>4418761.9293090031</v>
       </c>
       <c r="G153">
         <f t="shared" si="11"/>
-        <v>10.696199922337463</v>
+        <v>15.301370108325555</v>
       </c>
       <c r="H153">
         <v>11.152704082174399</v>
@@ -5404,11 +5404,11 @@
       </c>
       <c r="F154">
         <f t="shared" si="10"/>
-        <v>44223.518225807573</v>
+        <v>4422351.8225807576</v>
       </c>
       <c r="G154">
         <f t="shared" si="11"/>
-        <v>10.697012013114664</v>
+        <v>15.302182199102756</v>
       </c>
       <c r="H154">
         <v>11.14966695682512</v>
@@ -5434,11 +5434,11 @@
       </c>
       <c r="F155">
         <f t="shared" si="10"/>
-        <v>43960.27746836</v>
+        <v>4396027.7468360001</v>
       </c>
       <c r="G155">
         <f t="shared" si="11"/>
-        <v>10.691041720334763</v>
+        <v>15.296211906322855</v>
       </c>
       <c r="H155">
         <v>11.147408614533658</v>
@@ -5464,11 +5464,11 @@
       </c>
       <c r="F156">
         <f t="shared" si="10"/>
-        <v>44106.922592185627</v>
+        <v>4410692.2592185624</v>
       </c>
       <c r="G156">
         <f t="shared" si="11"/>
-        <v>10.694372023995163</v>
+        <v>15.299542209983255</v>
       </c>
       <c r="H156">
         <v>11.147446034305824</v>
@@ -5494,11 +5494,11 @@
       </c>
       <c r="F157">
         <f t="shared" si="10"/>
-        <v>44643.812314699593</v>
+        <v>4464381.23146996</v>
       </c>
       <c r="G157">
         <f t="shared" si="11"/>
-        <v>10.706470994723663</v>
+        <v>15.311641180711755</v>
       </c>
       <c r="H157">
         <v>11.168411705682324</v>
@@ -5524,11 +5524,11 @@
       </c>
       <c r="F158">
         <f t="shared" si="10"/>
-        <v>43178.290917433289</v>
+        <v>4317829.0917433286</v>
       </c>
       <c r="G158">
         <f t="shared" si="11"/>
-        <v>10.673093122864753</v>
+        <v>15.278263308852843</v>
       </c>
       <c r="H158">
         <v>11.154061619903645</v>
@@ -5554,11 +5554,11 @@
       </c>
       <c r="F159">
         <f t="shared" si="10"/>
-        <v>43552.414530573289</v>
+        <v>4355241.4530573282</v>
       </c>
       <c r="G159">
         <f t="shared" si="11"/>
-        <v>10.681720423466452</v>
+        <v>15.286890609454542</v>
       </c>
       <c r="H159">
         <v>11.155412949428232</v>
@@ -5584,11 +5584,11 @@
       </c>
       <c r="F160">
         <f t="shared" si="10"/>
-        <v>43967.76810643389</v>
+        <v>4396776.8106433889</v>
       </c>
       <c r="G160">
         <f t="shared" si="11"/>
-        <v>10.691212101424052</v>
+        <v>15.296382287412142</v>
       </c>
       <c r="H160">
         <v>11.174061013689279</v>
@@ -5614,11 +5614,11 @@
       </c>
       <c r="F161">
         <f t="shared" si="10"/>
-        <v>43865.490863592051</v>
+        <v>4386549.0863592047</v>
       </c>
       <c r="G161">
         <f t="shared" si="11"/>
-        <v>10.688883204824553</v>
+        <v>15.294053390812643</v>
       </c>
       <c r="H161">
         <v>11.161625373486585</v>
@@ -5644,11 +5644,11 @@
       </c>
       <c r="F162">
         <f t="shared" si="10"/>
-        <v>44192.161127818399</v>
+        <v>4419216.1127818404</v>
       </c>
       <c r="G162">
         <f t="shared" si="11"/>
-        <v>10.696302702288053</v>
+        <v>15.301472888276145</v>
       </c>
       <c r="H162">
         <v>11.165543861291615</v>
@@ -5674,11 +5674,11 @@
       </c>
       <c r="F163">
         <f t="shared" si="10"/>
-        <v>44441.122874736619</v>
+        <v>4444112.2874736618</v>
       </c>
       <c r="G163">
         <f t="shared" si="11"/>
-        <v>10.701920510642651</v>
+        <v>15.307090696630741</v>
       </c>
       <c r="H163">
         <v>11.175719663844509</v>
@@ -5704,11 +5704,11 @@
       </c>
       <c r="F164">
         <f t="shared" si="10"/>
-        <v>44172.661910348157</v>
+        <v>4417266.1910348153</v>
       </c>
       <c r="G164">
         <f t="shared" si="11"/>
-        <v>10.695861367894652</v>
+        <v>15.301031553882742</v>
       </c>
       <c r="H164">
         <v>11.17397713379491</v>
@@ -5734,11 +5734,11 @@
       </c>
       <c r="F165">
         <f t="shared" si="10"/>
-        <v>44737.494055235358</v>
+        <v>4473749.4055235349</v>
       </c>
       <c r="G165">
         <f t="shared" si="11"/>
-        <v>10.708567222193253</v>
+        <v>15.313737408181343</v>
       </c>
       <c r="H165">
         <v>11.177497208969454</v>
@@ -5764,11 +5764,11 @@
       </c>
       <c r="F166">
         <f t="shared" si="10"/>
-        <v>44547.827116423941</v>
+        <v>4454782.7116423948</v>
       </c>
       <c r="G166">
         <f t="shared" si="11"/>
-        <v>10.704318657667352</v>
+        <v>15.309488843655444</v>
       </c>
       <c r="H166">
         <v>11.181812899817777</v>
@@ -5794,11 +5794,11 @@
       </c>
       <c r="F167">
         <f t="shared" si="10"/>
-        <v>44668.449005973984</v>
+        <v>4466844.9005973982</v>
       </c>
       <c r="G167">
         <f t="shared" si="11"/>
-        <v>10.707022692587651</v>
+        <v>15.312192878575742</v>
       </c>
       <c r="H167">
         <v>11.18014521110385</v>
@@ -5824,11 +5824,11 @@
       </c>
       <c r="F168">
         <f t="shared" si="10"/>
-        <v>44841.223989238679</v>
+        <v>4484122.3989238683</v>
       </c>
       <c r="G168">
         <f t="shared" si="11"/>
-        <v>10.710883173629751</v>
+        <v>15.316053359617843</v>
       </c>
       <c r="H168">
         <v>11.184865420843131</v>
@@ -5854,11 +5854,11 @@
       </c>
       <c r="F169">
         <f t="shared" si="10"/>
-        <v>44738.560580489699</v>
+        <v>4473856.0580489691</v>
       </c>
       <c r="G169">
         <f t="shared" si="11"/>
-        <v>10.708591061537952</v>
+        <v>15.313761247526042</v>
       </c>
       <c r="H169">
         <v>11.188060018270987</v>
@@ -5884,11 +5884,11 @@
       </c>
       <c r="F170">
         <f t="shared" si="10"/>
-        <v>44006.207446972679</v>
+        <v>4400620.7446972672</v>
       </c>
       <c r="G170">
         <f t="shared" si="11"/>
-        <v>10.692085981290074</v>
+        <v>15.297256167278164</v>
       </c>
       <c r="H170">
         <v>11.191648759693285</v>
@@ -5914,11 +5914,11 @@
       </c>
       <c r="F171">
         <f t="shared" si="10"/>
-        <v>44396.354437449227</v>
+        <v>4439635.443744923</v>
       </c>
       <c r="G171">
         <f t="shared" si="11"/>
-        <v>10.700912637784674</v>
+        <v>15.306082823772764</v>
       </c>
       <c r="H171">
         <v>11.190758574223915</v>
@@ -5944,11 +5944,11 @@
       </c>
       <c r="F172">
         <f t="shared" si="10"/>
-        <v>43798.921310349142</v>
+        <v>4379892.1310349135</v>
       </c>
       <c r="G172">
         <f t="shared" si="11"/>
-        <v>10.687364468443674</v>
+        <v>15.292534654431764</v>
       </c>
       <c r="H172">
         <v>11.189419060633849</v>
@@ -5974,11 +5974,11 @@
       </c>
       <c r="F173">
         <f t="shared" si="10"/>
-        <v>44342.877157674775</v>
+        <v>4434287.7157674776</v>
       </c>
       <c r="G173">
         <f t="shared" si="11"/>
-        <v>10.699707369600874</v>
+        <v>15.304877555588964</v>
       </c>
       <c r="H173">
         <v>11.200222838687612</v>
@@ -6004,11 +6004,11 @@
       </c>
       <c r="F174">
         <f t="shared" si="10"/>
-        <v>44760.126024652556</v>
+        <v>4476012.6024652552</v>
       </c>
       <c r="G174">
         <f t="shared" si="11"/>
-        <v>10.709072977986075</v>
+        <v>15.314243163974165</v>
       </c>
       <c r="H174">
         <v>11.203581884341308</v>
@@ -6034,11 +6034,11 @@
       </c>
       <c r="F175">
         <f t="shared" si="10"/>
-        <v>44257.696164374473</v>
+        <v>4425769.6164374473</v>
       </c>
       <c r="G175">
         <f t="shared" si="11"/>
-        <v>10.697784559931575</v>
+        <v>15.302954745919665</v>
       </c>
       <c r="H175">
         <v>11.202337520008705</v>
@@ -6064,11 +6064,11 @@
       </c>
       <c r="F176">
         <f t="shared" si="10"/>
-        <v>44926.190862894364</v>
+        <v>4492619.0862894366</v>
       </c>
       <c r="G176">
         <f t="shared" si="11"/>
-        <v>10.712776219099975</v>
+        <v>15.317946405088067</v>
       </c>
       <c r="H176">
         <v>11.211138536571827</v>
@@ -6094,11 +6094,11 @@
       </c>
       <c r="F177">
         <f t="shared" si="10"/>
-        <v>44918.023972527633</v>
+        <v>4491802.3972527636</v>
       </c>
       <c r="G177">
         <f t="shared" si="11"/>
-        <v>10.712594417958874</v>
+        <v>15.317764603946966</v>
       </c>
       <c r="H177">
         <v>11.208470423126608</v>
@@ -6124,11 +6124,11 @@
       </c>
       <c r="F178">
         <f t="shared" si="10"/>
-        <v>44568.727300390863</v>
+        <v>4456872.7300390871</v>
       </c>
       <c r="G178">
         <f t="shared" si="11"/>
-        <v>10.704787710459774</v>
+        <v>15.309957896447866</v>
       </c>
       <c r="H178">
         <v>11.207950944406583</v>
@@ -6154,11 +6154,11 @@
       </c>
       <c r="F179">
         <f t="shared" si="10"/>
-        <v>45089.157412401932</v>
+        <v>4508915.7412401922</v>
       </c>
       <c r="G179">
         <f t="shared" si="11"/>
-        <v>10.716397084445275</v>
+        <v>15.321567270433365</v>
       </c>
       <c r="H179">
         <v>11.215747704038442</v>
@@ -6184,11 +6184,11 @@
       </c>
       <c r="F180">
         <f t="shared" si="10"/>
-        <v>44962.522903547921</v>
+        <v>4496252.290354793</v>
       </c>
       <c r="G180">
         <f t="shared" si="11"/>
-        <v>10.713584597395975</v>
+        <v>15.318754783384067</v>
       </c>
       <c r="H180">
         <v>11.217962125350629</v>
@@ -6214,11 +6214,11 @@
       </c>
       <c r="F181">
         <f t="shared" si="10"/>
-        <v>45181.202511308315</v>
+        <v>4518120.2511308324</v>
       </c>
       <c r="G181">
         <f t="shared" si="11"/>
-        <v>10.718436405677275</v>
+        <v>15.323606591665365</v>
       </c>
       <c r="H181">
         <v>11.221017508458294</v>
@@ -6244,11 +6244,11 @@
       </c>
       <c r="F182">
         <f t="shared" si="10"/>
-        <v>44829.536731102075</v>
+        <v>4482953.6731102075</v>
       </c>
       <c r="G182">
         <f t="shared" si="11"/>
-        <v>10.7106225031925</v>
+        <v>15.315792689180592</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.3">
@@ -6271,11 +6271,11 @@
       </c>
       <c r="F183">
         <f t="shared" si="10"/>
-        <v>44943.951309062024</v>
+        <v>4494395.1309062019</v>
       </c>
       <c r="G183">
         <f t="shared" si="11"/>
-        <v>10.713171465974401</v>
+        <v>15.318341651962493</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.3">
@@ -6298,11 +6298,11 @@
       </c>
       <c r="F184">
         <f t="shared" si="10"/>
-        <v>40364.850597725184</v>
+        <v>4036485.0597725185</v>
       </c>
       <c r="G184">
         <f t="shared" si="11"/>
-        <v>10.6057146505396</v>
+        <v>15.210884836527692</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.3">
@@ -6325,11 +6325,11 @@
       </c>
       <c r="F185">
         <f t="shared" si="10"/>
-        <v>34614.895699041328</v>
+        <v>3461489.5699041327</v>
       </c>
       <c r="G185">
         <f t="shared" si="11"/>
-        <v>10.4520393799353</v>
+        <v>15.057209565923392</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.3">
@@ -6352,11 +6352,11 @@
       </c>
       <c r="F186">
         <f t="shared" si="10"/>
-        <v>36224.697523172785</v>
+        <v>3622469.7523172782</v>
       </c>
       <c r="G186">
         <f t="shared" si="11"/>
-        <v>10.497496417207101</v>
+        <v>15.102666603195193</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.3">
@@ -6379,11 +6379,11 @@
       </c>
       <c r="F187">
         <f t="shared" si="10"/>
-        <v>38052.456940210308</v>
+        <v>3805245.6940210308</v>
       </c>
       <c r="G187">
         <f t="shared" si="11"/>
-        <v>10.546720932564201</v>
+        <v>15.151891118552292</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.3">
@@ -6406,11 +6406,11 @@
       </c>
       <c r="F188">
         <f t="shared" si="10"/>
-        <v>39329.389205471161</v>
+        <v>3932938.9205471165</v>
       </c>
       <c r="G188">
         <f t="shared" si="11"/>
-        <v>10.579727335314701</v>
+        <v>15.184897521302792</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.3">
@@ -6433,11 +6433,11 @@
       </c>
       <c r="F189">
         <f t="shared" si="10"/>
-        <v>39481.706982423209</v>
+        <v>3948170.6982423211</v>
       </c>
       <c r="G189">
         <f t="shared" si="11"/>
-        <v>10.583592729249601</v>
+        <v>15.188762915237692</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
@@ -6460,11 +6460,11 @@
       </c>
       <c r="F190">
         <f t="shared" si="10"/>
-        <v>40987.109554496019</v>
+        <v>4098710.9554496016</v>
       </c>
       <c r="G190">
         <f t="shared" si="11"/>
-        <v>10.621012895142201</v>
+        <v>15.226183081130293</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.3">
@@ -6487,11 +6487,11 @@
       </c>
       <c r="F191">
         <f t="shared" si="10"/>
-        <v>42218.419353780031</v>
+        <v>4221841.9353780029</v>
       </c>
       <c r="G191">
         <f t="shared" si="11"/>
-        <v>10.6506118823732</v>
+        <v>15.255782068361292</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.3">
@@ -6514,11 +6514,11 @@
       </c>
       <c r="F192">
         <f t="shared" si="10"/>
-        <v>42596.515619003716</v>
+        <v>4259651.5619003717</v>
       </c>
       <c r="G192">
         <f t="shared" si="11"/>
-        <v>10.6595277359311</v>
+        <v>15.264697921919192</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
@@ -6541,11 +6541,11 @@
       </c>
       <c r="F193">
         <f t="shared" si="10"/>
-        <v>43399.616402705658</v>
+        <v>4339961.6402705666</v>
       </c>
       <c r="G193">
         <f t="shared" si="11"/>
-        <v>10.6782058814021</v>
+        <v>15.283376067390192</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
@@ -6568,11 +6568,11 @@
       </c>
       <c r="F194">
         <f t="shared" si="10"/>
-        <v>42550.883042002257</v>
+        <v>4255088.3042002255</v>
       </c>
       <c r="G194">
         <f t="shared" si="11"/>
-        <v>10.65845588682971</v>
+        <v>15.263626072817802</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
@@ -6594,12 +6594,12 @@
         <v>51117378</v>
       </c>
       <c r="F195">
-        <f t="shared" ref="F195:F253" si="14">D195*10000000/E195</f>
-        <v>43414.098896388597</v>
+        <f t="shared" ref="F195:F253" si="14">D195*1000000000/E195</f>
+        <v>4341409.8896388598</v>
       </c>
       <c r="G195">
         <f t="shared" ref="G195:G253" si="15">LN(F195)</f>
-        <v>10.678539526696911</v>
+        <v>15.283709712685003</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
@@ -6622,11 +6622,11 @@
       </c>
       <c r="F196">
         <f t="shared" si="14"/>
-        <v>44224.441592380317</v>
+        <v>4422444.1592380311</v>
       </c>
       <c r="G196">
         <f t="shared" si="15"/>
-        <v>10.697032892433411</v>
+        <v>15.302203078421503</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
@@ -6649,11 +6649,11 @@
       </c>
       <c r="F197">
         <f t="shared" si="14"/>
-        <v>42980.586545701641</v>
+        <v>4298058.6545701642</v>
       </c>
       <c r="G197">
         <f t="shared" si="15"/>
-        <v>10.668503817048512</v>
+        <v>15.273674003036604</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
@@ -6676,11 +6676,11 @@
       </c>
       <c r="F198">
         <f t="shared" si="14"/>
-        <v>40595.950773921148</v>
+        <v>4059595.0773921143</v>
       </c>
       <c r="G198">
         <f t="shared" si="15"/>
-        <v>10.611423605983511</v>
+        <v>15.216593791971603</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
@@ -6703,11 +6703,11 @@
       </c>
       <c r="F199">
         <f t="shared" si="14"/>
-        <v>43687.449932049924</v>
+        <v>4368744.9932049923</v>
       </c>
       <c r="G199">
         <f t="shared" si="15"/>
-        <v>10.684816152928011</v>
+        <v>15.289986338916103</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
@@ -6730,11 +6730,11 @@
       </c>
       <c r="F200">
         <f t="shared" si="14"/>
-        <v>44139.951018808599</v>
+        <v>4413995.1018808596</v>
       </c>
       <c r="G200">
         <f t="shared" si="15"/>
-        <v>10.69512057013201</v>
+        <v>15.300290756120102</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
@@ -6757,11 +6757,11 @@
       </c>
       <c r="F201">
         <f t="shared" si="14"/>
-        <v>43745.386512984231</v>
+        <v>4374538.6512984233</v>
       </c>
       <c r="G201">
         <f t="shared" si="15"/>
-        <v>10.68614143509361</v>
+        <v>15.291311621081702</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
@@ -6784,11 +6784,11 @@
       </c>
       <c r="F202">
         <f t="shared" si="14"/>
-        <v>46205.503379060909</v>
+        <v>4620550.3379060905</v>
       </c>
       <c r="G202">
         <f t="shared" si="15"/>
-        <v>10.74085419073441</v>
+        <v>15.346024376722502</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
@@ -6811,11 +6811,11 @@
       </c>
       <c r="F203">
         <f t="shared" si="14"/>
-        <v>46114.255982247603</v>
+        <v>4611425.59822476</v>
       </c>
       <c r="G203">
         <f t="shared" si="15"/>
-        <v>10.73887742157561</v>
+        <v>15.344047607563702</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
@@ -6838,11 +6838,11 @@
       </c>
       <c r="F204">
         <f t="shared" si="14"/>
-        <v>46795.331260808722</v>
+        <v>4679533.1260808716</v>
       </c>
       <c r="G204">
         <f t="shared" si="15"/>
-        <v>10.753538717545011</v>
+        <v>15.358708903533103</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
@@ -6865,11 +6865,11 @@
       </c>
       <c r="F205">
         <f t="shared" si="14"/>
-        <v>47534.378533672418</v>
+        <v>4753437.853367242</v>
       </c>
       <c r="G205">
         <f t="shared" si="15"/>
-        <v>10.76920848683941</v>
+        <v>15.374378672827502</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
@@ -6892,11 +6892,11 @@
       </c>
       <c r="F206">
         <f t="shared" si="14"/>
-        <v>45706.476686307236</v>
+        <v>4570647.6686307238</v>
       </c>
       <c r="G206">
         <f t="shared" si="15"/>
-        <v>10.729995288641744</v>
+        <v>15.335165474629836</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
@@ -6919,11 +6919,11 @@
       </c>
       <c r="F207">
         <f t="shared" si="14"/>
-        <v>46276.403320183003</v>
+        <v>4627640.3320183</v>
       </c>
       <c r="G207">
         <f t="shared" si="15"/>
-        <v>10.742387462647644</v>
+        <v>15.347557648635735</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
@@ -6946,11 +6946,11 @@
       </c>
       <c r="F208">
         <f t="shared" si="14"/>
-        <v>47077.818957260592</v>
+        <v>4707781.8957260596</v>
       </c>
       <c r="G208">
         <f t="shared" si="15"/>
-        <v>10.759557233989744</v>
+        <v>15.364727419977836</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
@@ -6973,11 +6973,11 @@
       </c>
       <c r="F209">
         <f t="shared" si="14"/>
-        <v>47126.298520070544</v>
+        <v>4712629.8520070538</v>
       </c>
       <c r="G209">
         <f t="shared" si="15"/>
-        <v>10.760586479173243</v>
+        <v>15.365756665161335</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
@@ -7000,11 +7000,11 @@
       </c>
       <c r="F210">
         <f t="shared" si="14"/>
-        <v>47179.25187735536</v>
+        <v>4717925.1877355361</v>
       </c>
       <c r="G210">
         <f t="shared" si="15"/>
-        <v>10.761709496060943</v>
+        <v>15.366879682049035</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
@@ -7027,11 +7027,11 @@
       </c>
       <c r="F211">
         <f t="shared" si="14"/>
-        <v>47000.851617294487</v>
+        <v>4700085.1617294485</v>
       </c>
       <c r="G211">
         <f t="shared" si="15"/>
-        <v>10.757921000044943</v>
+        <v>15.363091186033035</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
@@ -7054,11 +7054,11 @@
       </c>
       <c r="F212">
         <f t="shared" si="14"/>
-        <v>46671.136077162788</v>
+        <v>4667113.6077162782</v>
       </c>
       <c r="G212">
         <f t="shared" si="15"/>
-        <v>10.750881181419443</v>
+        <v>15.356051367407535</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
@@ -7081,11 +7081,11 @@
       </c>
       <c r="F213">
         <f t="shared" si="14"/>
-        <v>47502.690154995144</v>
+        <v>4750269.0154995145</v>
       </c>
       <c r="G213">
         <f t="shared" si="15"/>
-        <v>10.768541623261044</v>
+        <v>15.373711809249135</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
@@ -7108,11 +7108,11 @@
       </c>
       <c r="F214">
         <f t="shared" si="14"/>
-        <v>48157.933528399546</v>
+        <v>4815793.3528399542</v>
       </c>
       <c r="G214">
         <f t="shared" si="15"/>
-        <v>10.782241170598644</v>
+        <v>15.387411356586735</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
@@ -7135,11 +7135,11 @@
       </c>
       <c r="F215">
         <f t="shared" si="14"/>
-        <v>47859.659756188637</v>
+        <v>4785965.9756188635</v>
       </c>
       <c r="G215">
         <f t="shared" si="15"/>
-        <v>10.776028252289343</v>
+        <v>15.381198438277435</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
@@ -7162,11 +7162,11 @@
       </c>
       <c r="F216">
         <f t="shared" si="14"/>
-        <v>46658.362313381782</v>
+        <v>4665836.2313381778</v>
       </c>
       <c r="G216">
         <f t="shared" si="15"/>
-        <v>10.750607446660743</v>
+        <v>15.355777632648834</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
@@ -7189,11 +7189,11 @@
       </c>
       <c r="F217">
         <f t="shared" si="14"/>
-        <v>47405.329891456488</v>
+        <v>4740532.9891456496</v>
       </c>
       <c r="G217">
         <f t="shared" si="15"/>
-        <v>10.766489946329143</v>
+        <v>15.371660132317235</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
@@ -7216,11 +7216,11 @@
       </c>
       <c r="F218">
         <f t="shared" si="14"/>
-        <v>47175.031524955783</v>
+        <v>4717503.1524955789</v>
       </c>
       <c r="G218">
         <f t="shared" si="15"/>
-        <v>10.761620038492083</v>
+        <v>15.366790224480173</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
@@ -7243,11 +7243,11 @@
       </c>
       <c r="F219">
         <f t="shared" si="14"/>
-        <v>47020.99172238852</v>
+        <v>4702099.1722388528</v>
       </c>
       <c r="G219">
         <f t="shared" si="15"/>
-        <v>10.758349413372882</v>
+        <v>15.363519599360973</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
@@ -7270,11 +7270,11 @@
       </c>
       <c r="F220">
         <f t="shared" si="14"/>
-        <v>47151.641775498952</v>
+        <v>4715164.1775498949</v>
       </c>
       <c r="G220">
         <f t="shared" si="15"/>
-        <v>10.761124107720482</v>
+        <v>15.366294293708572</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
@@ -7297,11 +7297,11 @@
       </c>
       <c r="F221">
         <f t="shared" si="14"/>
-        <v>46115.68849629123</v>
+        <v>4611568.8496291228</v>
       </c>
       <c r="G221">
         <f t="shared" si="15"/>
-        <v>10.738908485544084</v>
+        <v>15.344078671532174</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
@@ -7324,11 +7324,11 @@
       </c>
       <c r="F222">
         <f t="shared" si="14"/>
-        <v>46692.00297546776</v>
+        <v>4669200.297546776</v>
       </c>
       <c r="G222">
         <f t="shared" si="15"/>
-        <v>10.751328186497981</v>
+        <v>15.356498372486072</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
@@ -7351,11 +7351,11 @@
       </c>
       <c r="F223">
         <f t="shared" si="14"/>
-        <v>47662.96820902804</v>
+        <v>4766296.8209028039</v>
       </c>
       <c r="G223">
         <f t="shared" si="15"/>
-        <v>10.771910027543283</v>
+        <v>15.377080213531373</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
@@ -7378,11 +7378,11 @@
       </c>
       <c r="F224">
         <f t="shared" si="14"/>
-        <v>46216.570864356305</v>
+        <v>4621657.0864356309</v>
       </c>
       <c r="G224">
         <f t="shared" si="15"/>
-        <v>10.741093689478383</v>
+        <v>15.346263875466473</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
@@ -7405,11 +7405,11 @@
       </c>
       <c r="F225">
         <f t="shared" si="14"/>
-        <v>46971.897283387239</v>
+        <v>4697189.728338724</v>
       </c>
       <c r="G225">
         <f t="shared" si="15"/>
-        <v>10.757304771719983</v>
+        <v>15.362474957708073</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
@@ -7432,11 +7432,11 @@
       </c>
       <c r="F226">
         <f t="shared" si="14"/>
-        <v>47107.337733329754</v>
+        <v>4710733.7733329758</v>
       </c>
       <c r="G226">
         <f t="shared" si="15"/>
-        <v>10.760184058386983</v>
+        <v>15.365354244375073</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
@@ -7459,11 +7459,11 @@
       </c>
       <c r="F227">
         <f t="shared" si="14"/>
-        <v>46645.030802335423</v>
+        <v>4664503.0802335422</v>
       </c>
       <c r="G227">
         <f t="shared" si="15"/>
-        <v>10.750321679751483</v>
+        <v>15.355491865739573</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
@@ -7486,11 +7486,11 @@
       </c>
       <c r="F228">
         <f t="shared" si="14"/>
-        <v>47691.259206468698</v>
+        <v>4769125.9206468696</v>
       </c>
       <c r="G228">
         <f t="shared" si="15"/>
-        <v>10.772503414937583</v>
+        <v>15.377673600925673</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
@@ -7513,11 +7513,11 @@
       </c>
       <c r="F229">
         <f t="shared" si="14"/>
-        <v>47109.027810482185</v>
+        <v>4710902.7810482187</v>
       </c>
       <c r="G229">
         <f t="shared" si="15"/>
-        <v>10.760219934896183</v>
+        <v>15.365390120884273</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
@@ -7540,11 +7540,11 @@
       </c>
       <c r="F230">
         <f t="shared" si="14"/>
-        <v>47109.50570765289</v>
+        <v>4710950.5707652895</v>
       </c>
       <c r="G230">
         <f t="shared" si="15"/>
-        <v>10.760230079337045</v>
+        <v>15.365400265325135</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
@@ -7567,11 +7567,11 @@
       </c>
       <c r="F231">
         <f t="shared" si="14"/>
-        <v>46950.217024958074</v>
+        <v>4695021.7024958069</v>
       </c>
       <c r="G231">
         <f t="shared" si="15"/>
-        <v>10.756843107095547</v>
+        <v>15.362013293083637</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
@@ -7594,11 +7594,11 @@
       </c>
       <c r="F232">
         <f t="shared" si="14"/>
-        <v>46402.92621437183</v>
+        <v>4640292.6214371826</v>
       </c>
       <c r="G232">
         <f t="shared" si="15"/>
-        <v>10.745117801190746</v>
+        <v>15.350287987178836</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
@@ -7621,11 +7621,11 @@
       </c>
       <c r="F233">
         <f t="shared" si="14"/>
-        <v>47631.972036451218</v>
+        <v>4763197.2036451222</v>
       </c>
       <c r="G233">
         <f t="shared" si="15"/>
-        <v>10.771259496180544</v>
+        <v>15.376429682168636</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
@@ -7648,11 +7648,11 @@
       </c>
       <c r="F234">
         <f t="shared" si="14"/>
-        <v>47456.241381917403</v>
+        <v>4745624.13819174</v>
       </c>
       <c r="G234">
         <f t="shared" si="15"/>
-        <v>10.767563331360947</v>
+        <v>15.372733517349037</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
@@ -7675,11 +7675,11 @@
       </c>
       <c r="F235">
         <f t="shared" si="14"/>
-        <v>46459.339982663754</v>
+        <v>4645933.9982663747</v>
       </c>
       <c r="G235">
         <f t="shared" si="15"/>
-        <v>10.746332800081946</v>
+        <v>15.351502986070036</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
@@ -7702,11 +7702,11 @@
       </c>
       <c r="F236">
         <f t="shared" si="14"/>
-        <v>47247.355160589461</v>
+        <v>4724735.516058946</v>
       </c>
       <c r="G236">
         <f t="shared" si="15"/>
-        <v>10.763151955917946</v>
+        <v>15.368322141906036</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
@@ -7729,11 +7729,11 @@
       </c>
       <c r="F237">
         <f t="shared" si="14"/>
-        <v>47095.184773706213</v>
+        <v>4709518.4773706216</v>
       </c>
       <c r="G237">
         <f t="shared" si="15"/>
-        <v>10.759926040674344</v>
+        <v>15.365096226662436</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
@@ -7756,11 +7756,11 @@
       </c>
       <c r="F238">
         <f t="shared" si="14"/>
-        <v>46980.287181074047</v>
+        <v>4698028.7181074051</v>
       </c>
       <c r="G238">
         <f t="shared" si="15"/>
-        <v>10.757483371031046</v>
+        <v>15.362653557019136</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
@@ -7783,11 +7783,11 @@
       </c>
       <c r="F239">
         <f t="shared" si="14"/>
-        <v>47845.125731178596</v>
+        <v>4784512.5731178606</v>
       </c>
       <c r="G239">
         <f t="shared" si="15"/>
-        <v>10.775724526095345</v>
+        <v>15.380894712083435</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
@@ -7810,11 +7810,11 @@
       </c>
       <c r="F240">
         <f t="shared" si="14"/>
-        <v>47356.685239378763</v>
+        <v>4735668.5239378754</v>
       </c>
       <c r="G240">
         <f t="shared" si="15"/>
-        <v>10.765463276385846</v>
+        <v>15.370633462373936</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
@@ -7837,11 +7837,11 @@
       </c>
       <c r="F241">
         <f t="shared" si="14"/>
-        <v>48217.028939428645</v>
+        <v>4821702.8939428646</v>
       </c>
       <c r="G241">
         <f t="shared" si="15"/>
-        <v>10.783467535142346</v>
+        <v>15.388637721130436</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
@@ -7864,11 +7864,11 @@
       </c>
       <c r="F242">
         <f t="shared" si="14"/>
-        <v>47811.895578828611</v>
+        <v>4781189.5578828612</v>
       </c>
       <c r="G242">
         <f t="shared" si="15"/>
-        <v>10.775029749000435</v>
+        <v>15.380199934988527</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
@@ -7891,11 +7891,11 @@
       </c>
       <c r="F243">
         <f t="shared" si="14"/>
-        <v>47857.799239206259</v>
+        <v>4785779.9239206258</v>
       </c>
       <c r="G243">
         <f t="shared" si="15"/>
-        <v>10.775989377103935</v>
+        <v>15.381159563092027</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
@@ -7918,11 +7918,11 @@
       </c>
       <c r="F244">
         <f t="shared" si="14"/>
-        <v>47435.115833183867</v>
+        <v>4743511.5833183872</v>
       </c>
       <c r="G244">
         <f t="shared" si="15"/>
-        <v>10.767118073758935</v>
+        <v>15.372288259747027</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
@@ -7945,11 +7945,11 @@
       </c>
       <c r="F245">
         <f t="shared" si="14"/>
-        <v>47893.89355304381</v>
+        <v>4789389.3553043818</v>
       </c>
       <c r="G245">
         <f t="shared" si="15"/>
-        <v>10.776743292037334</v>
+        <v>15.381913478025426</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
@@ -7972,11 +7972,11 @@
       </c>
       <c r="F246">
         <f t="shared" si="14"/>
-        <v>48062.648518758404</v>
+        <v>4806264.8518758407</v>
       </c>
       <c r="G246">
         <f t="shared" si="15"/>
-        <v>10.780260616360435</v>
+        <v>15.385430802348527</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
@@ -7999,11 +7999,11 @@
       </c>
       <c r="F247">
         <f t="shared" si="14"/>
-        <v>47657.375474804023</v>
+        <v>4765737.5474804016</v>
       </c>
       <c r="G247">
         <f t="shared" si="15"/>
-        <v>10.771792681465534</v>
+        <v>15.376962867453626</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
@@ -8026,11 +8026,11 @@
       </c>
       <c r="F248">
         <f t="shared" si="14"/>
-        <v>49038.848259621132</v>
+        <v>4903884.8259621132</v>
       </c>
       <c r="G248">
         <f t="shared" si="15"/>
-        <v>10.800368084600635</v>
+        <v>15.405538270588726</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
@@ -8053,11 +8053,11 @@
       </c>
       <c r="F249">
         <f t="shared" si="14"/>
-        <v>47903.915949798189</v>
+        <v>4790391.5949798198</v>
       </c>
       <c r="G249">
         <f t="shared" si="15"/>
-        <v>10.776952532662834</v>
+        <v>15.382122718650926</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
@@ -8080,11 +8080,11 @@
       </c>
       <c r="F250">
         <f t="shared" si="14"/>
-        <v>48492.391222104299</v>
+        <v>4849239.1222104291</v>
       </c>
       <c r="G250">
         <f t="shared" si="15"/>
-        <v>10.789162182599835</v>
+        <v>15.394332368587927</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
@@ -8107,11 +8107,11 @@
       </c>
       <c r="F251">
         <f t="shared" si="14"/>
-        <v>48741.364530343963</v>
+        <v>4874136.4530343963</v>
       </c>
       <c r="G251">
         <f t="shared" si="15"/>
-        <v>10.794283322896135</v>
+        <v>15.399453508884227</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
@@ -8134,11 +8134,11 @@
       </c>
       <c r="F252">
         <f t="shared" si="14"/>
-        <v>48216.561390085546</v>
+        <v>4821656.1390085556</v>
       </c>
       <c r="G252">
         <f t="shared" si="15"/>
-        <v>10.783457838327335</v>
+        <v>15.388628024315427</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
@@ -8161,11 +8161,11 @@
       </c>
       <c r="F253">
         <f t="shared" si="14"/>
-        <v>48647.013031598835</v>
+        <v>4864701.3031598832</v>
       </c>
       <c r="G253">
         <f t="shared" si="15"/>
-        <v>10.792345688639834</v>
+        <v>15.397515874627926</v>
       </c>
     </row>
   </sheetData>
